--- a/docs/mat-bang-neo-ban-mong/bang_tinh_neo.xlsx
+++ b/docs/mat-bang-neo-ban-mong/bang_tinh_neo.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A78"/>
   <cols>
     <col min="1" max="1" width="180.83203125" customWidth="1"/>
   </cols>
@@ -556,207 +556,257 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">  BÈ 7 (bè có lực dây lớn nhất): F = 324,0 kN; chi phối ở mực nước 654,00 m, tải đẩy về hướng 135°, dây B7-D06 chịu 102,0 kN, 22 dây cùng căng; bè trôi 0,27 m. Mất dây B7-D06: dây lớn nhất còn lại 118,3 kN.</v>
+        <v xml:space="preserve">  Lực một dây: T = (EA / L_0) × (d − L_0) khi d &gt; L_0, T = 0 khi d ≤ L_0 (dây chùng). d là khoảng cách thẳng bích bè – chốt neo khi bè đã dịch đi, L_0 là chiều dài dây lúc vừa căng. Cáp PES-36: EA = 15 × 385 = 5.775 kN. Dây càng ngắn (L_0 nhỏ) càng cứng nên nhận càng nhiều lực.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">  Lực dây thiết kế của BÈ 7: T = 107,0 kN (đã cộng lực căng trước 5 kN; không nhỏ hơn F / (n × cos α) = 67,4 kN); khi đứt một dây: 123,3 kN. Cáp và cọc bờ của bè kiểm tra với lực này; mỗi đế vít xoắn kiểm tra với lực lớn nhất của chính (các) dây nối vào nó (bao mọi hướng, mọi mực nước).</v>
+        <v xml:space="preserve">  Vị trí cân bằng: độ dịch u của bè sao cho tổng thành phần ngang của lực các dây đang căng bằng F theo hướng tải; T thiết kế = T lớn nhất trên mọi hướng, mọi mực nước + lực căng trước T_0 = 5 kN.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">  Cáp PES-36, lực đứt 385 kN: hệ số an toàn 3,60 (yêu cầu ≥ 3,0); khi đứt một dây 3,12 (yêu cầu ≥ 2,0).</v>
+        <v xml:space="preserve">  BÈ 7 (bè có lực dây lớn nhất): F = 324,0 kN; chi phối ở mực nước 654,00 m, tải đẩy về hướng 135°, dây B7-D06 chịu 102,0 kN, 22 dây cùng căng; bè trôi 0,27 m. Mất dây B7-D06: dây lớn nhất còn lại 118,3 kN.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">  Độ trôi bè lớn nhất (mọi hướng, mọi mực nước): 0,5 – 0,9 m tùy bè (kiểm tra C12: ≤ nửa khoảng hở nhỏ nhất tới bè bên cạnh).</v>
+        <v xml:space="preserve">  Lực dây thiết kế của BÈ 7: T = 107,0 kN (đã cộng lực căng trước 5 kN; không nhỏ hơn F / (n × cos α) = 67,4 kN); khi đứt một dây: 123,3 kN. Cáp và cọc bờ của bè kiểm tra với lực này; mỗi đế vít xoắn kiểm tra với lực lớn nhất của chính (các) dây nối vào nó (bao mọi hướng, mọi mực nước).</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v/>
+        <v xml:space="preserve">  Cáp PES-36, lực đứt 385 kN: hệ số an toàn MBL / T = 385 / 107,0 = 3,60 (yêu cầu ≥ 3,0); khi đứt một dây 385 / 123,3 = 3,12 (yêu cầu ≥ 2,0).</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>5. Cọc khoan nhồi ven bờ (ví dụ BÈ 7)</v>
+        <v xml:space="preserve">  C9, khoảng cách trung bình giữa các dây: chu vi / số dây = 583,9 / 40 = 14,6 m ≤ 15 m (bắt buộc; các bè: 13,5–15,0 m).</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">  Cọc tròn D350 đổ tại chỗ, ngàm L_tk = 6,5 m, dài cả cọc 6,6 m; thép chủ 6Φ25 CB400-V, Đai xoắn Φ8 a150. Cáp móc cách mặt đất 0,1 m.</v>
+        <v xml:space="preserve">  C8, khoảng hở đáy bè – đáy hồ = chiều sâu nước − mớn nước bè = 13,40 m ở MNDB ≥ 1,5 m; ở MNC còn 13,40 − (662,76 − 649,50) = 0,14 m — DƯỚI mức 1,5 m.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">  Điểm neo CỌC ĐÔI: 2 cọc cạnh nhau, vuông góc phương cáp, cách nhau ≥ 3D; mỗi cọc chịu P = T / (2 × 0,9) = 59,4 kN (hệ số nhóm là GIẢ ĐỊNH); đài BTCT nối hai đầu cọc: thiết kế sơ bộ ở bảng thống kê vật tư neo (twinPileCap.ts).</v>
+        <v xml:space="preserve">  Độ trôi bè lớn nhất (mọi hướng, mọi mực nước): 0,5 – 0,9 m tùy bè (kiểm tra C12: ≤ nửa khoảng hở nhỏ nhất tới bè bên cạnh).</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">  BP-1, sức chịu ngang theo Broms (cọc ngắn trong đất sét): H_u = 290,2 kN; cho phép H_u / 2,5 = 116,1 kN ≥ P = 59,4 kN; mức sử dụng 0,51.</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">  BP-2, uốn thân cọc (TCVN 5574:2018): 1,2 × M_max = 1,2 × 51,2 = 61,4 kNm ≤ M_rd = 74,4 kNm; mức sử dụng 0,83.</v>
+        <v>5. Cọc khoan nhồi ven bờ (ví dụ BÈ 7)</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">  Cả hệ: 220 cọc, tổng dài 1.452,0 m, 139,7 m³ bê tông, 38,8 tấn thép. Lực kiểm tra cọc là toàn bộ lực dây (không giảm theo góc xiên), thiên về an toàn.</v>
+        <v xml:space="preserve">  Cọc tròn D350 đổ tại chỗ, ngàm L_tk = 6,5 m, dài cả cọc 6,6 m; thép chủ 6Φ25 CB400-V, Đai xoắn Φ8 a150. Cáp móc cách mặt đất 0,1 m.</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v xml:space="preserve">  Điểm neo CỌC ĐÔI: 2 cọc cạnh nhau, vuông góc phương cáp, cách nhau ≥ 3D; mỗi cọc chịu P = T / (2 × 0,9) = 59,4 kN (hệ số nhóm là GIẢ ĐỊNH); đài BTCT nối hai đầu cọc: thiết kế sơ bộ ở bảng thống kê vật tư neo (twinPileCap.ts).</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>6. Đế BTCT + vít xoắn (ví dụ BM-DV074, đế làm việc nặng nhất)</v>
+        <v xml:space="preserve">  BP-1, sức chịu ngang theo Broms (cọc ngắn trong đất sét). Sức kháng của đất trên 1 m cọc: p = 9 × c_u × D = 9 × 40 × 0,35 = 126,0 kN/m; đoạn 1,5D = 0,525 m dưới mặt đất không tính, phần ngàm làm việc g = L_tk − 1,5D = 6,5 − 0,525 = 5,975 m; tim chốt cáp cao e = 0,10 m trên mặt đất.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">  Một vít: ống Ø89×5, ren Ø105, ngàm 3,0 m. Sức chịu nhổ cực hạn Q_u = α × c_u × π × D_ren × L = 0,8 × 20 × π × 0,105 × 3,0 = 15,8 kN; cho phép Q_a = Q_u / 2 = 7,9 kN. Sức chịu ngang cực hạn H_u = 15,0 kN.</v>
+        <v xml:space="preserve">  H_u là nghiệm dương của (0,5 / p) × H_u² + (e + 1,5D + g) × H_u − 0,5 × p × g² = 0, tức (0,5 / 126,0) × H_u² + 6,600 × H_u − 2.249,1 = 0 → H_u = 290,2 kN. Cho phép H_u / 2,5 = 116,1 kN ≥ P = 59,4 kN; mức sử dụng = 59,4 / 116,1 = 0,51.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">  Đế BM-DV074 giữ hai dây B7-D06 (BÈ 7, T = 107,0 kN, dài 14,01 m) và B8-D19 (BÈ 8, T = 61,0 kN, dài 14,01 m). Bích bè cao hơn mặt nước 0,35 m.</v>
+        <v xml:space="preserve">  BP-2, uốn thân cọc (TCVN 5574:2018). Mô-men lớn nhất trong cọc: M_max = P × (e + 1,5D + 0,5 × P / p) = 59,4 × (0,10 + 0,525 + 0,5 × 59,4 / 126,0) = 51,2 kNm.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">  Tổ hợp chi phối: cả hai dây căng (MN cao). Lực nhổ T_v = 136,1 kN (hai dây cộng lại), lực ngang T_h = 26,9 kN (cộng véc-tơ).</v>
+        <v xml:space="preserve">  Khả năng chịu uốn của lồng 6 thanh Φ25 đặt trên vòng tròn: M_rd = A_1 thanh × R_s × r × k(n) = 490,9 mm² × 350 MPa × 0,125 m × 3,46 = 74,4 kNm (r = D/2 − 50 mm tới tim thép; k(n) = 2 / tan(π/n) là cánh tay đòn của n thanh ở hướng BẤT LỢI nhất, vì lồng thả vào lỗ khoan không định hướng được; bỏ qua bê tông chịu kéo).</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v xml:space="preserve">  Đế 5,00 × 5,00 × 0,4 m: thể tích 10,00 m³, nặng 250,0 kN trên cạn, W' = 10,00 × (25 − 10) = 150,0 kN trong nước (đã trừ lực đẩy nổi).</v>
+        <v xml:space="preserve">  Kiểm tra: 1,2 × M_max = 1,2 × 51,2 = 61,4 kNm ≤ M_rd = 74,4 kNm; mức sử dụng 0,83 (1,2 là hệ số tải trọng khi kiểm tra uốn).</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v xml:space="preserve">  SV-1 nhổ: T_v ≤ 0,9 × W' + 4 × Q_a = 166,7 kN; mức sử dụng 0,82.</v>
+        <v xml:space="preserve">  Cả hệ: 220 cọc, tổng dài 1.452,0 m, 139,7 m³ bê tông, 38,8 tấn thép. Lực kiểm tra cọc là toàn bộ lực dây (không giảm theo góc xiên), thiên về an toàn.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v xml:space="preserve">  SV-2 trượt: 1,5 × T_h ≤ bám dính đáy + gờ + 4 × H_u; mức sử dụng 0,45 (bám dính đáy lấy bằng 0 khi T_v &gt; W').</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">  SV-3 lật quanh mép đế: 1,5 × M_lật = 1,5 × 355,0 ≤ M_giữ = 533,3 kNm; mức sử dụng 1,00.</v>
+        <v>6. Đế BTCT + vít xoắn (ví dụ BM-DV074, đế làm việc nặng nhất)</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v xml:space="preserve">  SV-4 một vít: N_1 = 1,8 kN ≤ Q_a; mức sử dụng 0,23. SV-5 nền: 0,15. SV-6 thép bản (lưới Ø12 a200, hai lớp): 0,62.</v>
+        <v xml:space="preserve">  Một vít: ống Ø89×5, ren Ø105, ngàm 3,0 m. Sức chịu nhổ cực hạn Q_u = α × c_u × π × D_ren × L = 0,8 × 20 × π × 0,105 × 3,0 = 15,8 kN; cho phép Q_a = Q_u / 2 = 7,9 kN. Sức chịu ngang cực hạn H_u = 15,0 kN.</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">  Cả hệ: 101 đế (54 đế 2,50 m, 8 đế 2,75 m, 1 đế 3,00 m, 9 đế 3,25 m, 12 đế 3,50 m, 7 đế 3,75 m, 3 đế 4,00 m, 2 đế 4,25 m, 1 đế 4,50 m, 3 đế 4,75 m, 1 đế 5,00 m), 405,0 m³ bê tông, 17,9 tấn thép bản, 404 vít (1.506 m), đế nặng nhất khi cẩu 28,7 tấn.</v>
+        <v xml:space="preserve">  Đế BM-DV074 giữ hai dây B7-D06 (BÈ 7, T = 107,0 kN, dài 14,01 m) và B8-D19 (BÈ 8, T = 61,0 kN, dài 14,01 m). Bích bè cao hơn mặt nước 0,35 m.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v xml:space="preserve">  Tổng lực nhổ lên 101 đế 5.894 kN, tổng sức chống nhổ 8.693 kN. Mức sử dụng lớn nhất: nhổ 0,93, trượt 0,99, lật 1,00, một vít 0,95.</v>
+        <v xml:space="preserve">  Mỗi dây tách thành lực ngang T_h = T × cos θ và lực nhổ T_v = T × sin θ, θ là góc dốc của dây (tan θ = chênh cao bích bè – chốt đế / khoảng cách ngang): dây thoải khi nước thấp (trượt chi phối), dốc khi nước cao (nhổ, lật chi phối).</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v/>
+        <v xml:space="preserve">  Tổ hợp chi phối: cả hai dây căng (MN cao). Lực nhổ T_v = 136,1 kN (hai dây cộng lại), lực ngang T_h = 26,9 kN (cộng véc-tơ).</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>7. Chiều dài cắt cáp và điều chỉnh dây</v>
+        <v xml:space="preserve">  Đế 5,00 × 5,00 × 0,4 m: thể tích 10,00 m³, nặng 250,0 kN trên cạn, W' = 10,00 × (25 − 10) = 150,0 kN trong nước (đã trừ lực đẩy nổi).</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v xml:space="preserve">  Mỗi dây cắt đủ dài cho mực nước làm khoảng cách bích – chốt dài nhất (138 dây đáy ở MNLKT, 133 dây bờ ở MNC). Tổng chiều dài cắt: dây bờ 5.715 m, dây đáy 3.661 m, chưa gồm đoạn bện đầu và phụ kiện.</v>
+        <v xml:space="preserve">  SV-1 nhổ: T_v ≤ 0,9 × W' + 4 × Q_a = 166,7 kN; mức sử dụng 0,82.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v xml:space="preserve">  Thiết bị bù / điều chỉnh ở đầu bè phải thu – xả được: dây đáy tới 15,9 m, dây bờ tới 4,6 m (độ chùng lớn nhất của dây cắt cố định), và giữ được lực dây thiết kế. Thiết bị này CHƯA thiết kế.</v>
+        <v xml:space="preserve">  SV-2 trượt: 1,5 × T_h ≤ bám dính đáy + gờ + 4 × H_u. Bám dính đáy = 0,5 × c_u × B² = 250,0 kN (lấy bằng 0 khi T_v &gt; W': đế bị nhấc khỏi bùn); gờ sâu z = 0,15 m: B × (0,5 × γ' × z² + 2 × c_u × z) = 30,3 kN; H_u một vít = 15,0 kN (Broms, đầu tự do ở mặt bùn). 1,5 × 26,9 = 40,4 ≤ 340,3 kN; mức sử dụng 0,45.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
+        <v xml:space="preserve">  SV-3 lật quanh mép đáy phía xa dây: M_lật = T_h × (t + h_tai) + T_v × B / 2 = 26,9 × (0,4 + 0,15) + 136,1 × 5,00 / 2 = 355,0 kNm; M_giữ = W' × B / 2 + (n/2) × Q_u × (B − c) + (n/2) × Q_u × c = 533,3 kNm (c = 0,15 m từ mép đế tới tim lỗ vít). 1,5 × 355,0 = 532,5 ≤ 533,3 kNm; mức sử dụng 1,00.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>8. Giả định và vấn đề còn mở</v>
+        <v xml:space="preserve">  SV-4 một vít: lực nhổ lên vít chịu nặng nhất N_1 = max[(T_v − 0,9 × W') / n ; (M_lật − 0,9 × W' × B / 2) / (B − c) / (n/2)] = 1,8 kN ≤ Q_a = 7,9 kN; mức sử dụng 0,23.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v xml:space="preserve">  Mực nước hồ dao động 19,55 m (MNC 649,50 → MNDB 662,76 → MNLKT 669,05 m), gấp hơn 3 lần Huổi Vanh. Cáp cắt cố định không dùng được (lực dây và độ trôi quá lớn — xem bảng so sánh cách bù ở Mục 4). Lực dây tính bằng cân bằng tĩnh từng dây theo mực nước, với giả định dây được BÙ dao động mực nước (mặc định: bù liên tục bằng bộ tự căng có khóa chống bão — CHƯA chọn loại; so sánh cách bù ở Mục 4). Mô hình lấy độ cứng của chính sợi cáp, nên thiết bị bù phải KHÓA được khi có gió bão (khóa an toàn khi mất điện / mất tín hiệu).</v>
+        <v xml:space="preserve">  SV-5 áp lực lên nền bùn: W' / B² = 6,0 kPa ≤ 5,14 × c_u / 2,5 = 41,1 kPa (sức chịu tải giới hạn của nền sét mềm); mức sử dụng 0,15.</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v xml:space="preserve">  Nếu khóa của thiết bị bù KHÔNG khóa kịp, đối trọng chỉ giữ lực căng 5 kN và hành trình dư 3 m mỗi chiều: bè trôi 5,1–6,3 m (tới hết hành trình rồi dây mới căng) và lực dây vọt tới 108–296 kN (hệ số an toàn cáp chỉ 1,3–2,8; đế và cọc không được tính cho lực này). Đối trọng treo tự do KHÔNG đủ giữ bè: cần bộ khóa / phanh chủ động, dự phòng, kiểm tra định kỳ.</v>
+        <v xml:space="preserve">  SV-6 thép bản đế: tai neo kéo lên ở giữa, 4 vít giữ ở các góc; mô-men trên 1 m bản M = (n/2) × Q_u × (s/2) / B = 14,88 kNm/m (s = B − 2c); thép cần A_s = M / (0,9 × h_0 × R_s) = 182 mm²/m, tối thiểu 0,1% = 350 mm²/m; bố trí lưới Ø12 a200 hai lớp = 565 mm²/m; mức sử dụng 0,62.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v xml:space="preserve">  Theo địa hình IFC, 7/8 bè chạm đáy khi nước xuống MNC 649,50 m: BÈ 1 (đáy cao nhất 652,50, trung vị 647,33 m); BÈ 2 (đáy cao nhất 653,28, trung vị 647,00 m); BÈ 4 (đáy cao nhất 652,12, trung vị 647,00 m); BÈ 5 (đáy cao nhất 651,37, trung vị 649,00 m); BÈ 6 (đáy cao nhất 650,47, trung vị 647,27 m); BÈ 7 (đáy cao nhất 653,19, trung vị 649,11 m); BÈ 8 (đáy cao nhất 651,24, trung vị 649,16 m). Đáy thiết kế từng bè là trung vị địa hình IFC dưới bè, chưa phải khảo sát.</v>
+        <v xml:space="preserve">  Cả hệ: 101 đế (54 đế 2,50 m, 8 đế 2,75 m, 1 đế 3,00 m, 9 đế 3,25 m, 12 đế 3,50 m, 7 đế 3,75 m, 3 đế 4,00 m, 2 đế 4,25 m, 1 đế 4,50 m, 3 đế 4,75 m, 1 đế 5,00 m), 405,0 m³ bê tông, 17,9 tấn thép bản, 404 vít (1.506 m), đế nặng nhất khi cẩu 28,7 tấn.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v xml:space="preserve">  Đế vít xoắn đặt trên mặt đất IFC tại chỗ (không phải đáy thiết kế chung như Huổi Vanh): 52/101 đế có nền cao hơn MNC (tới 658,11 m) nên lộ khô khi hồ xuống mực nước chết.</v>
+        <v xml:space="preserve">  Tổng lực nhổ lên 101 đế 5.894 kN, tổng sức chống nhổ 8.693 kN. Mức sử dụng lớn nhất: nhổ 0,93, trượt 0,99, lật 1,00, một vít 0,95.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v xml:space="preserve">  Theo địa hình IFC (lưới ~10 m), 7/271 dây tì lên sườn dốc giữa bè và neo khi nước ở 650–653 m (B1-D01, B2-D08, B3-D13, B3-D38, B6-D17, B8-D06, B8-D18; sâu nhất 1,6 m dưới mặt đất): mô hình coi dây thẳng — cần ống / con lăn chống mài mòn ở đoạn tì, hoặc dời cọc theo khảo sát địa hình.</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v xml:space="preserve">  64/101 đế vít xoắn là đế ĐƠN ở vùng nước trống (không đối diện bè nào và cách bờ quá 60 m): quy tắc của Huổi Vanh "đế chỉ đặt giữa hai bè" không áp dụng được cho mặt bằng này — cần Chủ đầu tư xác nhận.</v>
+        <v>7. Chiều dài cắt cáp và điều chỉnh dây</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">  Vùng gió TCVN 2737:2023 của Sơn La CHƯA tra cứu: mốc so sánh 29,7 m/s (vùng II-B của Huổi Vanh) chỉ là tạm. Độ cứng dây EA = 15 × lực đứt là giả định; mô hình cân bằng không xét xoay bè và tải động.</v>
+        <v xml:space="preserve">  Mỗi dây cắt đủ dài cho mực nước làm khoảng cách bích – chốt dài nhất (138 dây đáy ở MNLKT, 133 dây bờ ở MNC). Tổng chiều dài cắt: dây bờ 5.715 m, dây đáy 3.661 m, chưa gồm đoạn bện đầu và phụ kiện.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">  Mô hình cân bằng không xét phân bố tải không đều trên bè lớn và tải động khi dây đang chùng bị giật căng.</v>
+        <v xml:space="preserve">  Thiết bị bù / điều chỉnh ở đầu bè phải thu – xả được: dây đáy tới 15,9 m, dây bờ tới 4,6 m (độ chùng lớn nhất của dây cắt cố định), và giữ được lực dây thiết kế. Thiết bị này CHƯA thiết kế.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v xml:space="preserve">  Chưa có khảo sát địa chất: c_u đất bờ và bùn đáy là giả định (lấy như Huổi Vanh).</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v xml:space="preserve">  Đế đặt trên địa hình IFC tại chỗ, chưa phải khảo sát. 126/133 cọc bờ đứng ở chỗ mặt đất thấp hơn MNDB.</v>
+        <v>8. Giả định và vấn đề còn mở</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
+        <v xml:space="preserve">  Mực nước hồ dao động 19,55 m (MNC 649,50 → MNDB 662,76 → MNLKT 669,05 m), gấp hơn 3 lần Huổi Vanh. Cáp cắt cố định không dùng được (lực dây và độ trôi quá lớn — xem bảng so sánh cách bù ở Mục 4). Lực dây tính bằng cân bằng tĩnh từng dây theo mực nước, với giả định dây được BÙ dao động mực nước (mặc định: bù liên tục bằng bộ tự căng có khóa chống bão — CHƯA chọn loại; so sánh cách bù ở Mục 4). Mô hình lấy độ cứng của chính sợi cáp, nên thiết bị bù phải KHÓA được khi có gió bão (khóa an toàn khi mất điện / mất tín hiệu).</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v xml:space="preserve">  Nếu khóa của thiết bị bù KHÔNG khóa kịp, đối trọng chỉ giữ lực căng 5 kN và hành trình dư 3 m mỗi chiều: bè trôi 5,1–6,3 m (tới hết hành trình rồi dây mới căng) và lực dây vọt tới 108–296 kN (hệ số an toàn cáp chỉ 1,3–2,8; đế và cọc không được tính cho lực này). Đối trọng treo tự do KHÔNG đủ giữ bè: cần bộ khóa / phanh chủ động, dự phòng, kiểm tra định kỳ.</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v xml:space="preserve">  Theo địa hình IFC, 7/8 bè chạm đáy khi nước xuống MNC 649,50 m: BÈ 1 (đáy cao nhất 652,50, trung vị 647,33 m); BÈ 2 (đáy cao nhất 653,28, trung vị 647,00 m); BÈ 4 (đáy cao nhất 652,12, trung vị 647,00 m); BÈ 5 (đáy cao nhất 651,37, trung vị 649,00 m); BÈ 6 (đáy cao nhất 650,47, trung vị 647,27 m); BÈ 7 (đáy cao nhất 653,19, trung vị 649,11 m); BÈ 8 (đáy cao nhất 651,24, trung vị 649,16 m). Đáy thiết kế từng bè là trung vị địa hình IFC dưới bè, chưa phải khảo sát.</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v xml:space="preserve">  Đế vít xoắn đặt trên mặt đất IFC tại chỗ (không phải đáy thiết kế chung như Huổi Vanh): 52/101 đế có nền cao hơn MNC (tới 658,11 m) nên lộ khô khi hồ xuống mực nước chết.</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v xml:space="preserve">  Theo địa hình IFC (lưới ~10 m), 7/271 dây tì lên sườn dốc giữa bè và neo khi nước ở 650–653 m (B1-D01, B2-D08, B3-D13, B3-D38, B6-D17, B8-D06, B8-D18; sâu nhất 1,6 m dưới mặt đất): mô hình coi dây thẳng — cần ống / con lăn chống mài mòn ở đoạn tì, hoặc dời cọc theo khảo sát địa hình.</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v xml:space="preserve">  64/101 đế vít xoắn là đế ĐƠN ở vùng nước trống (không đối diện bè nào và cách bờ quá 60 m): quy tắc của Huổi Vanh "đế chỉ đặt giữa hai bè" không áp dụng được cho mặt bằng này — cần Chủ đầu tư xác nhận.</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v xml:space="preserve">  Vùng gió TCVN 2737:2023 của Sơn La CHƯA tra cứu: mốc so sánh 29,7 m/s (vùng II-B của Huổi Vanh) chỉ là tạm. Độ cứng dây EA = 15 × lực đứt là giả định; mô hình cân bằng không xét xoay bè và tải động.</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve">  Mô hình cân bằng không xét phân bố tải không đều trên bè lớn và tải động khi dây đang chùng bị giật căng.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v xml:space="preserve">  Chưa có khảo sát địa chất: c_u đất bờ và bùn đáy là giả định (lấy như Huổi Vanh).</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v xml:space="preserve">  Đế đặt trên địa hình IFC tại chỗ, chưa phải khảo sát. 126/133 cọc bờ đứng ở chỗ mặt đất thấp hơn MNDB.</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A78"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/mat-bang-neo-ban-mong/bang_tinh_neo.xlsx
+++ b/docs/mat-bang-neo-ban-mong/bang_tinh_neo.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A78"/>
+  <dimension ref="A1:A104"/>
   <cols>
     <col min="1" max="1" width="180.83203125" customWidth="1"/>
   </cols>
@@ -804,9 +804,139 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>9. Giải thích bảng hạng mục kiểm tra (ví dụ BÈ 7)</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v xml:space="preserve">  Mỗi dòng của bảng kiểm tra trên web: công thức, ý nghĩa các ký hiệu và kết quả của bè ví dụ. Mức sử dụng = tải trọng phải chịu / khả năng chịu (đã chia hệ số an toàn): ≤ 1,00 là đạt. Dòng "KHÔNG ÁP DỤNG" là phép kiểm của loại neo khác, không dùng cho phương án cọc khoan nhồi + đế vít xoắn.</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v xml:space="preserve">  C1 — Sức giữ neo (nguyên vẹn): SF = R_total / H_line ≥ [SF]. R_total là tổng sức giữ của các neo, H_line là lực ngang trong dây; [SF] là hệ số an toàn yêu cầu. Dùng cho neo thả kéo lê trên đáy (neo cày, khối thả). Kết quả BÈ 7: KHÔNG ÁP DỤNG — hệ này không dùng neo thả: sức giữ là của cọc bờ (BP-1, BP-2) và đế vít xoắn (SV-1…SV-6).</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v xml:space="preserve">  C2 — Bền dây/xích neo (nguyên vẹn): SF = MBL / T_max ≥ [SF]. MBL là lực kéo đứt nhỏ nhất của cáp (nhà sản xuất công bố), T_max là lực lớn nhất một dây phải chịu (mô hình cân bằng, đã cộng lực căng trước); [SF] = 3 khi đủ dây. Kết quả BÈ 7: ĐẠT: giá trị 3,60, yêu cầu 3, mức sử dụng 0,83.</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v xml:space="preserve">  C3 — Không nhổ neo (chiều dài dây nằm đáy): L_ground ≥ L_ground,min. L_ground là chiều dài xích / cáp nằm trên đáy trước neo, L_ground,min là chiều dài tối thiểu để neo kéo lê không bị nhấc lên. Dùng cho neo thả. Kết quả BÈ 7: KHÔNG ÁP DỤNG — cọc và đế chịu được lực nhổ (kiểm ở SV-1, SV-4), không cần đoạn dây nằm trên đáy.</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v xml:space="preserve">  C4 — Tỷ lệ chiều dài dây / chiều sâu nước (Scope ratio): L_total / d ≥ [scope]. L_total là chiều dài dây, d là chiều sâu nước; tỷ lệ [scope] (thường ≥ 5) bảo đảm dây xích đủ thoải cho neo thả. Kết quả BÈ 7: KHÔNG ÁP DỤNG — dây căng thẳng tới cọc / đế, chiều dài dây do mặt bằng quyết định.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v xml:space="preserve">  C5 — Sức giữ neo (khi đứt 1 dây): SF = R_total / H_line,dam ≥ [SF]. Như C1 nhưng với lực ngang H_line,dam khi đứt một dây. Kết quả BÈ 7: KHÔNG ÁP DỤNG — hệ này không dùng neo thả: sức giữ là của cọc bờ (BP-1, BP-2) và đế vít xoắn (SV-1…SV-6).</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v xml:space="preserve">  C6 — Bền dây/xích neo (khi đứt 1 dây): SF = MBL / T_max,dam ≥ [SF]. Như C2 nhưng T_max,dam là lực lớn nhất trong các dây còn lại khi dây chịu lực lớn nhất bị đứt (tính lại ở mọi mực nước); [SF] = 2. Kết quả BÈ 7: ĐẠT: giá trị 3,12, yêu cầu 2, mức sử dụng 0,64.</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v xml:space="preserve">  C7 — Độ thiếu chiều dài dây neo: X_deficit ≤ [maxOffset]. X_deficit là phần dây còn thiếu so với chiều dài cần của dây xích chùng (đường dây xích) ở độ trôi cho phép [maxOffset]. Kết quả BÈ 7: KHÔNG ÁP DỤNG — không có đoạn dây xích dự trữ; cáp cắt theo bảng chiều dài cắt cáp (mục 7).</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v xml:space="preserve">  C8 — Khoảng hở an toàn đáy bè – đáy hồ: Clearance = h_nước − mớn nước bè ≥ [min]. h_nước là chiều sâu nước dưới bè ở độ sâu thiết kế, mớn nước là phần bè chìm dưới nước; [min] là khoảng hở tối thiểu để đáy bè không chạm đáy hồ. Kết quả BÈ 7: ĐẠT: giá trị 13,40 m, yêu cầu ≥ 1,5 m, mức sử dụng 0,11. Khoảng hở khi hồ xuống MNC: xem mục 4.</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v xml:space="preserve">  C9 — Khoảng cách trung bình giữa các dây neo: P_bè / N_dây ≤ [maxSpacing]. P_bè là chu vi đa giác bè đo trên mặt bằng, N_dây là số dây neo của bè; [maxSpacing] = 15 m là yêu cầu bắt buộc để lực phân bố đều quanh bè. Kết quả BÈ 7: ĐẠT: giá trị 14,6 m, yêu cầu ≤ 15 m, mức sử dụng 0,97.</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v xml:space="preserve">  C12 — Độ trôi ngang của bè (cân bằng tĩnh, mọi mực nước): u_max ≤ khe hở nhỏ nhất tới bè bên cạnh / 2. u_max là độ trôi ngang lớn nhất của bè trong mô hình cân bằng (mọi hướng, mọi mực nước); hai bè cạnh nhau có thể cùng trôi về phía nhau nên mỗi bè chỉ được trôi nửa khe hở. Kết quả BÈ 7: ĐẠT: giá trị 0,69 m, yêu cầu ≤ 13,10 m, mức sử dụng 0,05.</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v xml:space="preserve">  C10 — Sức chịu tải cho phép của cọc BỜ (P_max): P_req = T_dây × SF ≤ P_max. P_max là sức chịu tải cho phép của cọc bờ theo catalogue hoặc thí nghiệm thử tải; chỉ kiểm khi có nhập P_max. Kết quả BÈ 7: KHÔNG ÁP DỤNG — chưa có catalogue hoặc thí nghiệm thử tải nên chưa có P_max; sức chịu cọc bờ đã kiểm bằng tính toán ở BP-1, BP-2.</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v xml:space="preserve">  C11 — Sức chịu tải cho phép của cọc LÒNG HỒ (P_max): P_req = T_dây × SF ≤ P_max. Như C10 cho cọc đóng dưới đáy hồ (phương án PA1). Kết quả BÈ 7: KHÔNG ÁP DỤNG — neo đáy hồ là đế BTCT + vít xoắn (SV-1…SV-6), không phải cọc đóng.</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v xml:space="preserve">  BP-1 — Sức chịu ngang cọc neo BỜ (Broms): H_applied / H_allow ≤ 1,0. H_applied là lực ngang vào một cọc (T, hoặc T / (2 × 0,9) ở điểm cọc đôi), H_allow = H_u / 2,5 với H_u là sức chịu ngang giới hạn theo Broms (mục 5). Kết quả BÈ 7: ĐẠT: giá trị 0,512, yêu cầu ≤ 1,0, mức sử dụng 0,51.</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v xml:space="preserve">  BP-2 — Uốn tiết diện cọc BỜ (TCVN 5574:2018): γ·M_max / M_rd ≤ 1,0. M_max là mô-men lớn nhất trong thân cọc, γ = 1,2 là hệ số tải trọng, M_rd là khả năng chịu uốn của lồng thép theo TCVN 5574:2018 (mục 5). Kết quả BÈ 7: ĐẠT: giá trị 0,825, yêu cầu ≤ 1,0, mức sử dụng 0,83.</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v xml:space="preserve">  BP-3 — Sức chịu ngang cọc LÒNG HỒ (Cách 1): Th / H_allow ≤ 1,0. Sức chịu ngang của cọc đóng dưới đáy hồ (phương án PA1): T_h lực ngang, H_allow sức chịu cho phép. Kết quả BÈ 7: KHÔNG ÁP DỤNG — neo đáy hồ là đế BTCT + vít xoắn (SV-1…SV-6), không phải cọc đóng.</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v xml:space="preserve">  BP-4 — Sức chịu NHỔ cọc LÒNG HỒ (ma sát thân): Tv / Q_uplift,all ≤ 1,0. Sức chịu nhổ của cọc đóng dưới đáy hồ (PA1): T_v lực nhổ, Q_uplift,all sức chịu nhổ cho phép do ma sát thân cọc. Kết quả BÈ 7: KHÔNG ÁP DỤNG — neo đáy hồ là đế BTCT + vít xoắn (SV-1…SV-6), không phải cọc đóng.</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v xml:space="preserve">  BP-5 — Ứng suất uốn tiết diện cọc LÒNG HỒ: M_max / M_rd ≤ 1,0. Uốn thân cọc đóng dưới đáy hồ (PA1). Kết quả BÈ 7: KHÔNG ÁP DỤNG — neo đáy hồ là đế BTCT + vít xoắn (SV-1…SV-6), không phải cọc đóng.</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v xml:space="preserve">  SV-1 — Đế vít xoắn — chống NHỔ: Tv / (0,9·W' + n·Q_a) ≤ 1,0. T_v là lực nhổ, W' là trọng lượng đế trong nước (đã trừ lực đẩy nổi, chỉ lấy 0,9), n vít × Q_a là sức chịu nhổ cho phép của các vít (mục 6). Kết quả BÈ 7: ĐẠT: giá trị 0,738, yêu cầu ≤ 1,0, mức sử dụng 0,74.</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v xml:space="preserve">  SV-2 — Đế vít xoắn — chống TRƯỢT: 1,5·Th / (α·c_u·B² + R_gờ + n·H_u) ≤ 1,0. T_h là lực ngang nhân hệ số 1,5; chống trượt gồm bám dính đáy α·c_u·B² (bằng 0 khi đế bị nhấc), gờ đế R_gờ và sức chịu ngang của n vít H_u (mục 6). Kết quả BÈ 7: ĐẠT: giá trị 0,654, yêu cầu ≤ 1,0, mức sử dụng 0,65.</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v xml:space="preserve">  SV-3 — Đế vít xoắn — chống LẬT: 1,5·M_o / M_r ≤ 1,0. M_o là mô-men lật quanh mép đáy phía xa dây (nhân 1,5), M_r là mô-men giữ do trọng lượng đế và các vít (mục 6). Kết quả BÈ 7: ĐẠT: giá trị 0,981, yêu cầu ≤ 1,0, mức sử dụng 0,98.</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">  SV-4 — Đế vít xoắn — lực nhổ một vít: N_1 / Q_a ≤ 1,0. N_1 là lực nhổ lên vít chịu nặng nhất sau khi trừ phần trọng lượng đế gánh, Q_a là sức chịu nhổ cho phép của một vít (mục 6). Kết quả BÈ 7: ĐẠT: giá trị 0,585, yêu cầu ≤ 1,0, mức sử dụng 0,58.</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve">  SV-5 — Đế vít xoắn — áp lực lên nền bùn: W'/B² ≤ 5,14·c_u / 2,5. W'/B² là áp lực đế lên nền bùn, 5,14·c_u là sức chịu tải giới hạn của nền sét mềm, chia hệ số an toàn (mục 6). Kết quả BÈ 7: ĐẠT: giá trị 6,0, yêu cầu ≤ 41,1 kPa, mức sử dụng 0,15.</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v xml:space="preserve">  SV-6 — Đế vít xoắn — cốt thép bản đế: max(A_s yc ; 0,1%) / A_s bố trí ≤ 1,0. A_s yc là thép bản đế cần theo mô-men uốn, 0,1% là hàm lượng tối thiểu, A_s bố trí là lưới thép đặt trong bản (mục 6). Kết quả BÈ 7: ĐẠT: giá trị 0,619, yêu cầu ≤ 1,0, mức sử dụng 0,62.</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A104"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/mat-bang-neo-ban-mong/bang_tinh_neo.xlsx
+++ b/docs/mat-bang-neo-ban-mong/bang_tinh_neo.xlsx
@@ -516,22 +516,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">  Diện tích đón gió của pin: A = số tấm × diện tích tấm × sin(nghiêng) = 4.177 × 3,106 × sin 10° = 2.253 m².</v>
+        <v xml:space="preserve">  Diện tích đón gió của pin: A = số tấm × diện tích tấm × sin(nghiêng) = 4.200 × 3,106 × sin 10° = 2.265 m².</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v xml:space="preserve">  Lực gió lên pin: F_pin = q × C_d × A × hệ số che chắn = 250 × 1,15 × 2.253 × 0,55 = 356,2 kN.</v>
+        <v xml:space="preserve">  Lực gió lên pin: F_pin = q × C_d × A × hệ số che chắn = 250 × 1,15 × 2.265 × 0,55 = 358,2 kN.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">  Lực gió lên phao (mạn khô 0,35 m): F_phao = 17,7 kN. Tổng gió: 374,0 kN.</v>
+        <v xml:space="preserve">  Lực gió lên phao (mạn khô 0,35 m): F_phao = 17,7 kN. Tổng gió: 375,9 kN.</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">  Tổng lực môi trường: F = 374,0 × 1,05 = 392,7 kN.</v>
+        <v xml:space="preserve">  Tổng lực môi trường: F = 375,9 × 1,05 = 394,7 kN.</v>
       </c>
     </row>
     <row r="25">
@@ -556,7 +556,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">  Lực một dây: T = (EA / L_0) × (d − L_0) khi d &gt; L_0, T = 0 khi d ≤ L_0 (dây chùng). d là khoảng cách thẳng bích bè – chốt neo khi bè đã dịch đi, L_0 là chiều dài dây lúc vừa căng. Cáp PES-40: EA = 15 × 475 = 7.125 kN. Dây càng ngắn (L_0 nhỏ) càng cứng nên nhận càng nhiều lực.</v>
+        <v xml:space="preserve">  Lực một dây: T = (EA / L_0) × (d − L_0) khi d &gt; L_0, T = 0 khi d ≤ L_0 (dây chùng). d là khoảng cách thẳng bích bè – chốt neo khi bè đã dịch đi, L_0 là chiều dài dây lúc vừa căng. Cáp PES-48: EA = 15 × 688 = 10.320 kN. Dây càng ngắn (L_0 nhỏ) càng cứng nên nhận càng nhiều lực.</v>
       </c>
     </row>
     <row r="30">
@@ -566,17 +566,17 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">  BÈ 6 (bè có lực dây lớn nhất): F = 392,7 kN; chi phối ở mực nước 649,50 m, tải đẩy về hướng 300°, dây B6-D06 chịu 145,4 kN, 28 dây cùng căng; bè trôi 0,49 m. Mất dây B6-D06: dây lớn nhất còn lại 128,6 kN.</v>
+        <v xml:space="preserve">  BÈ 6 (bè có lực dây lớn nhất): F = 394,7 kN; chi phối ở mực nước 649,50 m, tải đẩy về hướng 300°, dây B6-D06 chịu 147,1 kN, 28 dây cùng căng; bè trôi 0,34 m. Mất dây B6-D06: dây lớn nhất còn lại 130,3 kN.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">  Lực dây thiết kế của BÈ 6: T = 150,4 kN (đã cộng lực căng trước 5 kN; không nhỏ hơn F / (n × cos α) = 80,6 kN); khi đứt một dây: 133,6 kN. Cáp và cọc bờ của bè kiểm tra với lực này; mỗi đế vít xoắn kiểm tra với lực lớn nhất của chính (các) dây nối vào nó (bao mọi hướng, mọi mực nước).</v>
+        <v xml:space="preserve">  Lực dây thiết kế của BÈ 6: T = 152,1 kN (đã cộng lực căng trước 5 kN; không nhỏ hơn F / (n × cos α) = 81,0 kN); khi đứt một dây: 135,3 kN. Cáp và cọc bờ của bè kiểm tra với lực này; mỗi đế vít xoắn kiểm tra với lực lớn nhất của chính (các) dây nối vào nó (bao mọi hướng, mọi mực nước).</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">  Cáp PES-40, lực đứt 475 kN: hệ số an toàn MBL / T = 475 / 150,4 = 3,16 (yêu cầu ≥ 3,0); khi đứt một dây 475 / 133,6 = 3,56 (yêu cầu ≥ 2,0).</v>
+        <v xml:space="preserve">  Cáp PES-48, lực đứt 688 kN: hệ số an toàn MBL / T = 688 / 152,1 = 4,52 (yêu cầu ≥ 3,0); khi đứt một dây 688 / 135,3 = 5,09 (yêu cầu ≥ 2,0).</v>
       </c>
     </row>
     <row r="34">
@@ -591,7 +591,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">  Độ trôi bè lớn nhất (mọi hướng, mọi mực nước): 0,5 – 0,8 m tùy bè (kiểm tra C12: ≤ nửa khoảng hở nhỏ nhất tới bè bên cạnh).</v>
+        <v xml:space="preserve">  Độ trôi bè lớn nhất (mọi hướng, mọi mực nước): 0,4 – 0,8 m tùy bè (kiểm tra C12: ≤ nửa khoảng hở nhỏ nhất tới bè bên cạnh).</v>
       </c>
     </row>
     <row r="37">
@@ -616,12 +616,12 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">  H_u là nghiệm dương của (0,5 / p) × H_u² + (e + 1,5D + g) × H_u − 0,5 × p × g² = 0, tức (0,5 / 126,0) × H_u² + 6,600 × H_u − 2.249,1 = 0 → H_u = 290,2 kN. Cho phép H_u / 2,5 = 116,1 kN ≥ T = 150,4 kN; mức sử dụng = 150,4 / 116,1 = 0,64.</v>
+        <v xml:space="preserve">  H_u là nghiệm dương của (0,5 / p) × H_u² + (e + 1,5D + g) × H_u − 0,5 × p × g² = 0, tức (0,5 / 126,0) × H_u² + 6,600 × H_u − 2.249,1 = 0 → H_u = 290,2 kN. Cho phép H_u / 2,5 = 116,1 kN ≥ T = 152,1 kN; mức sử dụng = 152,1 / 116,1 = 0,65.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">  BP-2, uốn thân cọc (TCVN 5574:2018). Mô-men lớn nhất trong cọc: M_max = P × (e + 1,5D + 0,5 × P / p) = 150,4 × (0,10 + 0,525 + 0,5 × 150,4 / 126,0) = 69,0 kNm.</v>
+        <v xml:space="preserve">  BP-2, uốn thân cọc (TCVN 5574:2018). Mô-men lớn nhất trong cọc: M_max = P × (e + 1,5D + 0,5 × P / p) = 152,1 × (0,10 + 0,525 + 0,5 × 152,1 / 126,0) = 69,7 kNm.</v>
       </c>
     </row>
     <row r="43">
@@ -631,12 +631,12 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">  Kiểm tra: 1,2 × M_max = 1,2 × 69,0 = 82,7 kNm ≤ M_rd = 93,3 kNm; mức sử dụng 0,89 (1,2 là hệ số tải trọng khi kiểm tra uốn).</v>
+        <v xml:space="preserve">  Kiểm tra: 1,2 × M_max = 1,2 × 69,7 = 83,6 kNm ≤ M_rd = 93,3 kNm; mức sử dụng 0,90 (1,2 là hệ số tải trọng khi kiểm tra uốn).</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v xml:space="preserve">  Cọc ĐƠN theo lực của chính dây (như đế neo đáy): ở BÈ 5 27/27 điểm, BÈ 6 45/45 điểm, lực lớn nhất của CHÍNH dây (mọi mực nước, mọi hướng gió, cộng lực căng trước) không quá 77,2 kN (BÈ 5), 74,8 kN (BÈ 6) nên dùng một cọc 6Φ28 CB400-V, L_tk 6,5 m (BP-1 0,67 / 0,64, BP-2 0,93 / 0,89); chỉ các dây lực lớn hơn mới dùng cọc của bè. Lực bè T ở trên là lực bất lợi nhất của bè, có sàn F/(6 cos 30°).</v>
+        <v xml:space="preserve">  Cọc ĐƠN theo lực của chính dây (như đế neo đáy): ở BÈ 5 27/27 điểm, BÈ 6 45/45 điểm, lực lớn nhất của CHÍNH dây (mọi mực nước, mọi hướng gió, cộng lực căng trước) không quá 77,0 kN (BÈ 5), 75,4 kN (BÈ 6) nên dùng một cọc 6Φ28 CB400-V, L_tk 6,5 m (BP-1 0,66 / 0,65, BP-2 0,92 / 0,90); chỉ các dây lực lớn hơn mới dùng cọc của bè. Lực bè T ở trên là lực bất lợi nhất của bè, có sàn F/(6 cos 30°).</v>
       </c>
     </row>
     <row r="46">
@@ -651,7 +651,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>6. Đế BTCT + vít xoắn (ví dụ BM-DV023, đế làm việc nặng nhất)</v>
+        <v>6. Đế BTCT + vít xoắn (ví dụ BM-DV003, đế làm việc nặng nhất)</v>
       </c>
     </row>
     <row r="49">
@@ -661,7 +661,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">  Đế BM-DV023 giữ hai dây B4-D05 (BÈ 4, T = 61,5 kN, dài 15,56 m) và B5-D11 (BÈ 5, T = 54,2 kN, dài 15,57 m). Bích bè cao hơn mặt nước 0,35 m.</v>
+        <v xml:space="preserve">  Đế BM-DV003 giữ hai dây B1-D12 (BÈ 1, T = 51,1 kN, dài 15,66 m) và B2-D26 (BÈ 2, T = 53,5 kN, dài 15,68 m). Bích bè cao hơn mặt nước 0,35 m.</v>
       </c>
     </row>
     <row r="51">
@@ -671,52 +671,52 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v xml:space="preserve">  Tổ hợp chi phối: cả hai dây căng (MN cao). Lực nhổ T_v = 93,3 kN (hai dây cộng lại), lực ngang T_h = 4,3 kN (cộng véc-tơ).</v>
+        <v xml:space="preserve">  Tổ hợp chi phối: cả hai dây căng (MN cao). Lực nhổ T_v = 83,5 kN (hai dây cộng lại), lực ngang T_h = 1,5 kN (cộng véc-tơ).</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v xml:space="preserve">  Đế 3,25 × 3,25 × 0,5 m: thể tích 5,28 m³, nặng 132,0 kN trên cạn, W' = 5,28 × (25 − 10) = 79,2 kN trong nước (đã trừ lực đẩy nổi).</v>
+        <v xml:space="preserve">  Đế 3,25 × 3,25 × 0,4 m: thể tích 4,23 m³, nặng 105,6 kN trên cạn, W' = 4,23 × (25 − 10) = 63,4 kN trong nước (đã trừ lực đẩy nổi).</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v xml:space="preserve">  SV-1 nhổ: T_v ≤ 0,9 × W' + 4 × Q_a = 103,0 kN; mức sử dụng 0,91.</v>
+        <v xml:space="preserve">  SV-1 nhổ: T_v ≤ 0,9 × W' + 4 × Q_a = 88,7 kN; mức sử dụng 0,94.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v xml:space="preserve">  SV-2 trượt: 1,5 × T_h ≤ bám dính đáy + gờ + 4 × H_u. Bám dính đáy = 0,5 × c_u × B² = 0,0 kN (lấy bằng 0 khi T_v &gt; W': đế bị nhấc khỏi bùn); gờ sâu z = 0,15 m: B × (0,5 × γ' × z² + 2 × c_u × z) = 19,7 kN; H_u một vít = 15,0 kN (Broms, đầu tự do ở mặt bùn). 1,5 × 4,3 = 6,4 ≤ 79,7 kN; mức sử dụng 0,45.</v>
+        <v xml:space="preserve">  SV-2 trượt: 1,5 × T_h ≤ bám dính đáy + gờ + 4 × H_u. Bám dính đáy = 0,5 × c_u × B² = 0,0 kN (lấy bằng 0 khi T_v &gt; W': đế bị nhấc khỏi bùn); gờ sâu z = 0,15 m: B × (0,5 × γ' × z² + 2 × c_u × z) = 19,7 kN; H_u một vít = 15,0 kN (Broms, đầu tự do ở mặt bùn). 1,5 × 1,5 = 2,2 ≤ 79,7 kN; mức sử dụng 0,39.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v xml:space="preserve">  SV-3 lật quanh mép đáy phía xa dây: M_lật = T_h × (t + h_tai) + T_v × B / 2 = 4,3 × (0,5 + 0,15) + 93,3 × 3,25 / 2 = 154,4 kNm; M_giữ = W' × B / 2 + (n/2) × Q_u × (B − c) + (n/2) × Q_u × c = 231,6 kNm (c = 0,15 m từ mép đế tới tim lỗ vít). 1,5 × 154,4 = 231,6 ≤ 231,6 kNm; mức sử dụng 1,00.</v>
+        <v xml:space="preserve">  SV-3 lật quanh mép đáy phía xa dây: M_lật = T_h × (t + h_tai) + T_v × B / 2 = 1,5 × (0,4 + 0,15) + 83,5 × 3,25 / 2 = 136,5 kNm; M_giữ = W' × B / 2 + (n/2) × Q_u × (B − c) + (n/2) × Q_u × c = 205,9 kNm (c = 0,15 m từ mép đế tới tim lỗ vít). 1,5 × 136,5 = 204,8 ≤ 205,9 kNm; mức sử dụng 0,99.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v xml:space="preserve">  SV-4 một vít: lực nhổ lên vít chịu nặng nhất N_1 = max[(T_v − 0,9 × W') / n ; (M_lật − 0,9 × W' × B / 2) / (B − c) / (n/2)] = 6,2 kN ≤ Q_a = 7,9 kN; mức sử dụng 0,79.</v>
+        <v xml:space="preserve">  SV-4 một vít: lực nhổ lên vít chịu nặng nhất N_1 = max[(T_v − 0,9 × W') / n ; (M_lật − 0,9 × W' × B / 2) / (B − c) / (n/2)] = 7,1 kN ≤ Q_a = 7,9 kN; mức sử dụng 0,89.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v xml:space="preserve">  SV-5 áp lực lên nền bùn: W' / B² = 7,5 kPa ≤ 5,14 × c_u / 2,5 = 41,1 kPa (sức chịu tải giới hạn của nền sét mềm); mức sử dụng 0,18.</v>
+        <v xml:space="preserve">  SV-5 áp lực lên nền bùn: W' / B² = 6,0 kPa ≤ 5,14 × c_u / 2,5 = 41,1 kPa (sức chịu tải giới hạn của nền sét mềm); mức sử dụng 0,15.</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v xml:space="preserve">  SV-6 thép bản đế: tai neo kéo lên ở giữa, 4 vít giữ ở các góc; mô-men trên 1 m bản M = (n/2) × Q_u × (s/2) / B = 14,37 kNm/m (s = B − 2c); thép cần A_s = M / (0,9 × h_0 × R_s) = 136 mm²/m, tối thiểu 0,1% = 450 mm²/m; bố trí lưới Ø12 a200 hai lớp = 565 mm²/m; mức sử dụng 0,80.</v>
+        <v xml:space="preserve">  SV-6 thép bản đế: tai neo kéo lên ở giữa, 4 vít giữ ở các góc; mô-men trên 1 m bản M = (n/2) × Q_u × (s/2) / B = 14,37 kNm/m (s = B − 2c); thép cần A_s = M / (0,9 × h_0 × R_s) = 175 mm²/m, tối thiểu 0,1% = 350 mm²/m; bố trí lưới Ø12 a200 hai lớp = 565 mm²/m; mức sử dụng 0,62.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v xml:space="preserve">  Cả hệ: 35 đế (10 đế 2,50 m, 1 đế 2,75 m, 5 đế 3,00 m, 6 đế 3,25 m, 3 đế 3,50 m, 2 đế 3,75 m, 6 đế 4,00 m, 1 đế 4,75 m, 1 đế 5,25 m), 173,3 m³ bê tông, 7,2 tấn thép bản, 140 vít (523 m), đế nặng nhất khi cẩu 35,1 tấn.</v>
+        <v xml:space="preserve">  Cả hệ: 35 đế (10 đế 2,50 m, 1 đế 2,75 m, 6 đế 3,00 m, 5 đế 3,25 m, 3 đế 3,50 m, 1 đế 3,75 m, 6 đế 4,00 m, 1 đế 4,25 m, 1 đế 4,75 m, 1 đế 5,25 m), 173,6 m³ bê tông, 7,3 tấn thép bản, 140 vít (523 m), đế nặng nhất khi cẩu 35,1 tấn.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v xml:space="preserve">  Tổng lực nhổ lên 35 đế 2.692 kN, tổng sức chống nhổ 3.457 kN. Mức sử dụng lớn nhất: nhổ 0,96, trượt 0,82, lật 1,00, một vít 0,96.</v>
+        <v xml:space="preserve">  Tổng lực nhổ lên 35 đế 2.693 kN, tổng sức chống nhổ 3.461 kN. Mức sử dụng lớn nhất: nhổ 0,96, trượt 0,82, lật 0,99, một vít 0,96.</v>
       </c>
     </row>
     <row r="62">
@@ -756,7 +756,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">  Nếu khóa của thiết bị bù KHÔNG khóa kịp, đối trọng chỉ giữ lực căng 5 kN và hành trình dư 3 m mỗi chiều: bè trôi 4,3–6,7 m (tới hết hành trình rồi dây mới căng) và lực dây vọt tới 91–359 kN (hệ số an toàn cáp chỉ 1,3–3,4; đế và cọc không được tính cho lực này). Đối trọng treo tự do KHÔNG đủ giữ bè: cần bộ khóa / phanh chủ động, dự phòng, kiểm tra định kỳ.</v>
+        <v xml:space="preserve">  Nếu khóa của thiết bị bù KHÔNG khóa kịp, đối trọng chỉ giữ lực căng 5 kN và hành trình dư 3 m mỗi chiều: bè trôi 4,3–6,7 m (tới hết hành trình rồi dây mới căng) và lực dây vọt tới 89–379 kN (hệ số an toàn cáp chỉ 1,6–3,4; đế và cọc không được tính cho lực này). Đối trọng treo tự do KHÔNG đủ giữ bè: cần bộ khóa / phanh chủ động, dự phòng, kiểm tra định kỳ.</v>
       </c>
     </row>
     <row r="70">
@@ -826,7 +826,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">  C2 — Bền dây/xích neo (nguyên vẹn): SF = MBL / T_max ≥ [SF]. MBL là lực kéo đứt nhỏ nhất của cáp (nhà sản xuất công bố), T_max là lực lớn nhất một dây phải chịu (mô hình cân bằng, đã cộng lực căng trước); [SF] = 3 khi đủ dây. Kết quả BÈ 6: ĐẠT: giá trị 3,16, yêu cầu 3, mức sử dụng 0,95.</v>
+        <v xml:space="preserve">  C2 — Bền dây/xích neo (nguyên vẹn): SF = MBL / T_max ≥ [SF]. MBL là lực kéo đứt nhỏ nhất của cáp (nhà sản xuất công bố), T_max là lực lớn nhất một dây phải chịu (mô hình cân bằng, đã cộng lực căng trước); [SF] = 3 khi đủ dây. Kết quả BÈ 6: ĐẠT: giá trị 4,52, yêu cầu 3, mức sử dụng 0,66.</v>
       </c>
     </row>
     <row r="84">
@@ -846,7 +846,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">  C6 — Bền dây/xích neo (khi đứt 1 dây): SF = MBL / T_max,dam ≥ [SF]. Như C2 nhưng T_max,dam là lực lớn nhất trong các dây còn lại khi dây chịu lực lớn nhất bị đứt (tính lại ở mọi mực nước); [SF] = 2. Kết quả BÈ 6: ĐẠT: giá trị 3,56, yêu cầu 2, mức sử dụng 0,56.</v>
+        <v xml:space="preserve">  C6 — Bền dây/xích neo (khi đứt 1 dây): SF = MBL / T_max,dam ≥ [SF]. Như C2 nhưng T_max,dam là lực lớn nhất trong các dây còn lại khi dây chịu lực lớn nhất bị đứt (tính lại ở mọi mực nước); [SF] = 2. Kết quả BÈ 6: ĐẠT: giá trị 5,09, yêu cầu 2, mức sử dụng 0,39.</v>
       </c>
     </row>
     <row r="88">
@@ -866,7 +866,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">  C12 — Độ trôi ngang của bè (cân bằng tĩnh, mọi mực nước): u_max ≤ khe hở nhỏ nhất tới bè bên cạnh / 2. u_max là độ trôi ngang lớn nhất của bè trong mô hình cân bằng (mọi hướng, mọi mực nước); hai bè cạnh nhau có thể cùng trôi về phía nhau nên mỗi bè chỉ được trôi nửa khe hở. Kết quả BÈ 6: ĐẠT: giá trị 0,59 m, yêu cầu ≤ 18,63 m, mức sử dụng 0,03.</v>
+        <v xml:space="preserve">  C12 — Độ trôi ngang của bè (cân bằng tĩnh, mọi mực nước): u_max ≤ khe hở nhỏ nhất tới bè bên cạnh / 2. u_max là độ trôi ngang lớn nhất của bè trong mô hình cân bằng (mọi hướng, mọi mực nước); hai bè cạnh nhau có thể cùng trôi về phía nhau nên mỗi bè chỉ được trôi nửa khe hở. Kết quả BÈ 6: ĐẠT: giá trị 0,41 m, yêu cầu ≤ 18,63 m, mức sử dụng 0,02.</v>
       </c>
     </row>
     <row r="92">
@@ -881,12 +881,12 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">  BP-1 — Sức chịu ngang cọc neo BỜ (Broms): H_applied / H_allow ≤ 1,0. H_applied là lực ngang vào một cọc (T, hoặc T / (2 × 0,9) ở điểm cọc đôi), H_allow = H_u / 2,5 với H_u là sức chịu ngang giới hạn theo Broms (mục 5). Kết quả BÈ 6: ĐẠT: giá trị 0,720, yêu cầu ≤ 1,0, mức sử dụng 0,72.</v>
+        <v xml:space="preserve">  BP-1 — Sức chịu ngang cọc neo BỜ (Broms): H_applied / H_allow ≤ 1,0. H_applied là lực ngang vào một cọc (T, hoặc T / (2 × 0,9) ở điểm cọc đôi), H_allow = H_u / 2,5 với H_u là sức chịu ngang giới hạn theo Broms (mục 5). Kết quả BÈ 6: ĐẠT: giá trị 0,728, yêu cầu ≤ 1,0, mức sử dụng 0,73.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">  BP-2 — Uốn tiết diện cọc BỜ (TCVN 5574:2018): γ·M_max / M_rd ≤ 1,0. M_max là mô-men lớn nhất trong thân cọc, γ = 1,2 là hệ số tải trọng, M_rd là khả năng chịu uốn của lồng thép theo TCVN 5574:2018 (mục 5). Kết quả BÈ 6: ĐẠT: giá trị 0,827, yêu cầu ≤ 1,0, mức sử dụng 0,83.</v>
+        <v xml:space="preserve">  BP-2 — Uốn tiết diện cọc BỜ (TCVN 5574:2018): γ·M_max / M_rd ≤ 1,0. M_max là mô-men lớn nhất trong thân cọc, γ = 1,2 là hệ số tải trọng, M_rd là khả năng chịu uốn của lồng thép theo TCVN 5574:2018 (mục 5). Kết quả BÈ 6: ĐẠT: giá trị 0,840, yêu cầu ≤ 1,0, mức sử dụng 0,84.</v>
       </c>
     </row>
     <row r="96">
@@ -906,22 +906,22 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">  SV-1 — Đế vít xoắn — chống NHỔ: Tv / (0,9·W' + n·Q_a) ≤ 1,0. T_v là lực nhổ, W' là trọng lượng đế trong nước (đã trừ lực đẩy nổi, chỉ lấy 0,9), n vít × Q_a là sức chịu nhổ cho phép của các vít (mục 6). Kết quả BÈ 6: ĐẠT: giá trị 0,681, yêu cầu ≤ 1,0, mức sử dụng 0,68.</v>
+        <v xml:space="preserve">  SV-1 — Đế vít xoắn — chống NHỔ: Tv / (0,9·W' + n·Q_a) ≤ 1,0. T_v là lực nhổ, W' là trọng lượng đế trong nước (đã trừ lực đẩy nổi, chỉ lấy 0,9), n vít × Q_a là sức chịu nhổ cho phép của các vít (mục 6). Kết quả BÈ 6: ĐẠT: giá trị 0,688, yêu cầu ≤ 1,0, mức sử dụng 0,69.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v xml:space="preserve">  SV-2 — Đế vít xoắn — chống TRƯỢT: 1,5·Th / (α·c_u·B² + R_gờ + n·H_u) ≤ 1,0. T_h là lực ngang nhân hệ số 1,5; chống trượt gồm bám dính đáy α·c_u·B² (bằng 0 khi đế bị nhấc), gờ đế R_gờ và sức chịu ngang của n vít H_u (mục 6). Kết quả BÈ 6: ĐẠT: giá trị 0,661, yêu cầu ≤ 1,0, mức sử dụng 0,66.</v>
+        <v xml:space="preserve">  SV-2 — Đế vít xoắn — chống TRƯỢT: 1,5·Th / (α·c_u·B² + R_gờ + n·H_u) ≤ 1,0. T_h là lực ngang nhân hệ số 1,5; chống trượt gồm bám dính đáy α·c_u·B² (bằng 0 khi đế bị nhấc), gờ đế R_gờ và sức chịu ngang của n vít H_u (mục 6). Kết quả BÈ 6: ĐẠT: giá trị 0,669, yêu cầu ≤ 1,0, mức sử dụng 0,67.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v xml:space="preserve">  SV-3 — Đế vít xoắn — chống LẬT: 1,5·M_o / M_r ≤ 1,0. M_o là mô-men lật quanh mép đáy phía xa dây (nhân 1,5), M_r là mô-men giữ do trọng lượng đế và các vít (mục 6). Kết quả BÈ 6: ĐẠT: giá trị 0,950, yêu cầu ≤ 1,0, mức sử dụng 0,95.</v>
+        <v xml:space="preserve">  SV-3 — Đế vít xoắn — chống LẬT: 1,5·M_o / M_r ≤ 1,0. M_o là mô-men lật quanh mép đáy phía xa dây (nhân 1,5), M_r là mô-men giữ do trọng lượng đế và các vít (mục 6). Kết quả BÈ 6: ĐẠT: giá trị 0,961, yêu cầu ≤ 1,0, mức sử dụng 0,96.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">  SV-4 — Đế vít xoắn — lực nhổ một vít: N_1 / Q_a ≤ 1,0. N_1 là lực nhổ lên vít chịu nặng nhất sau khi trừ phần trọng lượng đế gánh, Q_a là sức chịu nhổ cho phép của một vít (mục 6). Kết quả BÈ 6: ĐẠT: giá trị 0,005, yêu cầu ≤ 1,0, mức sử dụng 0,00.</v>
+        <v xml:space="preserve">  SV-4 — Đế vít xoắn — lực nhổ một vít: N_1 / Q_a ≤ 1,0. N_1 là lực nhổ lên vít chịu nặng nhất sau khi trừ phần trọng lượng đế gánh, Q_a là sức chịu nhổ cho phép của một vít (mục 6). Kết quả BÈ 6: ĐẠT: giá trị 0,055, yêu cầu ≤ 1,0, mức sử dụng 0,06.</v>
       </c>
     </row>
     <row r="103">
@@ -1033,7 +1033,7 @@
         <v>650</v>
       </c>
       <c r="C7">
-        <v>80.1</v>
+        <v>80</v>
       </c>
       <c r="D7" t="str">
         <v>B1-D27</v>
@@ -1079,7 +1079,7 @@
         <v>652</v>
       </c>
       <c r="C9">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="D9" t="str">
         <v>B1-D27</v>
@@ -1102,7 +1102,7 @@
         <v>653</v>
       </c>
       <c r="C10">
-        <v>75.8</v>
+        <v>75.7</v>
       </c>
       <c r="D10" t="str">
         <v>B1-D27</v>
@@ -1125,7 +1125,7 @@
         <v>654</v>
       </c>
       <c r="C11">
-        <v>74.2</v>
+        <v>74.1</v>
       </c>
       <c r="D11" t="str">
         <v>B1-D27</v>
@@ -1171,7 +1171,7 @@
         <v>656</v>
       </c>
       <c r="C13">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="D13" t="str">
         <v>B1-D27</v>
@@ -1194,7 +1194,7 @@
         <v>657</v>
       </c>
       <c r="C14">
-        <v>69</v>
+        <v>68.9</v>
       </c>
       <c r="D14" t="str">
         <v>B1-D27</v>
@@ -1240,7 +1240,7 @@
         <v>659</v>
       </c>
       <c r="C16">
-        <v>65.3</v>
+        <v>65.2</v>
       </c>
       <c r="D16" t="str">
         <v>B1-D27</v>
@@ -1286,7 +1286,7 @@
         <v>661</v>
       </c>
       <c r="C18">
-        <v>61.6</v>
+        <v>61.5</v>
       </c>
       <c r="D18" t="str">
         <v>B1-D27</v>
@@ -1355,7 +1355,7 @@
         <v>663</v>
       </c>
       <c r="C21">
-        <v>58.1</v>
+        <v>58</v>
       </c>
       <c r="D21" t="str">
         <v>B1-D27</v>
@@ -1378,7 +1378,7 @@
         <v>664</v>
       </c>
       <c r="C22">
-        <v>56.5</v>
+        <v>56.4</v>
       </c>
       <c r="D22" t="str">
         <v>B1-D27</v>
@@ -1424,7 +1424,7 @@
         <v>666</v>
       </c>
       <c r="C24">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="D24" t="str">
         <v>B1-D27</v>
@@ -1516,7 +1516,7 @@
         <v>669.05</v>
       </c>
       <c r="C28">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="D28" t="str">
         <v>B1-D01</v>
@@ -1539,7 +1539,7 @@
         <v>649.5</v>
       </c>
       <c r="C29">
-        <v>74.2</v>
+        <v>74.4</v>
       </c>
       <c r="D29" t="str">
         <v>B2-D59</v>
@@ -1562,7 +1562,7 @@
         <v>650</v>
       </c>
       <c r="C30">
-        <v>72.7</v>
+        <v>72.9</v>
       </c>
       <c r="D30" t="str">
         <v>B2-D59</v>
@@ -1585,7 +1585,7 @@
         <v>651</v>
       </c>
       <c r="C31">
-        <v>69.6</v>
+        <v>69.7</v>
       </c>
       <c r="D31" t="str">
         <v>B2-D59</v>
@@ -1608,7 +1608,7 @@
         <v>652</v>
       </c>
       <c r="C32">
-        <v>66.3</v>
+        <v>66.4</v>
       </c>
       <c r="D32" t="str">
         <v>B2-D59</v>
@@ -1631,7 +1631,7 @@
         <v>653</v>
       </c>
       <c r="C33">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="D33" t="str">
         <v>B2-D59</v>
@@ -1654,7 +1654,7 @@
         <v>654</v>
       </c>
       <c r="C34">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
       <c r="D34" t="str">
         <v>B2-D59</v>
@@ -1677,7 +1677,7 @@
         <v>655</v>
       </c>
       <c r="C35">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
       <c r="D35" t="str">
         <v>B2-D59</v>
@@ -1700,7 +1700,7 @@
         <v>656</v>
       </c>
       <c r="C36">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="D36" t="str">
         <v>B2-D28</v>
@@ -1723,7 +1723,7 @@
         <v>657</v>
       </c>
       <c r="C37">
-        <v>55.8</v>
+        <v>55.9</v>
       </c>
       <c r="D37" t="str">
         <v>B2-D28</v>
@@ -1746,7 +1746,7 @@
         <v>658</v>
       </c>
       <c r="C38">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="D38" t="str">
         <v>B2-D28</v>
@@ -1769,7 +1769,7 @@
         <v>659</v>
       </c>
       <c r="C39">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="D39" t="str">
         <v>B2-D28</v>
@@ -1792,7 +1792,7 @@
         <v>660</v>
       </c>
       <c r="C40">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="D40" t="str">
         <v>B2-D28</v>
@@ -1815,7 +1815,7 @@
         <v>661</v>
       </c>
       <c r="C41">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="D41" t="str">
         <v>B2-D28</v>
@@ -1824,7 +1824,7 @@
         <v>285</v>
       </c>
       <c r="F41">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G41">
         <v>25</v>
@@ -1838,7 +1838,7 @@
         <v>662</v>
       </c>
       <c r="C42">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="D42" t="str">
         <v>B2-D28</v>
@@ -1861,7 +1861,7 @@
         <v>662.76</v>
       </c>
       <c r="C43">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
       <c r="D43" t="str">
         <v>B2-D28</v>
@@ -1884,7 +1884,7 @@
         <v>663</v>
       </c>
       <c r="C44">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="D44" t="str">
         <v>B2-D28</v>
@@ -1907,7 +1907,7 @@
         <v>664</v>
       </c>
       <c r="C45">
-        <v>60.2</v>
+        <v>60.4</v>
       </c>
       <c r="D45" t="str">
         <v>B2-D28</v>
@@ -1930,7 +1930,7 @@
         <v>665</v>
       </c>
       <c r="C46">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="D46" t="str">
         <v>B2-D28</v>
@@ -1953,7 +1953,7 @@
         <v>666</v>
       </c>
       <c r="C47">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
       <c r="D47" t="str">
         <v>B2-D28</v>
@@ -1976,7 +1976,7 @@
         <v>667</v>
       </c>
       <c r="C48">
-        <v>60.9</v>
+        <v>61</v>
       </c>
       <c r="D48" t="str">
         <v>B2-D28</v>
@@ -1999,7 +1999,7 @@
         <v>668</v>
       </c>
       <c r="C49">
-        <v>61.1</v>
+        <v>61.2</v>
       </c>
       <c r="D49" t="str">
         <v>B2-D28</v>
@@ -2022,7 +2022,7 @@
         <v>669</v>
       </c>
       <c r="C50">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="D50" t="str">
         <v>B2-D28</v>
@@ -2045,7 +2045,7 @@
         <v>669.05</v>
       </c>
       <c r="C51">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="D51" t="str">
         <v>B2-D28</v>
@@ -2068,7 +2068,7 @@
         <v>649.5</v>
       </c>
       <c r="C52">
-        <v>49.6</v>
+        <v>48.8</v>
       </c>
       <c r="D52" t="str">
         <v>B3-D18</v>
@@ -2091,7 +2091,7 @@
         <v>650</v>
       </c>
       <c r="C53">
-        <v>49.2</v>
+        <v>48.4</v>
       </c>
       <c r="D53" t="str">
         <v>B3-D18</v>
@@ -2114,7 +2114,7 @@
         <v>651</v>
       </c>
       <c r="C54">
-        <v>48.4</v>
+        <v>47.6</v>
       </c>
       <c r="D54" t="str">
         <v>B3-D18</v>
@@ -2123,7 +2123,7 @@
         <v>345</v>
       </c>
       <c r="F54">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="G54">
         <v>7</v>
@@ -2137,7 +2137,7 @@
         <v>652</v>
       </c>
       <c r="C55">
-        <v>47.6</v>
+        <v>46.8</v>
       </c>
       <c r="D55" t="str">
         <v>B3-D18</v>
@@ -2160,7 +2160,7 @@
         <v>653</v>
       </c>
       <c r="C56">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="D56" t="str">
         <v>B3-D18</v>
@@ -2183,7 +2183,7 @@
         <v>654</v>
       </c>
       <c r="C57">
-        <v>45.9</v>
+        <v>45.2</v>
       </c>
       <c r="D57" t="str">
         <v>B3-D18</v>
@@ -2206,7 +2206,7 @@
         <v>655</v>
       </c>
       <c r="C58">
-        <v>45.1</v>
+        <v>44.3</v>
       </c>
       <c r="D58" t="str">
         <v>B3-D18</v>
@@ -2229,7 +2229,7 @@
         <v>656</v>
       </c>
       <c r="C59">
-        <v>44.2</v>
+        <v>43.5</v>
       </c>
       <c r="D59" t="str">
         <v>B3-D13</v>
@@ -2238,7 +2238,7 @@
         <v>165</v>
       </c>
       <c r="F59">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -2252,7 +2252,7 @@
         <v>657</v>
       </c>
       <c r="C60">
-        <v>47</v>
+        <v>46.2</v>
       </c>
       <c r="D60" t="str">
         <v>B3-D02</v>
@@ -2261,7 +2261,7 @@
         <v>180</v>
       </c>
       <c r="F60">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="G60">
         <v>7</v>
@@ -2275,7 +2275,7 @@
         <v>658</v>
       </c>
       <c r="C61">
-        <v>49.8</v>
+        <v>48.9</v>
       </c>
       <c r="D61" t="str">
         <v>B3-D02</v>
@@ -2298,7 +2298,7 @@
         <v>659</v>
       </c>
       <c r="C62">
-        <v>52.5</v>
+        <v>51.6</v>
       </c>
       <c r="D62" t="str">
         <v>B3-D02</v>
@@ -2307,7 +2307,7 @@
         <v>180</v>
       </c>
       <c r="F62">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G62">
         <v>8</v>
@@ -2321,7 +2321,7 @@
         <v>660</v>
       </c>
       <c r="C63">
-        <v>55.2</v>
+        <v>54.3</v>
       </c>
       <c r="D63" t="str">
         <v>B3-D02</v>
@@ -2344,7 +2344,7 @@
         <v>661</v>
       </c>
       <c r="C64">
-        <v>57.8</v>
+        <v>56.8</v>
       </c>
       <c r="D64" t="str">
         <v>B3-D02</v>
@@ -2367,7 +2367,7 @@
         <v>662</v>
       </c>
       <c r="C65">
-        <v>60.2</v>
+        <v>59.3</v>
       </c>
       <c r="D65" t="str">
         <v>B3-D02</v>
@@ -2390,7 +2390,7 @@
         <v>662.76</v>
       </c>
       <c r="C66">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D66" t="str">
         <v>B3-D02</v>
@@ -2413,7 +2413,7 @@
         <v>663</v>
       </c>
       <c r="C67">
-        <v>62.5</v>
+        <v>61.5</v>
       </c>
       <c r="D67" t="str">
         <v>B3-D02</v>
@@ -2436,7 +2436,7 @@
         <v>664</v>
       </c>
       <c r="C68">
-        <v>64.7</v>
+        <v>63.6</v>
       </c>
       <c r="D68" t="str">
         <v>B3-D02</v>
@@ -2445,7 +2445,7 @@
         <v>180</v>
       </c>
       <c r="F68">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G68">
         <v>7</v>
@@ -2459,7 +2459,7 @@
         <v>665</v>
       </c>
       <c r="C69">
-        <v>66.6</v>
+        <v>65.6</v>
       </c>
       <c r="D69" t="str">
         <v>B3-D02</v>
@@ -2482,7 +2482,7 @@
         <v>666</v>
       </c>
       <c r="C70">
-        <v>68.4</v>
+        <v>67.3</v>
       </c>
       <c r="D70" t="str">
         <v>B3-D02</v>
@@ -2491,7 +2491,7 @@
         <v>180</v>
       </c>
       <c r="F70">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
       <c r="G70">
         <v>7</v>
@@ -2505,7 +2505,7 @@
         <v>667</v>
       </c>
       <c r="C71">
-        <v>70</v>
+        <v>68.9</v>
       </c>
       <c r="D71" t="str">
         <v>B3-D02</v>
@@ -2514,7 +2514,7 @@
         <v>180</v>
       </c>
       <c r="F71">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="G71">
         <v>7</v>
@@ -2528,7 +2528,7 @@
         <v>668</v>
       </c>
       <c r="C72">
-        <v>71.4</v>
+        <v>70.3</v>
       </c>
       <c r="D72" t="str">
         <v>B3-D02</v>
@@ -2537,7 +2537,7 @@
         <v>180</v>
       </c>
       <c r="F72">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="G72">
         <v>7</v>
@@ -2551,7 +2551,7 @@
         <v>669</v>
       </c>
       <c r="C73">
-        <v>72.6</v>
+        <v>71.5</v>
       </c>
       <c r="D73" t="str">
         <v>B3-D02</v>
@@ -2560,7 +2560,7 @@
         <v>180</v>
       </c>
       <c r="F73">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="G73">
         <v>7</v>
@@ -2574,7 +2574,7 @@
         <v>669.05</v>
       </c>
       <c r="C74">
-        <v>72.6</v>
+        <v>71.5</v>
       </c>
       <c r="D74" t="str">
         <v>B3-D02</v>
@@ -2583,7 +2583,7 @@
         <v>180</v>
       </c>
       <c r="F74">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="G74">
         <v>7</v>
@@ -2597,7 +2597,7 @@
         <v>649.5</v>
       </c>
       <c r="C75">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="D75" t="str">
         <v>B4-D10</v>
@@ -2620,7 +2620,7 @@
         <v>650</v>
       </c>
       <c r="C76">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="D76" t="str">
         <v>B4-D10</v>
@@ -2643,7 +2643,7 @@
         <v>651</v>
       </c>
       <c r="C77">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="D77" t="str">
         <v>B4-D10</v>
@@ -2666,7 +2666,7 @@
         <v>652</v>
       </c>
       <c r="C78">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="D78" t="str">
         <v>B4-D10</v>
@@ -2689,7 +2689,7 @@
         <v>653</v>
       </c>
       <c r="C79">
-        <v>60.7</v>
+        <v>60.9</v>
       </c>
       <c r="D79" t="str">
         <v>B4-D10</v>
@@ -2712,7 +2712,7 @@
         <v>654</v>
       </c>
       <c r="C80">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
       <c r="D80" t="str">
         <v>B4-D10</v>
@@ -2735,7 +2735,7 @@
         <v>655</v>
       </c>
       <c r="C81">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
       <c r="D81" t="str">
         <v>B4-D10</v>
@@ -2758,7 +2758,7 @@
         <v>656</v>
       </c>
       <c r="C82">
-        <v>63.5</v>
+        <v>63.6</v>
       </c>
       <c r="D82" t="str">
         <v>B4-D10</v>
@@ -2781,7 +2781,7 @@
         <v>657</v>
       </c>
       <c r="C83">
-        <v>64.5</v>
+        <v>64.6</v>
       </c>
       <c r="D83" t="str">
         <v>B4-D10</v>
@@ -2804,7 +2804,7 @@
         <v>658</v>
       </c>
       <c r="C84">
-        <v>65.6</v>
+        <v>65.7</v>
       </c>
       <c r="D84" t="str">
         <v>B4-D10</v>
@@ -2827,7 +2827,7 @@
         <v>659</v>
       </c>
       <c r="C85">
-        <v>66.7</v>
+        <v>66.8</v>
       </c>
       <c r="D85" t="str">
         <v>B4-D10</v>
@@ -2850,7 +2850,7 @@
         <v>660</v>
       </c>
       <c r="C86">
-        <v>67.8</v>
+        <v>67.9</v>
       </c>
       <c r="D86" t="str">
         <v>B4-D10</v>
@@ -2873,7 +2873,7 @@
         <v>661</v>
       </c>
       <c r="C87">
-        <v>68.9</v>
+        <v>69</v>
       </c>
       <c r="D87" t="str">
         <v>B4-D10</v>
@@ -2896,7 +2896,7 @@
         <v>662</v>
       </c>
       <c r="C88">
-        <v>70</v>
+        <v>70.1</v>
       </c>
       <c r="D88" t="str">
         <v>B4-D10</v>
@@ -2919,7 +2919,7 @@
         <v>662.76</v>
       </c>
       <c r="C89">
-        <v>70.8</v>
+        <v>71</v>
       </c>
       <c r="D89" t="str">
         <v>B4-D10</v>
@@ -2942,7 +2942,7 @@
         <v>663</v>
       </c>
       <c r="C90">
-        <v>71.1</v>
+        <v>71.2</v>
       </c>
       <c r="D90" t="str">
         <v>B4-D10</v>
@@ -2965,7 +2965,7 @@
         <v>664</v>
       </c>
       <c r="C91">
-        <v>72.2</v>
+        <v>72.4</v>
       </c>
       <c r="D91" t="str">
         <v>B4-D10</v>
@@ -2974,7 +2974,7 @@
         <v>180</v>
       </c>
       <c r="F91">
-        <v>0.55</v>
+        <v>0.56</v>
       </c>
       <c r="G91">
         <v>14</v>
@@ -2988,7 +2988,7 @@
         <v>665</v>
       </c>
       <c r="C92">
-        <v>73.4</v>
+        <v>73.6</v>
       </c>
       <c r="D92" t="str">
         <v>B4-D10</v>
@@ -3011,7 +3011,7 @@
         <v>666</v>
       </c>
       <c r="C93">
-        <v>74.5</v>
+        <v>74.7</v>
       </c>
       <c r="D93" t="str">
         <v>B4-D10</v>
@@ -3034,7 +3034,7 @@
         <v>667</v>
       </c>
       <c r="C94">
-        <v>75.6</v>
+        <v>75.8</v>
       </c>
       <c r="D94" t="str">
         <v>B4-D10</v>
@@ -3043,7 +3043,7 @@
         <v>180</v>
       </c>
       <c r="F94">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="G94">
         <v>14</v>
@@ -3057,7 +3057,7 @@
         <v>668</v>
       </c>
       <c r="C95">
-        <v>76.6</v>
+        <v>76.8</v>
       </c>
       <c r="D95" t="str">
         <v>B4-D10</v>
@@ -3080,7 +3080,7 @@
         <v>669</v>
       </c>
       <c r="C96">
-        <v>77.5</v>
+        <v>77.7</v>
       </c>
       <c r="D96" t="str">
         <v>B4-D10</v>
@@ -3103,7 +3103,7 @@
         <v>669.05</v>
       </c>
       <c r="C97">
-        <v>77.6</v>
+        <v>77.8</v>
       </c>
       <c r="D97" t="str">
         <v>B4-D10</v>
@@ -3126,7 +3126,7 @@
         <v>649.5</v>
       </c>
       <c r="C98">
-        <v>101.2</v>
+        <v>100.9</v>
       </c>
       <c r="D98" t="str">
         <v>B5-D17</v>
@@ -3149,7 +3149,7 @@
         <v>650</v>
       </c>
       <c r="C99">
-        <v>100.7</v>
+        <v>100.4</v>
       </c>
       <c r="D99" t="str">
         <v>B5-D17</v>
@@ -3172,7 +3172,7 @@
         <v>651</v>
       </c>
       <c r="C100">
-        <v>99.7</v>
+        <v>99.4</v>
       </c>
       <c r="D100" t="str">
         <v>B5-D17</v>
@@ -3195,7 +3195,7 @@
         <v>652</v>
       </c>
       <c r="C101">
-        <v>98.5</v>
+        <v>98.2</v>
       </c>
       <c r="D101" t="str">
         <v>B5-D17</v>
@@ -3218,7 +3218,7 @@
         <v>653</v>
       </c>
       <c r="C102">
-        <v>97.1</v>
+        <v>96.9</v>
       </c>
       <c r="D102" t="str">
         <v>B5-D17</v>
@@ -3241,7 +3241,7 @@
         <v>654</v>
       </c>
       <c r="C103">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="D103" t="str">
         <v>B5-D17</v>
@@ -3264,7 +3264,7 @@
         <v>655</v>
       </c>
       <c r="C104">
-        <v>94.3</v>
+        <v>94</v>
       </c>
       <c r="D104" t="str">
         <v>B5-D17</v>
@@ -3287,7 +3287,7 @@
         <v>656</v>
       </c>
       <c r="C105">
-        <v>92.7</v>
+        <v>92.4</v>
       </c>
       <c r="D105" t="str">
         <v>B5-D17</v>
@@ -3296,7 +3296,7 @@
         <v>135</v>
       </c>
       <c r="F105">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="G105">
         <v>13</v>
@@ -3310,7 +3310,7 @@
         <v>657</v>
       </c>
       <c r="C106">
-        <v>91</v>
+        <v>90.7</v>
       </c>
       <c r="D106" t="str">
         <v>B5-D17</v>
@@ -3333,7 +3333,7 @@
         <v>658</v>
       </c>
       <c r="C107">
-        <v>89.3</v>
+        <v>89</v>
       </c>
       <c r="D107" t="str">
         <v>B5-D17</v>
@@ -3356,7 +3356,7 @@
         <v>659</v>
       </c>
       <c r="C108">
-        <v>87.5</v>
+        <v>87.2</v>
       </c>
       <c r="D108" t="str">
         <v>B5-D17</v>
@@ -3365,7 +3365,7 @@
         <v>135</v>
       </c>
       <c r="F108">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="G108">
         <v>13</v>
@@ -3379,7 +3379,7 @@
         <v>660</v>
       </c>
       <c r="C109">
-        <v>85.6</v>
+        <v>85.4</v>
       </c>
       <c r="D109" t="str">
         <v>B5-D17</v>
@@ -3402,7 +3402,7 @@
         <v>661</v>
       </c>
       <c r="C110">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="D110" t="str">
         <v>B5-D17</v>
@@ -3411,7 +3411,7 @@
         <v>135</v>
       </c>
       <c r="F110">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="G110">
         <v>13</v>
@@ -3425,7 +3425,7 @@
         <v>662</v>
       </c>
       <c r="C111">
-        <v>81.9</v>
+        <v>81.6</v>
       </c>
       <c r="D111" t="str">
         <v>B5-D17</v>
@@ -3448,7 +3448,7 @@
         <v>662.76</v>
       </c>
       <c r="C112">
-        <v>80.4</v>
+        <v>80.2</v>
       </c>
       <c r="D112" t="str">
         <v>B5-D17</v>
@@ -3457,7 +3457,7 @@
         <v>135</v>
       </c>
       <c r="F112">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="G112">
         <v>13</v>
@@ -3471,7 +3471,7 @@
         <v>663</v>
       </c>
       <c r="C113">
-        <v>79.9</v>
+        <v>79.7</v>
       </c>
       <c r="D113" t="str">
         <v>B5-D17</v>
@@ -3494,7 +3494,7 @@
         <v>664</v>
       </c>
       <c r="C114">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="D114" t="str">
         <v>B5-D17</v>
@@ -3517,7 +3517,7 @@
         <v>665</v>
       </c>
       <c r="C115">
-        <v>76.1</v>
+        <v>75.9</v>
       </c>
       <c r="D115" t="str">
         <v>B5-D17</v>
@@ -3540,7 +3540,7 @@
         <v>666</v>
       </c>
       <c r="C116">
-        <v>74.2</v>
+        <v>74</v>
       </c>
       <c r="D116" t="str">
         <v>B5-D17</v>
@@ -3563,7 +3563,7 @@
         <v>667</v>
       </c>
       <c r="C117">
-        <v>72.4</v>
+        <v>72.2</v>
       </c>
       <c r="D117" t="str">
         <v>B5-D17</v>
@@ -3572,7 +3572,7 @@
         <v>135</v>
       </c>
       <c r="F117">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="G117">
         <v>13</v>
@@ -3586,7 +3586,7 @@
         <v>668</v>
       </c>
       <c r="C118">
-        <v>71.6</v>
+        <v>71.4</v>
       </c>
       <c r="D118" t="str">
         <v>B5-D08</v>
@@ -3595,7 +3595,7 @@
         <v>165</v>
       </c>
       <c r="F118">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="G118">
         <v>13</v>
@@ -3609,7 +3609,7 @@
         <v>669</v>
       </c>
       <c r="C119">
-        <v>72.2</v>
+        <v>71.9</v>
       </c>
       <c r="D119" t="str">
         <v>B5-D08</v>
@@ -3632,7 +3632,7 @@
         <v>669.05</v>
       </c>
       <c r="C120">
-        <v>72.2</v>
+        <v>72</v>
       </c>
       <c r="D120" t="str">
         <v>B5-D08</v>
@@ -3655,7 +3655,7 @@
         <v>649.5</v>
       </c>
       <c r="C121">
-        <v>145.4</v>
+        <v>147.1</v>
       </c>
       <c r="D121" t="str">
         <v>B6-D06</v>
@@ -3664,7 +3664,7 @@
         <v>300</v>
       </c>
       <c r="F121">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
       <c r="G121">
         <v>22</v>
@@ -3678,7 +3678,7 @@
         <v>650</v>
       </c>
       <c r="C122">
-        <v>144.4</v>
+        <v>146.1</v>
       </c>
       <c r="D122" t="str">
         <v>B6-D06</v>
@@ -3687,7 +3687,7 @@
         <v>300</v>
       </c>
       <c r="F122">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
       <c r="G122">
         <v>22</v>
@@ -3701,7 +3701,7 @@
         <v>651</v>
       </c>
       <c r="C123">
-        <v>142.2</v>
+        <v>143.9</v>
       </c>
       <c r="D123" t="str">
         <v>B6-D06</v>
@@ -3710,7 +3710,7 @@
         <v>300</v>
       </c>
       <c r="F123">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
       <c r="G123">
         <v>22</v>
@@ -3724,7 +3724,7 @@
         <v>652</v>
       </c>
       <c r="C124">
-        <v>140</v>
+        <v>141.7</v>
       </c>
       <c r="D124" t="str">
         <v>B6-D06</v>
@@ -3733,7 +3733,7 @@
         <v>300</v>
       </c>
       <c r="F124">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="G124">
         <v>21</v>
@@ -3747,7 +3747,7 @@
         <v>653</v>
       </c>
       <c r="C125">
-        <v>137.7</v>
+        <v>139.3</v>
       </c>
       <c r="D125" t="str">
         <v>B6-D06</v>
@@ -3756,7 +3756,7 @@
         <v>300</v>
       </c>
       <c r="F125">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="G125">
         <v>21</v>
@@ -3770,7 +3770,7 @@
         <v>654</v>
       </c>
       <c r="C126">
-        <v>135.2</v>
+        <v>136.8</v>
       </c>
       <c r="D126" t="str">
         <v>B6-D06</v>
@@ -3779,7 +3779,7 @@
         <v>300</v>
       </c>
       <c r="F126">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="G126">
         <v>21</v>
@@ -3793,7 +3793,7 @@
         <v>655</v>
       </c>
       <c r="C127">
-        <v>132.7</v>
+        <v>134.3</v>
       </c>
       <c r="D127" t="str">
         <v>B6-D06</v>
@@ -3802,7 +3802,7 @@
         <v>300</v>
       </c>
       <c r="F127">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="G127">
         <v>21</v>
@@ -3816,7 +3816,7 @@
         <v>656</v>
       </c>
       <c r="C128">
-        <v>130.1</v>
+        <v>131.7</v>
       </c>
       <c r="D128" t="str">
         <v>B6-D06</v>
@@ -3825,7 +3825,7 @@
         <v>300</v>
       </c>
       <c r="F128">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="G128">
         <v>21</v>
@@ -3839,7 +3839,7 @@
         <v>657</v>
       </c>
       <c r="C129">
-        <v>127.5</v>
+        <v>129</v>
       </c>
       <c r="D129" t="str">
         <v>B6-D06</v>
@@ -3848,7 +3848,7 @@
         <v>300</v>
       </c>
       <c r="F129">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="G129">
         <v>21</v>
@@ -3862,7 +3862,7 @@
         <v>658</v>
       </c>
       <c r="C130">
-        <v>124.8</v>
+        <v>126.3</v>
       </c>
       <c r="D130" t="str">
         <v>B6-D06</v>
@@ -3871,7 +3871,7 @@
         <v>300</v>
       </c>
       <c r="F130">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
       <c r="G130">
         <v>21</v>
@@ -3885,7 +3885,7 @@
         <v>659</v>
       </c>
       <c r="C131">
-        <v>122.1</v>
+        <v>123.6</v>
       </c>
       <c r="D131" t="str">
         <v>B6-D06</v>
@@ -3894,7 +3894,7 @@
         <v>300</v>
       </c>
       <c r="F131">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
       <c r="G131">
         <v>21</v>
@@ -3908,7 +3908,7 @@
         <v>660</v>
       </c>
       <c r="C132">
-        <v>119.4</v>
+        <v>120.9</v>
       </c>
       <c r="D132" t="str">
         <v>B6-D06</v>
@@ -3917,7 +3917,7 @@
         <v>300</v>
       </c>
       <c r="F132">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="G132">
         <v>21</v>
@@ -3931,7 +3931,7 @@
         <v>661</v>
       </c>
       <c r="C133">
-        <v>116.7</v>
+        <v>118.2</v>
       </c>
       <c r="D133" t="str">
         <v>B6-D06</v>
@@ -3940,7 +3940,7 @@
         <v>300</v>
       </c>
       <c r="F133">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="G133">
         <v>21</v>
@@ -3954,7 +3954,7 @@
         <v>662</v>
       </c>
       <c r="C134">
-        <v>114.1</v>
+        <v>115.6</v>
       </c>
       <c r="D134" t="str">
         <v>B6-D06</v>
@@ -3963,7 +3963,7 @@
         <v>300</v>
       </c>
       <c r="F134">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="G134">
         <v>21</v>
@@ -3977,7 +3977,7 @@
         <v>662.76</v>
       </c>
       <c r="C135">
-        <v>112.1</v>
+        <v>113.6</v>
       </c>
       <c r="D135" t="str">
         <v>B6-D06</v>
@@ -3986,7 +3986,7 @@
         <v>300</v>
       </c>
       <c r="F135">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="G135">
         <v>21</v>
@@ -4000,7 +4000,7 @@
         <v>663</v>
       </c>
       <c r="C136">
-        <v>111.5</v>
+        <v>113</v>
       </c>
       <c r="D136" t="str">
         <v>B6-D06</v>
@@ -4009,7 +4009,7 @@
         <v>300</v>
       </c>
       <c r="F136">
-        <v>0.52</v>
+        <v>0.36</v>
       </c>
       <c r="G136">
         <v>21</v>
@@ -4023,7 +4023,7 @@
         <v>664</v>
       </c>
       <c r="C137">
-        <v>109</v>
+        <v>110.4</v>
       </c>
       <c r="D137" t="str">
         <v>B6-D06</v>
@@ -4032,7 +4032,7 @@
         <v>300</v>
       </c>
       <c r="F137">
-        <v>0.52</v>
+        <v>0.37</v>
       </c>
       <c r="G137">
         <v>21</v>
@@ -4046,7 +4046,7 @@
         <v>665</v>
       </c>
       <c r="C138">
-        <v>107.2</v>
+        <v>108.4</v>
       </c>
       <c r="D138" t="str">
         <v>B6-D25</v>
@@ -4055,7 +4055,7 @@
         <v>135</v>
       </c>
       <c r="F138">
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="G138">
         <v>21</v>
@@ -4069,7 +4069,7 @@
         <v>666</v>
       </c>
       <c r="C139">
-        <v>106.5</v>
+        <v>107.7</v>
       </c>
       <c r="D139" t="str">
         <v>B6-D25</v>
@@ -4078,7 +4078,7 @@
         <v>135</v>
       </c>
       <c r="F139">
-        <v>0.54</v>
+        <v>0.38</v>
       </c>
       <c r="G139">
         <v>21</v>
@@ -4092,7 +4092,7 @@
         <v>667</v>
       </c>
       <c r="C140">
-        <v>105.6</v>
+        <v>106.8</v>
       </c>
       <c r="D140" t="str">
         <v>B6-D25</v>
@@ -4101,7 +4101,7 @@
         <v>135</v>
       </c>
       <c r="F140">
-        <v>0.55</v>
+        <v>0.39</v>
       </c>
       <c r="G140">
         <v>21</v>
@@ -4115,7 +4115,7 @@
         <v>668</v>
       </c>
       <c r="C141">
-        <v>104.6</v>
+        <v>105.9</v>
       </c>
       <c r="D141" t="str">
         <v>B6-D25</v>
@@ -4124,7 +4124,7 @@
         <v>135</v>
       </c>
       <c r="F141">
-        <v>0.56</v>
+        <v>0.39</v>
       </c>
       <c r="G141">
         <v>21</v>
@@ -4138,7 +4138,7 @@
         <v>669</v>
       </c>
       <c r="C142">
-        <v>103.5</v>
+        <v>104.8</v>
       </c>
       <c r="D142" t="str">
         <v>B6-D25</v>
@@ -4147,7 +4147,7 @@
         <v>135</v>
       </c>
       <c r="F142">
-        <v>0.58</v>
+        <v>0.41</v>
       </c>
       <c r="G142">
         <v>21</v>
@@ -4161,7 +4161,7 @@
         <v>669.05</v>
       </c>
       <c r="C143">
-        <v>103.4</v>
+        <v>104.7</v>
       </c>
       <c r="D143" t="str">
         <v>B6-D25</v>
@@ -4170,7 +4170,7 @@
         <v>135</v>
       </c>
       <c r="F143">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="G143">
         <v>21</v>
@@ -5057,25 +5057,25 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>2915</v>
+        <v>2912</v>
       </c>
       <c r="H6">
-        <v>1572.2</v>
+        <v>1570.6</v>
       </c>
       <c r="I6">
         <v>250</v>
       </c>
       <c r="J6">
-        <v>248.6</v>
+        <v>248.3</v>
       </c>
       <c r="K6">
         <v>14.5</v>
       </c>
       <c r="L6">
-        <v>263.1</v>
+        <v>262.8</v>
       </c>
       <c r="M6">
-        <v>276.2</v>
+        <v>275.9</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="Q6" t="str">
         <v>Cân bằng tĩnh theo mực nước</v>
@@ -5093,7 +5093,7 @@
         <v>85.7</v>
       </c>
       <c r="S6">
-        <v>117.7</v>
+        <v>117.6</v>
       </c>
       <c r="T6" t="str">
         <v>PES-32</v>
@@ -5131,25 +5131,25 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>4191</v>
+        <v>4200</v>
       </c>
       <c r="H7">
-        <v>2260.4</v>
+        <v>2265.3</v>
       </c>
       <c r="I7">
         <v>250</v>
       </c>
       <c r="J7">
-        <v>357.4</v>
+        <v>358.2</v>
       </c>
       <c r="K7">
         <v>19.2</v>
       </c>
       <c r="L7">
-        <v>376.6</v>
+        <v>377.4</v>
       </c>
       <c r="M7">
-        <v>395.4</v>
+        <v>396.3</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -5158,16 +5158,16 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="Q7" t="str">
         <v>Chia n dây</v>
       </c>
       <c r="R7">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="S7">
-        <v>96.3</v>
+        <v>96.5</v>
       </c>
       <c r="T7" t="str">
         <v>PES-32</v>
@@ -5176,10 +5176,10 @@
         <v>305</v>
       </c>
       <c r="V7">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="W7">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="X7" t="str">
         <v>ĐẠT</v>
@@ -5205,25 +5205,25 @@
         <v>4</v>
       </c>
       <c r="G8">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="H8">
-        <v>384.6</v>
+        <v>377.5</v>
       </c>
       <c r="I8">
         <v>250</v>
       </c>
       <c r="J8">
-        <v>60.8</v>
+        <v>59.7</v>
       </c>
       <c r="K8">
         <v>6.6</v>
       </c>
       <c r="L8">
-        <v>67.4</v>
+        <v>66.3</v>
       </c>
       <c r="M8">
-        <v>70.8</v>
+        <v>69.6</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -5232,16 +5232,16 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="Q8" t="str">
         <v>Cân bằng tĩnh theo mực nước</v>
       </c>
       <c r="R8">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="S8">
-        <v>115.3</v>
+        <v>113.7</v>
       </c>
       <c r="T8" t="str">
         <v>PES-32</v>
@@ -5250,10 +5250,10 @@
         <v>305</v>
       </c>
       <c r="V8">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="W8">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="X8" t="str">
         <v>ĐẠT</v>
@@ -5279,25 +5279,25 @@
         <v>14</v>
       </c>
       <c r="G9">
-        <v>2095</v>
+        <v>2100</v>
       </c>
       <c r="H9">
-        <v>1129.9</v>
+        <v>1132.6</v>
       </c>
       <c r="I9">
         <v>250</v>
       </c>
       <c r="J9">
-        <v>178.7</v>
+        <v>179.1</v>
       </c>
       <c r="K9">
         <v>11.8</v>
       </c>
       <c r="L9">
-        <v>190.5</v>
+        <v>190.9</v>
       </c>
       <c r="M9">
-        <v>200.1</v>
+        <v>200.5</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -5306,16 +5306,16 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="Q9" t="str">
         <v>Cân bằng tĩnh theo mực nước</v>
       </c>
       <c r="R9">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="S9">
-        <v>97.2</v>
+        <v>97.4</v>
       </c>
       <c r="T9" t="str">
         <v>PES-32</v>
@@ -5327,7 +5327,7 @@
         <v>3.69</v>
       </c>
       <c r="W9">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="X9" t="str">
         <v>ĐẠT</v>
@@ -5353,25 +5353,25 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>2809</v>
+        <v>2800</v>
       </c>
       <c r="H10">
-        <v>1515</v>
+        <v>1510.2</v>
       </c>
       <c r="I10">
         <v>250</v>
       </c>
       <c r="J10">
-        <v>239.6</v>
+        <v>238.8</v>
       </c>
       <c r="K10">
         <v>12.4</v>
       </c>
       <c r="L10">
-        <v>252</v>
+        <v>251.2</v>
       </c>
       <c r="M10">
-        <v>264.6</v>
+        <v>263.8</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -5380,16 +5380,16 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="Q10" t="str">
         <v>Cân bằng tĩnh theo mực nước</v>
       </c>
       <c r="R10">
-        <v>106.2</v>
+        <v>105.9</v>
       </c>
       <c r="S10">
-        <v>97.1</v>
+        <v>96.8</v>
       </c>
       <c r="T10" t="str">
         <v>PES-36</v>
@@ -5398,10 +5398,10 @@
         <v>385</v>
       </c>
       <c r="V10">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="W10">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="X10" t="str">
         <v>ĐẠT</v>
@@ -5427,25 +5427,25 @@
         <v>5</v>
       </c>
       <c r="G11">
-        <v>4177</v>
+        <v>4200</v>
       </c>
       <c r="H11">
-        <v>2252.9</v>
+        <v>2265.3</v>
       </c>
       <c r="I11">
         <v>250</v>
       </c>
       <c r="J11">
-        <v>356.2</v>
+        <v>358.2</v>
       </c>
       <c r="K11">
         <v>17.7</v>
       </c>
       <c r="L11">
-        <v>374</v>
+        <v>375.9</v>
       </c>
       <c r="M11">
-        <v>392.7</v>
+        <v>394.7</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -5454,28 +5454,28 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>80.6</v>
+        <v>81</v>
       </c>
       <c r="Q11" t="str">
         <v>Cân bằng tĩnh theo mực nước</v>
       </c>
       <c r="R11">
-        <v>150.4</v>
+        <v>152.1</v>
       </c>
       <c r="S11">
-        <v>133.6</v>
+        <v>135.3</v>
       </c>
       <c r="T11" t="str">
-        <v>PES-40</v>
+        <v>PES-48</v>
       </c>
       <c r="U11">
-        <v>475</v>
+        <v>688</v>
       </c>
       <c r="V11">
-        <v>3.16</v>
+        <v>4.52</v>
       </c>
       <c r="W11">
-        <v>3.56</v>
+        <v>5.09</v>
       </c>
       <c r="X11" t="str">
         <v>ĐẠT</v>
@@ -5646,16 +5646,16 @@
         <v>0.74</v>
       </c>
       <c r="M6">
-        <v>82.7</v>
+        <v>82.6</v>
       </c>
       <c r="N6">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="O6">
         <v>116</v>
       </c>
       <c r="P6">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Q6">
         <v>96.1</v>
@@ -5705,7 +5705,7 @@
         <v>Đai xoắn Φ8 a150</v>
       </c>
       <c r="I7">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="J7">
         <v>290.2</v>
@@ -5717,10 +5717,10 @@
         <v>0.7</v>
       </c>
       <c r="M7">
-        <v>76.8</v>
+        <v>77</v>
       </c>
       <c r="N7">
-        <v>92.1</v>
+        <v>92.4</v>
       </c>
       <c r="O7">
         <v>116</v>
@@ -5776,7 +5776,7 @@
         <v>Đai xoắn Φ8 a150</v>
       </c>
       <c r="I8">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="J8">
         <v>290.2</v>
@@ -5785,19 +5785,19 @@
         <v>116.1</v>
       </c>
       <c r="L8">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="M8">
-        <v>72.4</v>
+        <v>71.1</v>
       </c>
       <c r="N8">
-        <v>86.9</v>
+        <v>85.3</v>
       </c>
       <c r="O8">
         <v>93.3</v>
       </c>
       <c r="P8">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="Q8">
         <v>81.9</v>
@@ -5847,7 +5847,7 @@
         <v>Đai xoắn Φ8 a150</v>
       </c>
       <c r="I9">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="J9">
         <v>290.2</v>
@@ -5859,16 +5859,16 @@
         <v>0.71</v>
       </c>
       <c r="M9">
-        <v>78.7</v>
+        <v>78.9</v>
       </c>
       <c r="N9">
-        <v>94.4</v>
+        <v>94.7</v>
       </c>
       <c r="O9">
         <v>116</v>
       </c>
       <c r="P9">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="Q9">
         <v>96.1</v>
@@ -5918,7 +5918,7 @@
         <v>Đai xoắn Φ8 a150</v>
       </c>
       <c r="I10">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="J10">
         <v>290.2</v>
@@ -5927,19 +5927,19 @@
         <v>116.1</v>
       </c>
       <c r="L10">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="M10">
-        <v>71.9</v>
+        <v>71.7</v>
       </c>
       <c r="N10">
-        <v>86.3</v>
+        <v>86</v>
       </c>
       <c r="O10">
         <v>93.3</v>
       </c>
       <c r="P10">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="Q10">
         <v>81.9</v>
@@ -5989,7 +5989,7 @@
         <v>Đai xoắn Φ8 a150</v>
       </c>
       <c r="I11">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="J11">
         <v>290.2</v>
@@ -5998,19 +5998,19 @@
         <v>116.1</v>
       </c>
       <c r="L11">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="M11">
-        <v>69</v>
+        <v>69.7</v>
       </c>
       <c r="N11">
-        <v>82.7</v>
+        <v>83.6</v>
       </c>
       <c r="O11">
         <v>93.3</v>
       </c>
       <c r="P11">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="Q11">
         <v>81.9</v>
@@ -6317,7 +6317,7 @@
         <v>0.74</v>
       </c>
       <c r="V6">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W6">
         <v>1</v>
@@ -6403,7 +6403,7 @@
         <v>0.74</v>
       </c>
       <c r="V7">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W7">
         <v>1</v>
@@ -6489,7 +6489,7 @@
         <v>0.74</v>
       </c>
       <c r="V8">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W8">
         <v>1</v>
@@ -6575,7 +6575,7 @@
         <v>0.74</v>
       </c>
       <c r="V9">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W9">
         <v>1</v>
@@ -6661,7 +6661,7 @@
         <v>0.74</v>
       </c>
       <c r="V10">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W10">
         <v>1</v>
@@ -6747,7 +6747,7 @@
         <v>0.74</v>
       </c>
       <c r="V11">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W11">
         <v>1</v>
@@ -6833,7 +6833,7 @@
         <v>0.74</v>
       </c>
       <c r="V12">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W12">
         <v>1</v>
@@ -6919,7 +6919,7 @@
         <v>0.74</v>
       </c>
       <c r="V13">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W13">
         <v>1</v>
@@ -7005,7 +7005,7 @@
         <v>0.74</v>
       </c>
       <c r="V14">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W14">
         <v>1</v>
@@ -7091,7 +7091,7 @@
         <v>0.74</v>
       </c>
       <c r="V15">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W15">
         <v>1</v>
@@ -7177,7 +7177,7 @@
         <v>0.74</v>
       </c>
       <c r="V16">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W16">
         <v>1</v>
@@ -7263,7 +7263,7 @@
         <v>0.74</v>
       </c>
       <c r="V17">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W17">
         <v>1</v>
@@ -7349,7 +7349,7 @@
         <v>0.74</v>
       </c>
       <c r="V18">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W18">
         <v>1</v>
@@ -7435,7 +7435,7 @@
         <v>0.74</v>
       </c>
       <c r="V19">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W19">
         <v>1</v>
@@ -7521,7 +7521,7 @@
         <v>0.74</v>
       </c>
       <c r="V20">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W20">
         <v>1</v>
@@ -7607,7 +7607,7 @@
         <v>0.74</v>
       </c>
       <c r="V21">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W21">
         <v>1</v>
@@ -7693,7 +7693,7 @@
         <v>0.74</v>
       </c>
       <c r="V22">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W22">
         <v>1</v>
@@ -7779,7 +7779,7 @@
         <v>0.74</v>
       </c>
       <c r="V23">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W23">
         <v>1</v>
@@ -7865,7 +7865,7 @@
         <v>0.74</v>
       </c>
       <c r="V24">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W24">
         <v>1</v>
@@ -7951,7 +7951,7 @@
         <v>0.74</v>
       </c>
       <c r="V25">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W25">
         <v>1</v>
@@ -8037,7 +8037,7 @@
         <v>0.74</v>
       </c>
       <c r="V26">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W26">
         <v>1</v>
@@ -8123,7 +8123,7 @@
         <v>0.74</v>
       </c>
       <c r="V27">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W27">
         <v>1</v>
@@ -8209,7 +8209,7 @@
         <v>0.74</v>
       </c>
       <c r="V28">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W28">
         <v>1</v>
@@ -8295,7 +8295,7 @@
         <v>0.74</v>
       </c>
       <c r="V29">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W29">
         <v>1</v>
@@ -8381,7 +8381,7 @@
         <v>0.74</v>
       </c>
       <c r="V30">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W30">
         <v>1</v>
@@ -8467,7 +8467,7 @@
         <v>0.74</v>
       </c>
       <c r="V31">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W31">
         <v>1</v>
@@ -8553,7 +8553,7 @@
         <v>0.74</v>
       </c>
       <c r="V32">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W32">
         <v>1</v>
@@ -8639,7 +8639,7 @@
         <v>0.74</v>
       </c>
       <c r="V33">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W33">
         <v>1</v>
@@ -8725,7 +8725,7 @@
         <v>0.74</v>
       </c>
       <c r="V34">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W34">
         <v>1</v>
@@ -8811,7 +8811,7 @@
         <v>0.74</v>
       </c>
       <c r="V35">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W35">
         <v>1</v>
@@ -8897,7 +8897,7 @@
         <v>0.74</v>
       </c>
       <c r="V36">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W36">
         <v>1</v>
@@ -8983,7 +8983,7 @@
         <v>0.74</v>
       </c>
       <c r="V37">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W37">
         <v>1</v>
@@ -9069,7 +9069,7 @@
         <v>0.74</v>
       </c>
       <c r="V38">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W38">
         <v>1</v>
@@ -9155,7 +9155,7 @@
         <v>0.74</v>
       </c>
       <c r="V39">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="W39">
         <v>1</v>
@@ -9232,7 +9232,7 @@
         <v>287.5</v>
       </c>
       <c r="S40">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T40">
         <v>96.1</v>
@@ -9318,7 +9318,7 @@
         <v>210</v>
       </c>
       <c r="S41">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T41">
         <v>96.1</v>
@@ -9404,7 +9404,7 @@
         <v>40</v>
       </c>
       <c r="S42">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T42">
         <v>96.1</v>
@@ -9490,7 +9490,7 @@
         <v>240</v>
       </c>
       <c r="S43">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T43">
         <v>96.1</v>
@@ -9576,7 +9576,7 @@
         <v>40</v>
       </c>
       <c r="S44">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T44">
         <v>96.1</v>
@@ -9662,7 +9662,7 @@
         <v>160</v>
       </c>
       <c r="S45">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T45">
         <v>96.1</v>
@@ -9748,7 +9748,7 @@
         <v>125</v>
       </c>
       <c r="S46">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T46">
         <v>96.1</v>
@@ -9834,7 +9834,7 @@
         <v>215</v>
       </c>
       <c r="S47">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T47">
         <v>96.1</v>
@@ -9920,7 +9920,7 @@
         <v>105</v>
       </c>
       <c r="S48">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T48">
         <v>96.1</v>
@@ -10006,7 +10006,7 @@
         <v>290</v>
       </c>
       <c r="S49">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T49">
         <v>96.1</v>
@@ -10092,7 +10092,7 @@
         <v>340</v>
       </c>
       <c r="S50">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T50">
         <v>96.1</v>
@@ -10178,7 +10178,7 @@
         <v>350</v>
       </c>
       <c r="S51">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T51">
         <v>96.1</v>
@@ -10264,7 +10264,7 @@
         <v>180</v>
       </c>
       <c r="S52">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T52">
         <v>96.1</v>
@@ -10350,7 +10350,7 @@
         <v>255</v>
       </c>
       <c r="S53">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T53">
         <v>96.1</v>
@@ -10436,7 +10436,7 @@
         <v>40</v>
       </c>
       <c r="S54">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T54">
         <v>96.1</v>
@@ -10522,7 +10522,7 @@
         <v>105</v>
       </c>
       <c r="S55">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T55">
         <v>96.1</v>
@@ -10608,7 +10608,7 @@
         <v>185</v>
       </c>
       <c r="S56">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T56">
         <v>96.1</v>
@@ -10694,7 +10694,7 @@
         <v>215</v>
       </c>
       <c r="S57">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T57">
         <v>96.1</v>
@@ -10780,7 +10780,7 @@
         <v>285</v>
       </c>
       <c r="S58">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T58">
         <v>96.1</v>
@@ -10866,7 +10866,7 @@
         <v>132.5</v>
       </c>
       <c r="S59">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T59">
         <v>96.1</v>
@@ -10952,7 +10952,7 @@
         <v>40</v>
       </c>
       <c r="S60">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T60">
         <v>96.1</v>
@@ -11038,7 +11038,7 @@
         <v>280</v>
       </c>
       <c r="S61">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T61">
         <v>96.1</v>
@@ -11124,7 +11124,7 @@
         <v>15</v>
       </c>
       <c r="S62">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T62">
         <v>96.1</v>
@@ -11210,7 +11210,7 @@
         <v>190</v>
       </c>
       <c r="S63">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T63">
         <v>96.1</v>
@@ -11296,7 +11296,7 @@
         <v>170</v>
       </c>
       <c r="S64">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T64">
         <v>96.1</v>
@@ -11382,7 +11382,7 @@
         <v>25</v>
       </c>
       <c r="S65">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T65">
         <v>96.1</v>
@@ -11468,7 +11468,7 @@
         <v>290</v>
       </c>
       <c r="S66">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T66">
         <v>96.1</v>
@@ -11554,7 +11554,7 @@
         <v>345</v>
       </c>
       <c r="S67">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T67">
         <v>96.1</v>
@@ -11640,7 +11640,7 @@
         <v>247.5</v>
       </c>
       <c r="S68">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T68">
         <v>96.1</v>
@@ -11726,7 +11726,7 @@
         <v>100</v>
       </c>
       <c r="S69">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T69">
         <v>96.1</v>
@@ -11812,7 +11812,7 @@
         <v>280</v>
       </c>
       <c r="S70">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T70">
         <v>96.1</v>
@@ -11898,7 +11898,7 @@
         <v>10</v>
       </c>
       <c r="S71">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T71">
         <v>96.1</v>
@@ -11984,7 +11984,7 @@
         <v>255</v>
       </c>
       <c r="S72">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T72">
         <v>96.1</v>
@@ -12070,7 +12070,7 @@
         <v>200</v>
       </c>
       <c r="S73">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T73">
         <v>96.1</v>
@@ -12156,7 +12156,7 @@
         <v>145</v>
       </c>
       <c r="S74">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T74">
         <v>96.1</v>
@@ -12242,7 +12242,7 @@
         <v>50</v>
       </c>
       <c r="S75">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T75">
         <v>96.1</v>
@@ -12328,7 +12328,7 @@
         <v>180</v>
       </c>
       <c r="S76">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T76">
         <v>96.1</v>
@@ -12414,7 +12414,7 @@
         <v>30</v>
       </c>
       <c r="S77">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T77">
         <v>96.1</v>
@@ -12500,7 +12500,7 @@
         <v>30</v>
       </c>
       <c r="S78">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T78">
         <v>96.1</v>
@@ -12586,7 +12586,7 @@
         <v>127.5</v>
       </c>
       <c r="S79">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T79">
         <v>96.1</v>
@@ -12672,7 +12672,7 @@
         <v>219.7</v>
       </c>
       <c r="S80">
-        <v>81.1</v>
+        <v>81.3</v>
       </c>
       <c r="T80">
         <v>96.1</v>
@@ -12758,16 +12758,16 @@
         <v>69</v>
       </c>
       <c r="S81">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T81">
         <v>81.9</v>
       </c>
       <c r="U81">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V81">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W81">
         <v>1</v>
@@ -12844,16 +12844,16 @@
         <v>269</v>
       </c>
       <c r="S82">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T82">
         <v>81.9</v>
       </c>
       <c r="U82">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V82">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W82">
         <v>1</v>
@@ -12930,16 +12930,16 @@
         <v>94</v>
       </c>
       <c r="S83">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T83">
         <v>81.9</v>
       </c>
       <c r="U83">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V83">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W83">
         <v>1</v>
@@ -13016,16 +13016,16 @@
         <v>84</v>
       </c>
       <c r="S84">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T84">
         <v>81.9</v>
       </c>
       <c r="U84">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V84">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W84">
         <v>1</v>
@@ -13102,16 +13102,16 @@
         <v>254</v>
       </c>
       <c r="S85">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T85">
         <v>81.9</v>
       </c>
       <c r="U85">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V85">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W85">
         <v>1</v>
@@ -13188,16 +13188,16 @@
         <v>229</v>
       </c>
       <c r="S86">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T86">
         <v>81.9</v>
       </c>
       <c r="U86">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V86">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W86">
         <v>1</v>
@@ -13274,16 +13274,16 @@
         <v>94</v>
       </c>
       <c r="S87">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T87">
         <v>81.9</v>
       </c>
       <c r="U87">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V87">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W87">
         <v>1</v>
@@ -13360,16 +13360,16 @@
         <v>264</v>
       </c>
       <c r="S88">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T88">
         <v>81.9</v>
       </c>
       <c r="U88">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V88">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W88">
         <v>1</v>
@@ -13446,16 +13446,16 @@
         <v>84</v>
       </c>
       <c r="S89">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T89">
         <v>81.9</v>
       </c>
       <c r="U89">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V89">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W89">
         <v>1</v>
@@ -13532,16 +13532,16 @@
         <v>84</v>
       </c>
       <c r="S90">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T90">
         <v>81.9</v>
       </c>
       <c r="U90">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V90">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W90">
         <v>1</v>
@@ -13618,16 +13618,16 @@
         <v>229</v>
       </c>
       <c r="S91">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T91">
         <v>81.9</v>
       </c>
       <c r="U91">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V91">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W91">
         <v>1</v>
@@ -13704,16 +13704,16 @@
         <v>239</v>
       </c>
       <c r="S92">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T92">
         <v>81.9</v>
       </c>
       <c r="U92">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V92">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W92">
         <v>1</v>
@@ -13790,16 +13790,16 @@
         <v>109</v>
       </c>
       <c r="S93">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T93">
         <v>81.9</v>
       </c>
       <c r="U93">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V93">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W93">
         <v>1</v>
@@ -13876,16 +13876,16 @@
         <v>274</v>
       </c>
       <c r="S94">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T94">
         <v>81.9</v>
       </c>
       <c r="U94">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V94">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W94">
         <v>1</v>
@@ -13962,16 +13962,16 @@
         <v>259</v>
       </c>
       <c r="S95">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="T95">
         <v>81.9</v>
       </c>
       <c r="U95">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V95">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="W95">
         <v>1</v>
@@ -14048,7 +14048,7 @@
         <v>94.9</v>
       </c>
       <c r="S96">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T96">
         <v>96.1</v>
@@ -14057,7 +14057,7 @@
         <v>0.71</v>
       </c>
       <c r="V96">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W96">
         <v>1</v>
@@ -14134,7 +14134,7 @@
         <v>84.9</v>
       </c>
       <c r="S97">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T97">
         <v>96.1</v>
@@ -14143,7 +14143,7 @@
         <v>0.71</v>
       </c>
       <c r="V97">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W97">
         <v>1</v>
@@ -14220,7 +14220,7 @@
         <v>267.7</v>
       </c>
       <c r="S98">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T98">
         <v>96.1</v>
@@ -14229,7 +14229,7 @@
         <v>0.71</v>
       </c>
       <c r="V98">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W98">
         <v>1</v>
@@ -14306,7 +14306,7 @@
         <v>135</v>
       </c>
       <c r="S99">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T99">
         <v>96.1</v>
@@ -14315,7 +14315,7 @@
         <v>0.71</v>
       </c>
       <c r="V99">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W99">
         <v>1</v>
@@ -14392,7 +14392,7 @@
         <v>85</v>
       </c>
       <c r="S100">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T100">
         <v>96.1</v>
@@ -14401,7 +14401,7 @@
         <v>0.71</v>
       </c>
       <c r="V100">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W100">
         <v>1</v>
@@ -14478,7 +14478,7 @@
         <v>119.9</v>
       </c>
       <c r="S101">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T101">
         <v>96.1</v>
@@ -14487,7 +14487,7 @@
         <v>0.71</v>
       </c>
       <c r="V101">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W101">
         <v>1</v>
@@ -14564,7 +14564,7 @@
         <v>79.9</v>
       </c>
       <c r="S102">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T102">
         <v>96.1</v>
@@ -14573,7 +14573,7 @@
         <v>0.71</v>
       </c>
       <c r="V102">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W102">
         <v>1</v>
@@ -14650,7 +14650,7 @@
         <v>122.4</v>
       </c>
       <c r="S103">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T103">
         <v>96.1</v>
@@ -14659,7 +14659,7 @@
         <v>0.71</v>
       </c>
       <c r="V103">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W103">
         <v>1</v>
@@ -14736,7 +14736,7 @@
         <v>286.7</v>
       </c>
       <c r="S104">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T104">
         <v>96.1</v>
@@ -14745,7 +14745,7 @@
         <v>0.71</v>
       </c>
       <c r="V104">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W104">
         <v>1</v>
@@ -14822,7 +14822,7 @@
         <v>104.9</v>
       </c>
       <c r="S105">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T105">
         <v>96.1</v>
@@ -14831,7 +14831,7 @@
         <v>0.71</v>
       </c>
       <c r="V105">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W105">
         <v>1</v>
@@ -14908,7 +14908,7 @@
         <v>79.9</v>
       </c>
       <c r="S106">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T106">
         <v>96.1</v>
@@ -14917,7 +14917,7 @@
         <v>0.71</v>
       </c>
       <c r="V106">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W106">
         <v>1</v>
@@ -14994,7 +14994,7 @@
         <v>127.4</v>
       </c>
       <c r="S107">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T107">
         <v>96.1</v>
@@ -15003,7 +15003,7 @@
         <v>0.71</v>
       </c>
       <c r="V107">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W107">
         <v>1</v>
@@ -15080,7 +15080,7 @@
         <v>254.9</v>
       </c>
       <c r="S108">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T108">
         <v>96.1</v>
@@ -15089,7 +15089,7 @@
         <v>0.71</v>
       </c>
       <c r="V108">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W108">
         <v>1</v>
@@ -15166,7 +15166,7 @@
         <v>94.9</v>
       </c>
       <c r="S109">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T109">
         <v>96.1</v>
@@ -15175,7 +15175,7 @@
         <v>0.71</v>
       </c>
       <c r="V109">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W109">
         <v>1</v>
@@ -15252,7 +15252,7 @@
         <v>295.4</v>
       </c>
       <c r="S110">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T110">
         <v>96.1</v>
@@ -15261,7 +15261,7 @@
         <v>0.71</v>
       </c>
       <c r="V110">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W110">
         <v>1</v>
@@ -15338,7 +15338,7 @@
         <v>114.9</v>
       </c>
       <c r="S111">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T111">
         <v>96.1</v>
@@ -15347,7 +15347,7 @@
         <v>0.71</v>
       </c>
       <c r="V111">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W111">
         <v>1</v>
@@ -15424,7 +15424,7 @@
         <v>69.9</v>
       </c>
       <c r="S112">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T112">
         <v>96.1</v>
@@ -15433,7 +15433,7 @@
         <v>0.71</v>
       </c>
       <c r="V112">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W112">
         <v>1</v>
@@ -15510,7 +15510,7 @@
         <v>109.9</v>
       </c>
       <c r="S113">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T113">
         <v>96.1</v>
@@ -15519,7 +15519,7 @@
         <v>0.71</v>
       </c>
       <c r="V113">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W113">
         <v>1</v>
@@ -15596,7 +15596,7 @@
         <v>129.9</v>
       </c>
       <c r="S114">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T114">
         <v>96.1</v>
@@ -15605,7 +15605,7 @@
         <v>0.71</v>
       </c>
       <c r="V114">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W114">
         <v>1</v>
@@ -15682,7 +15682,7 @@
         <v>124.9</v>
       </c>
       <c r="S115">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T115">
         <v>96.1</v>
@@ -15691,7 +15691,7 @@
         <v>0.71</v>
       </c>
       <c r="V115">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W115">
         <v>1</v>
@@ -15768,7 +15768,7 @@
         <v>277.4</v>
       </c>
       <c r="S116">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T116">
         <v>96.1</v>
@@ -15777,7 +15777,7 @@
         <v>0.71</v>
       </c>
       <c r="V116">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W116">
         <v>1</v>
@@ -15854,7 +15854,7 @@
         <v>252.5</v>
       </c>
       <c r="S117">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="T117">
         <v>96.1</v>
@@ -15863,7 +15863,7 @@
         <v>0.71</v>
       </c>
       <c r="V117">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="W117">
         <v>1</v>
@@ -15940,16 +15940,16 @@
         <v>265.3</v>
       </c>
       <c r="S118">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T118">
         <v>81.9</v>
       </c>
       <c r="U118">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V118">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W118">
         <v>1</v>
@@ -16026,16 +16026,16 @@
         <v>130.3</v>
       </c>
       <c r="S119">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T119">
         <v>81.9</v>
       </c>
       <c r="U119">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V119">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W119">
         <v>1</v>
@@ -16112,16 +16112,16 @@
         <v>245.3</v>
       </c>
       <c r="S120">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T120">
         <v>81.9</v>
       </c>
       <c r="U120">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V120">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W120">
         <v>1</v>
@@ -16198,16 +16198,16 @@
         <v>252.8</v>
       </c>
       <c r="S121">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T121">
         <v>81.9</v>
       </c>
       <c r="U121">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V121">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W121">
         <v>1</v>
@@ -16284,16 +16284,16 @@
         <v>100.3</v>
       </c>
       <c r="S122">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T122">
         <v>81.9</v>
       </c>
       <c r="U122">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V122">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W122">
         <v>1</v>
@@ -16370,16 +16370,16 @@
         <v>175.3</v>
       </c>
       <c r="S123">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T123">
         <v>81.9</v>
       </c>
       <c r="U123">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V123">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W123">
         <v>1</v>
@@ -16456,16 +16456,16 @@
         <v>355.3</v>
       </c>
       <c r="S124">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T124">
         <v>81.9</v>
       </c>
       <c r="U124">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V124">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W124">
         <v>1</v>
@@ -16542,16 +16542,16 @@
         <v>190.3</v>
       </c>
       <c r="S125">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T125">
         <v>81.9</v>
       </c>
       <c r="U125">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V125">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W125">
         <v>1</v>
@@ -16628,16 +16628,16 @@
         <v>10.3</v>
       </c>
       <c r="S126">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T126">
         <v>81.9</v>
       </c>
       <c r="U126">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V126">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W126">
         <v>1</v>
@@ -16714,16 +16714,16 @@
         <v>140.3</v>
       </c>
       <c r="S127">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T127">
         <v>81.9</v>
       </c>
       <c r="U127">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V127">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W127">
         <v>1</v>
@@ -16800,16 +16800,16 @@
         <v>200.3</v>
       </c>
       <c r="S128">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T128">
         <v>81.9</v>
       </c>
       <c r="U128">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V128">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W128">
         <v>1</v>
@@ -16886,16 +16886,16 @@
         <v>245.3</v>
       </c>
       <c r="S129">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T129">
         <v>81.9</v>
       </c>
       <c r="U129">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V129">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W129">
         <v>1</v>
@@ -16972,16 +16972,16 @@
         <v>252.3</v>
       </c>
       <c r="S130">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T130">
         <v>81.9</v>
       </c>
       <c r="U130">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V130">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W130">
         <v>1</v>
@@ -17058,16 +17058,16 @@
         <v>190.3</v>
       </c>
       <c r="S131">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T131">
         <v>81.9</v>
       </c>
       <c r="U131">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V131">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W131">
         <v>1</v>
@@ -17144,16 +17144,16 @@
         <v>190.3</v>
       </c>
       <c r="S132">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T132">
         <v>81.9</v>
       </c>
       <c r="U132">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V132">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W132">
         <v>1</v>
@@ -17230,16 +17230,16 @@
         <v>140.4</v>
       </c>
       <c r="S133">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T133">
         <v>81.9</v>
       </c>
       <c r="U133">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V133">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W133">
         <v>1</v>
@@ -17316,16 +17316,16 @@
         <v>350.3</v>
       </c>
       <c r="S134">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T134">
         <v>81.9</v>
       </c>
       <c r="U134">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V134">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W134">
         <v>1</v>
@@ -17402,16 +17402,16 @@
         <v>107.8</v>
       </c>
       <c r="S135">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T135">
         <v>81.9</v>
       </c>
       <c r="U135">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V135">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W135">
         <v>1</v>
@@ -17488,16 +17488,16 @@
         <v>120.3</v>
       </c>
       <c r="S136">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T136">
         <v>81.9</v>
       </c>
       <c r="U136">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V136">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W136">
         <v>1</v>
@@ -17574,16 +17574,16 @@
         <v>125.3</v>
       </c>
       <c r="S137">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T137">
         <v>81.9</v>
       </c>
       <c r="U137">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V137">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W137">
         <v>1</v>
@@ -17660,16 +17660,16 @@
         <v>190.3</v>
       </c>
       <c r="S138">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T138">
         <v>81.9</v>
       </c>
       <c r="U138">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V138">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W138">
         <v>1</v>
@@ -17746,16 +17746,16 @@
         <v>255.3</v>
       </c>
       <c r="S139">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T139">
         <v>81.9</v>
       </c>
       <c r="U139">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V139">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W139">
         <v>1</v>
@@ -17832,16 +17832,16 @@
         <v>240.3</v>
       </c>
       <c r="S140">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T140">
         <v>81.9</v>
       </c>
       <c r="U140">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V140">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W140">
         <v>1</v>
@@ -17918,16 +17918,16 @@
         <v>260.3</v>
       </c>
       <c r="S141">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T141">
         <v>81.9</v>
       </c>
       <c r="U141">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V141">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W141">
         <v>1</v>
@@ -18004,16 +18004,16 @@
         <v>5.3</v>
       </c>
       <c r="S142">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T142">
         <v>81.9</v>
       </c>
       <c r="U142">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V142">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W142">
         <v>1</v>
@@ -18090,16 +18090,16 @@
         <v>135.3</v>
       </c>
       <c r="S143">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T143">
         <v>81.9</v>
       </c>
       <c r="U143">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V143">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W143">
         <v>1</v>
@@ -18176,16 +18176,16 @@
         <v>240.3</v>
       </c>
       <c r="S144">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="T144">
         <v>81.9</v>
       </c>
       <c r="U144">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="V144">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W144">
         <v>1</v>
@@ -18262,16 +18262,16 @@
         <v>185</v>
       </c>
       <c r="S145">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T145">
         <v>81.9</v>
       </c>
       <c r="U145">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V145">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W145">
         <v>1</v>
@@ -18348,16 +18348,16 @@
         <v>35</v>
       </c>
       <c r="S146">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T146">
         <v>81.9</v>
       </c>
       <c r="U146">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V146">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W146">
         <v>1</v>
@@ -18434,16 +18434,16 @@
         <v>65</v>
       </c>
       <c r="S147">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T147">
         <v>81.9</v>
       </c>
       <c r="U147">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V147">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W147">
         <v>1</v>
@@ -18520,16 +18520,16 @@
         <v>185</v>
       </c>
       <c r="S148">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T148">
         <v>81.9</v>
       </c>
       <c r="U148">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V148">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W148">
         <v>1</v>
@@ -18606,16 +18606,16 @@
         <v>245</v>
       </c>
       <c r="S149">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T149">
         <v>81.9</v>
       </c>
       <c r="U149">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V149">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W149">
         <v>1</v>
@@ -18692,16 +18692,16 @@
         <v>15</v>
       </c>
       <c r="S150">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T150">
         <v>81.9</v>
       </c>
       <c r="U150">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V150">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W150">
         <v>1</v>
@@ -18778,16 +18778,16 @@
         <v>5</v>
       </c>
       <c r="S151">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T151">
         <v>81.9</v>
       </c>
       <c r="U151">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V151">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W151">
         <v>1</v>
@@ -18864,16 +18864,16 @@
         <v>215</v>
       </c>
       <c r="S152">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T152">
         <v>81.9</v>
       </c>
       <c r="U152">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V152">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W152">
         <v>1</v>
@@ -18950,16 +18950,16 @@
         <v>170</v>
       </c>
       <c r="S153">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T153">
         <v>81.9</v>
       </c>
       <c r="U153">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V153">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W153">
         <v>1</v>
@@ -19036,16 +19036,16 @@
         <v>40</v>
       </c>
       <c r="S154">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T154">
         <v>81.9</v>
       </c>
       <c r="U154">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V154">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W154">
         <v>1</v>
@@ -19122,16 +19122,16 @@
         <v>35</v>
       </c>
       <c r="S155">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T155">
         <v>81.9</v>
       </c>
       <c r="U155">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V155">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W155">
         <v>1</v>
@@ -19208,16 +19208,16 @@
         <v>215</v>
       </c>
       <c r="S156">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T156">
         <v>81.9</v>
       </c>
       <c r="U156">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V156">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W156">
         <v>1</v>
@@ -19294,16 +19294,16 @@
         <v>50</v>
       </c>
       <c r="S157">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T157">
         <v>81.9</v>
       </c>
       <c r="U157">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V157">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W157">
         <v>1</v>
@@ -19380,16 +19380,16 @@
         <v>70</v>
       </c>
       <c r="S158">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T158">
         <v>81.9</v>
       </c>
       <c r="U158">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V158">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W158">
         <v>1</v>
@@ -19466,16 +19466,16 @@
         <v>30</v>
       </c>
       <c r="S159">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T159">
         <v>81.9</v>
       </c>
       <c r="U159">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V159">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W159">
         <v>1</v>
@@ -19552,16 +19552,16 @@
         <v>205</v>
       </c>
       <c r="S160">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T160">
         <v>81.9</v>
       </c>
       <c r="U160">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V160">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W160">
         <v>1</v>
@@ -19638,16 +19638,16 @@
         <v>245</v>
       </c>
       <c r="S161">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T161">
         <v>81.9</v>
       </c>
       <c r="U161">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V161">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W161">
         <v>1</v>
@@ -19724,16 +19724,16 @@
         <v>60</v>
       </c>
       <c r="S162">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T162">
         <v>81.9</v>
       </c>
       <c r="U162">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V162">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W162">
         <v>1</v>
@@ -19810,16 +19810,16 @@
         <v>170</v>
       </c>
       <c r="S163">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T163">
         <v>81.9</v>
       </c>
       <c r="U163">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V163">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W163">
         <v>1</v>
@@ -19896,16 +19896,16 @@
         <v>30</v>
       </c>
       <c r="S164">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T164">
         <v>81.9</v>
       </c>
       <c r="U164">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V164">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W164">
         <v>1</v>
@@ -19982,16 +19982,16 @@
         <v>225</v>
       </c>
       <c r="S165">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T165">
         <v>81.9</v>
       </c>
       <c r="U165">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V165">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W165">
         <v>1</v>
@@ -20068,16 +20068,16 @@
         <v>235</v>
       </c>
       <c r="S166">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T166">
         <v>81.9</v>
       </c>
       <c r="U166">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V166">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W166">
         <v>1</v>
@@ -20154,16 +20154,16 @@
         <v>50</v>
       </c>
       <c r="S167">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T167">
         <v>81.9</v>
       </c>
       <c r="U167">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V167">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W167">
         <v>1</v>
@@ -20240,16 +20240,16 @@
         <v>60</v>
       </c>
       <c r="S168">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T168">
         <v>81.9</v>
       </c>
       <c r="U168">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V168">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W168">
         <v>1</v>
@@ -20326,16 +20326,16 @@
         <v>10</v>
       </c>
       <c r="S169">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T169">
         <v>81.9</v>
       </c>
       <c r="U169">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V169">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W169">
         <v>1</v>
@@ -20412,16 +20412,16 @@
         <v>185</v>
       </c>
       <c r="S170">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T170">
         <v>81.9</v>
       </c>
       <c r="U170">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V170">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W170">
         <v>1</v>
@@ -20498,16 +20498,16 @@
         <v>200</v>
       </c>
       <c r="S171">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T171">
         <v>81.9</v>
       </c>
       <c r="U171">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V171">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W171">
         <v>1</v>
@@ -20584,16 +20584,16 @@
         <v>40</v>
       </c>
       <c r="S172">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T172">
         <v>81.9</v>
       </c>
       <c r="U172">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V172">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W172">
         <v>1</v>
@@ -20670,16 +20670,16 @@
         <v>5</v>
       </c>
       <c r="S173">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T173">
         <v>81.9</v>
       </c>
       <c r="U173">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V173">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W173">
         <v>1</v>
@@ -20756,16 +20756,16 @@
         <v>180</v>
       </c>
       <c r="S174">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T174">
         <v>81.9</v>
       </c>
       <c r="U174">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V174">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W174">
         <v>1</v>
@@ -20842,16 +20842,16 @@
         <v>20</v>
       </c>
       <c r="S175">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T175">
         <v>81.9</v>
       </c>
       <c r="U175">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V175">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W175">
         <v>1</v>
@@ -20928,16 +20928,16 @@
         <v>235</v>
       </c>
       <c r="S176">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T176">
         <v>81.9</v>
       </c>
       <c r="U176">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V176">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W176">
         <v>1</v>
@@ -21014,16 +21014,16 @@
         <v>35</v>
       </c>
       <c r="S177">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T177">
         <v>81.9</v>
       </c>
       <c r="U177">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V177">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W177">
         <v>1</v>
@@ -21100,16 +21100,16 @@
         <v>10</v>
       </c>
       <c r="S178">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T178">
         <v>81.9</v>
       </c>
       <c r="U178">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V178">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W178">
         <v>1</v>
@@ -21186,16 +21186,16 @@
         <v>190</v>
       </c>
       <c r="S179">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T179">
         <v>81.9</v>
       </c>
       <c r="U179">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V179">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W179">
         <v>1</v>
@@ -21272,16 +21272,16 @@
         <v>35</v>
       </c>
       <c r="S180">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T180">
         <v>81.9</v>
       </c>
       <c r="U180">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V180">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W180">
         <v>1</v>
@@ -21358,16 +21358,16 @@
         <v>225</v>
       </c>
       <c r="S181">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T181">
         <v>81.9</v>
       </c>
       <c r="U181">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V181">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W181">
         <v>1</v>
@@ -21444,16 +21444,16 @@
         <v>65</v>
       </c>
       <c r="S182">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T182">
         <v>81.9</v>
       </c>
       <c r="U182">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V182">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W182">
         <v>1</v>
@@ -21530,16 +21530,16 @@
         <v>235</v>
       </c>
       <c r="S183">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T183">
         <v>81.9</v>
       </c>
       <c r="U183">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V183">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W183">
         <v>1</v>
@@ -21616,16 +21616,16 @@
         <v>35</v>
       </c>
       <c r="S184">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T184">
         <v>81.9</v>
       </c>
       <c r="U184">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V184">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W184">
         <v>1</v>
@@ -21702,16 +21702,16 @@
         <v>245</v>
       </c>
       <c r="S185">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T185">
         <v>81.9</v>
       </c>
       <c r="U185">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V185">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W185">
         <v>1</v>
@@ -21788,16 +21788,16 @@
         <v>207.5</v>
       </c>
       <c r="S186">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T186">
         <v>81.9</v>
       </c>
       <c r="U186">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V186">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W186">
         <v>1</v>
@@ -21874,16 +21874,16 @@
         <v>40</v>
       </c>
       <c r="S187">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T187">
         <v>81.9</v>
       </c>
       <c r="U187">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V187">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W187">
         <v>1</v>
@@ -21960,16 +21960,16 @@
         <v>210</v>
       </c>
       <c r="S188">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T188">
         <v>81.9</v>
       </c>
       <c r="U188">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V188">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W188">
         <v>1</v>
@@ -22046,16 +22046,16 @@
         <v>250</v>
       </c>
       <c r="S189">
-        <v>74.8</v>
+        <v>75.4</v>
       </c>
       <c r="T189">
         <v>81.9</v>
       </c>
       <c r="U189">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="V189">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="W189">
         <v>1</v>
@@ -22289,7 +22289,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="E6">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="F6">
         <v>15.3</v>
@@ -22301,7 +22301,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="I6">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="J6">
         <v>15.3</v>
@@ -22325,7 +22325,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q6">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="R6">
         <v>88.1</v>
@@ -22367,13 +22367,13 @@
         <v>103</v>
       </c>
       <c r="AE6">
-        <v>151.1</v>
+        <v>151.3</v>
       </c>
       <c r="AF6">
         <v>231.6</v>
       </c>
       <c r="AG6">
-        <v>5.69</v>
+        <v>5.72</v>
       </c>
       <c r="AH6">
         <v>0.86</v>
@@ -22426,7 +22426,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="I7">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
       <c r="J7">
         <v>15.15</v>
@@ -22450,7 +22450,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q7">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="R7">
         <v>76.4</v>
@@ -22492,13 +22492,13 @@
         <v>80.3</v>
       </c>
       <c r="AE7">
-        <v>114.7</v>
+        <v>114.8</v>
       </c>
       <c r="AF7">
         <v>176</v>
       </c>
       <c r="AG7">
-        <v>7.34</v>
+        <v>7.36</v>
       </c>
       <c r="AH7">
         <v>0.95</v>
@@ -22539,7 +22539,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="E8">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F8">
         <v>15.66</v>
@@ -22551,7 +22551,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="I8">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
       <c r="J8">
         <v>15.68</v>
@@ -22575,7 +22575,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q8">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="R8">
         <v>83.5</v>
@@ -22617,13 +22617,13 @@
         <v>88.7</v>
       </c>
       <c r="AE8">
-        <v>136.4</v>
+        <v>136.5</v>
       </c>
       <c r="AF8">
         <v>205.9</v>
       </c>
       <c r="AG8">
-        <v>7.06</v>
+        <v>7.07</v>
       </c>
       <c r="AH8">
         <v>0.94</v>
@@ -22664,7 +22664,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="E9">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="F9">
         <v>16.16</v>
@@ -22676,7 +22676,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="I9">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="J9">
         <v>16.16</v>
@@ -22700,7 +22700,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="R9">
         <v>82.8</v>
@@ -22742,19 +22742,19 @@
         <v>92.4</v>
       </c>
       <c r="AE9">
-        <v>127.6</v>
+        <v>127.8</v>
       </c>
       <c r="AF9">
         <v>196.3</v>
       </c>
       <c r="AG9">
-        <v>6.41</v>
+        <v>6.43</v>
       </c>
       <c r="AH9">
         <v>0.9</v>
       </c>
       <c r="AI9">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AJ9">
         <v>0.98</v>
@@ -22825,10 +22825,10 @@
         <v>B1-D27 căng (MN cao)</v>
       </c>
       <c r="Q10">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="R10">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="S10">
         <v>3.5</v>
@@ -22867,13 +22867,13 @@
         <v>97.8</v>
       </c>
       <c r="AE10">
-        <v>146.9</v>
+        <v>146.8</v>
       </c>
       <c r="AF10">
         <v>239.5</v>
       </c>
       <c r="AG10">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="AH10">
         <v>0.69</v>
@@ -22914,7 +22914,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="E11">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="F11">
         <v>15.02</v>
@@ -22926,7 +22926,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="I11">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="J11">
         <v>15.02</v>
@@ -22950,10 +22950,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q11">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="R11">
-        <v>76.4</v>
+        <v>76.5</v>
       </c>
       <c r="S11">
         <v>3</v>
@@ -22992,13 +22992,13 @@
         <v>80.3</v>
       </c>
       <c r="AE11">
-        <v>114.7</v>
+        <v>114.8</v>
       </c>
       <c r="AF11">
         <v>176</v>
       </c>
       <c r="AG11">
-        <v>7.34</v>
+        <v>7.35</v>
       </c>
       <c r="AH11">
         <v>0.95</v>
@@ -23039,7 +23039,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="E12">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="F12">
         <v>15.67</v>
@@ -23051,7 +23051,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="I12">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="J12">
         <v>15.67</v>
@@ -23075,10 +23075,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R12">
-        <v>80.8</v>
+        <v>80.9</v>
       </c>
       <c r="S12">
         <v>3.25</v>
@@ -23117,25 +23117,25 @@
         <v>88.7</v>
       </c>
       <c r="AE12">
-        <v>133.1</v>
+        <v>133.2</v>
       </c>
       <c r="AF12">
         <v>205.9</v>
       </c>
       <c r="AG12">
-        <v>6.52</v>
+        <v>6.54</v>
       </c>
       <c r="AH12">
         <v>0.91</v>
       </c>
       <c r="AI12">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AJ12">
         <v>0.97</v>
       </c>
       <c r="AK12">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AL12">
         <v>0.15</v>
@@ -23176,7 +23176,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="I13">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="J13">
         <v>15.01</v>
@@ -23200,10 +23200,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q13">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="R13">
-        <v>76.8</v>
+        <v>76.9</v>
       </c>
       <c r="S13">
         <v>3</v>
@@ -23242,19 +23242,19 @@
         <v>80.3</v>
       </c>
       <c r="AE13">
-        <v>116.2</v>
+        <v>116.3</v>
       </c>
       <c r="AF13">
         <v>176</v>
       </c>
       <c r="AG13">
-        <v>7.6</v>
+        <v>7.61</v>
       </c>
       <c r="AH13">
         <v>0.96</v>
       </c>
       <c r="AI13">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AJ13">
         <v>0.99</v>
@@ -23289,7 +23289,7 @@
         <v>BÈ 1</v>
       </c>
       <c r="E14">
-        <v>85.5</v>
+        <v>85.4</v>
       </c>
       <c r="F14">
         <v>17.51</v>
@@ -23328,7 +23328,7 @@
         <v>52.8</v>
       </c>
       <c r="R14">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="S14">
         <v>3.5</v>
@@ -23367,13 +23367,13 @@
         <v>97.8</v>
       </c>
       <c r="AE14">
-        <v>146.8</v>
+        <v>146.6</v>
       </c>
       <c r="AF14">
         <v>239.5</v>
       </c>
       <c r="AG14">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="AH14">
         <v>0.69</v>
@@ -23414,7 +23414,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="E15">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="F15">
         <v>15.96</v>
@@ -23426,7 +23426,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="I15">
-        <v>82.6</v>
+        <v>82.8</v>
       </c>
       <c r="J15">
         <v>15.25</v>
@@ -23450,10 +23450,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q15">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="R15">
-        <v>102.4</v>
+        <v>102.6</v>
       </c>
       <c r="S15">
         <v>3.75</v>
@@ -23492,13 +23492,13 @@
         <v>126.6</v>
       </c>
       <c r="AE15">
-        <v>209</v>
+        <v>209.4</v>
       </c>
       <c r="AF15">
         <v>316.5</v>
       </c>
       <c r="AG15">
-        <v>4.31</v>
+        <v>4.37</v>
       </c>
       <c r="AH15">
         <v>0.81</v>
@@ -23510,7 +23510,7 @@
         <v>0.99</v>
       </c>
       <c r="AK15">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="AL15">
         <v>0.18</v>
@@ -23539,7 +23539,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="E16">
-        <v>71.1</v>
+        <v>71.2</v>
       </c>
       <c r="F16">
         <v>8.41</v>
@@ -23551,7 +23551,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="I16">
-        <v>57.9</v>
+        <v>58</v>
       </c>
       <c r="J16">
         <v>16.43</v>
@@ -23578,7 +23578,7 @@
         <v>42.8</v>
       </c>
       <c r="R16">
-        <v>113.1</v>
+        <v>113.3</v>
       </c>
       <c r="S16">
         <v>4.75</v>
@@ -23617,19 +23617,19 @@
         <v>153.5</v>
       </c>
       <c r="AE16">
-        <v>292</v>
+        <v>292.6</v>
       </c>
       <c r="AF16">
         <v>471.9</v>
       </c>
       <c r="AG16">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="AH16">
         <v>0.74</v>
       </c>
       <c r="AI16">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="AJ16">
         <v>0.93</v>
@@ -23700,7 +23700,7 @@
         <v>B2-D23 căng (MN cao)</v>
       </c>
       <c r="Q17">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="R17">
         <v>24</v>
@@ -23742,7 +23742,7 @@
         <v>65.4</v>
       </c>
       <c r="AE17">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="AF17">
         <v>126</v>
@@ -23789,7 +23789,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="E18">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="F18">
         <v>8.34</v>
@@ -23801,7 +23801,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="I18">
-        <v>68.4</v>
+        <v>67.5</v>
       </c>
       <c r="J18">
         <v>8.35</v>
@@ -23825,10 +23825,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R18">
-        <v>133.8</v>
+        <v>133.1</v>
       </c>
       <c r="S18">
         <v>4</v>
@@ -23867,13 +23867,13 @@
         <v>161.3</v>
       </c>
       <c r="AE18">
-        <v>270</v>
+        <v>268.8</v>
       </c>
       <c r="AF18">
         <v>414.7</v>
       </c>
       <c r="AG18">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH18">
         <v>0.83</v>
@@ -23882,10 +23882,10 @@
         <v>0.44</v>
       </c>
       <c r="AJ18">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AK18">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="AL18">
         <v>0.22</v>
@@ -23914,7 +23914,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="E19">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="F19">
         <v>12.9</v>
@@ -23926,7 +23926,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="I19">
-        <v>78.4</v>
+        <v>78.6</v>
       </c>
       <c r="J19">
         <v>12.9</v>
@@ -23950,10 +23950,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q19">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="R19">
-        <v>116.6</v>
+        <v>116.8</v>
       </c>
       <c r="S19">
         <v>4</v>
@@ -23992,25 +23992,25 @@
         <v>139.7</v>
       </c>
       <c r="AE19">
-        <v>240.4</v>
+        <v>240.9</v>
       </c>
       <c r="AF19">
         <v>366.7</v>
       </c>
       <c r="AG19">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="AH19">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AI19">
         <v>0.44</v>
       </c>
       <c r="AJ19">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AK19">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="AL19">
         <v>0.18</v>
@@ -24075,7 +24075,7 @@
         <v>B2-D34 căng (MN cao)</v>
       </c>
       <c r="Q20">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="R20">
         <v>24</v>
@@ -24117,7 +24117,7 @@
         <v>65.4</v>
       </c>
       <c r="AE20">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="AF20">
         <v>126</v>
@@ -24176,7 +24176,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="I21">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="J21">
         <v>14.29</v>
@@ -24200,10 +24200,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q21">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="R21">
-        <v>77.3</v>
+        <v>77.5</v>
       </c>
       <c r="S21">
         <v>3.5</v>
@@ -24242,13 +24242,13 @@
         <v>97.8</v>
       </c>
       <c r="AE21">
-        <v>153</v>
+        <v>153.2</v>
       </c>
       <c r="AF21">
         <v>239.5</v>
       </c>
       <c r="AG21">
-        <v>5.55</v>
+        <v>5.59</v>
       </c>
       <c r="AH21">
         <v>0.79</v>
@@ -24260,7 +24260,7 @@
         <v>0.96</v>
       </c>
       <c r="AK21">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AL21">
         <v>0.15</v>
@@ -24289,7 +24289,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="E22">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="F22">
         <v>23.35</v>
@@ -24301,7 +24301,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="I22">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="J22">
         <v>14.25</v>
@@ -24325,10 +24325,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q22">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="R22">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="S22">
         <v>3</v>
@@ -24367,13 +24367,13 @@
         <v>80.3</v>
       </c>
       <c r="AE22">
-        <v>108</v>
+        <v>108.2</v>
       </c>
       <c r="AF22">
         <v>176</v>
       </c>
       <c r="AG22">
-        <v>6.16</v>
+        <v>6.19</v>
       </c>
       <c r="AH22">
         <v>0.74</v>
@@ -24414,7 +24414,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="E23">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="F23">
         <v>9.52</v>
@@ -24426,7 +24426,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="I23">
-        <v>77.6</v>
+        <v>76.5</v>
       </c>
       <c r="J23">
         <v>9.52</v>
@@ -24450,10 +24450,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q23">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="R23">
-        <v>117.6</v>
+        <v>116.7</v>
       </c>
       <c r="S23">
         <v>4</v>
@@ -24492,25 +24492,25 @@
         <v>139.7</v>
       </c>
       <c r="AE23">
-        <v>241.9</v>
+        <v>239.8</v>
       </c>
       <c r="AF23">
         <v>366.7</v>
       </c>
       <c r="AG23">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="AH23">
         <v>0.84</v>
       </c>
       <c r="AI23">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AJ23">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="AK23">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="AL23">
         <v>0.18</v>
@@ -24539,7 +24539,7 @@
         <v>BÈ 2</v>
       </c>
       <c r="E24">
-        <v>79.2</v>
+        <v>79.4</v>
       </c>
       <c r="F24">
         <v>11.47</v>
@@ -24551,7 +24551,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="I24">
-        <v>72.1</v>
+        <v>72.2</v>
       </c>
       <c r="J24">
         <v>11.47</v>
@@ -24578,7 +24578,7 @@
         <v>3.3</v>
       </c>
       <c r="R24">
-        <v>134.1</v>
+        <v>134.4</v>
       </c>
       <c r="S24">
         <v>4</v>
@@ -24617,13 +24617,13 @@
         <v>161.3</v>
       </c>
       <c r="AE24">
-        <v>270.8</v>
+        <v>271.3</v>
       </c>
       <c r="AF24">
         <v>414.7</v>
       </c>
       <c r="AG24">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH24">
         <v>0.83</v>
@@ -24635,7 +24635,7 @@
         <v>0.98</v>
       </c>
       <c r="AK24">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="AL24">
         <v>0.22</v>
@@ -24664,7 +24664,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="E25">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="F25">
         <v>17.5</v>
@@ -24700,10 +24700,10 @@
         <v>B3-D16 căng (MN cao)</v>
       </c>
       <c r="Q25">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="R25">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="S25">
         <v>2.5</v>
@@ -24742,7 +24742,7 @@
         <v>65.4</v>
       </c>
       <c r="AE25">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="AF25">
         <v>126</v>
@@ -24751,7 +24751,7 @@
         <v>0</v>
       </c>
       <c r="AH25">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="AI25">
         <v>0.33</v>
@@ -24789,7 +24789,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="E26">
-        <v>54.6</v>
+        <v>53.8</v>
       </c>
       <c r="F26">
         <v>17.5</v>
@@ -24825,10 +24825,10 @@
         <v>B3-D18 căng (MN cao)</v>
       </c>
       <c r="Q26">
-        <v>38.8</v>
+        <v>38.3</v>
       </c>
       <c r="R26">
-        <v>38.4</v>
+        <v>37.8</v>
       </c>
       <c r="S26">
         <v>2.5</v>
@@ -24867,25 +24867,25 @@
         <v>65.4</v>
       </c>
       <c r="AE26">
-        <v>69.3</v>
+        <v>68.3</v>
       </c>
       <c r="AF26">
         <v>126</v>
       </c>
       <c r="AG26">
-        <v>5.77</v>
+        <v>5.55</v>
       </c>
       <c r="AH26">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="AI26">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="AJ26">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="AK26">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AL26">
         <v>0.15</v>
@@ -24914,7 +24914,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="E27">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="F27">
         <v>28.75</v>
@@ -24926,7 +24926,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="I27">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="J27">
         <v>28.76</v>
@@ -24950,7 +24950,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q27">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="R27">
         <v>47.1</v>
@@ -24992,13 +24992,13 @@
         <v>65.4</v>
       </c>
       <c r="AE27">
-        <v>59</v>
+        <v>58.9</v>
       </c>
       <c r="AF27">
         <v>126</v>
       </c>
       <c r="AG27">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="AH27">
         <v>0.72</v>
@@ -25039,7 +25039,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="E28">
-        <v>61.5</v>
+        <v>61.6</v>
       </c>
       <c r="F28">
         <v>15.56</v>
@@ -25051,7 +25051,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="I28">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="J28">
         <v>15.57</v>
@@ -25075,34 +25075,34 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q28">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="R28">
-        <v>93.3</v>
+        <v>93.1</v>
       </c>
       <c r="S28">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T28">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="U28">
-        <v>5.26</v>
+        <v>5.37</v>
       </c>
       <c r="V28">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="W28">
-        <v>79.2</v>
+        <v>81</v>
       </c>
       <c r="X28">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="Y28" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="Z28">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="AA28">
         <v>4</v>
@@ -25111,37 +25111,37 @@
         <v>Ø89×5</v>
       </c>
       <c r="AC28">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD28">
-        <v>103</v>
+        <v>104.6</v>
       </c>
       <c r="AE28">
-        <v>154.4</v>
+        <v>143.1</v>
       </c>
       <c r="AF28">
-        <v>231.6</v>
+        <v>216.5</v>
       </c>
       <c r="AG28">
-        <v>6.22</v>
+        <v>5.91</v>
       </c>
       <c r="AH28">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="AI28">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AJ28">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="AK28">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="AL28">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="AM28">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AN28" t="str">
         <v>ĐẠT</v>
@@ -25176,7 +25176,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="I29">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="J29">
         <v>22.12</v>
@@ -25200,10 +25200,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q29">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="R29">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="S29">
         <v>2.5</v>
@@ -25248,7 +25248,7 @@
         <v>126</v>
       </c>
       <c r="AG29">
-        <v>7.32</v>
+        <v>7.33</v>
       </c>
       <c r="AH29">
         <v>0.93</v>
@@ -25260,7 +25260,7 @@
         <v>0.91</v>
       </c>
       <c r="AK29">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AL29">
         <v>0.15</v>
@@ -25289,7 +25289,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="E30">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="F30">
         <v>25.35</v>
@@ -25301,7 +25301,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="I30">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="J30">
         <v>25.37</v>
@@ -25325,7 +25325,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R30">
         <v>53.5</v>
@@ -25373,13 +25373,13 @@
         <v>126</v>
       </c>
       <c r="AG30">
-        <v>5.25</v>
+        <v>5.26</v>
       </c>
       <c r="AH30">
         <v>0.82</v>
       </c>
       <c r="AI30">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="AJ30">
         <v>0.8</v>
@@ -25414,7 +25414,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="E31">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="F31">
         <v>13</v>
@@ -25426,7 +25426,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="I31">
-        <v>57.5</v>
+        <v>57.3</v>
       </c>
       <c r="J31">
         <v>13.07</v>
@@ -25450,10 +25450,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q31">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="R31">
-        <v>74.9</v>
+        <v>74.8</v>
       </c>
       <c r="S31">
         <v>3.25</v>
@@ -25492,13 +25492,13 @@
         <v>88.7</v>
       </c>
       <c r="AE31">
-        <v>130.8</v>
+        <v>130.6</v>
       </c>
       <c r="AF31">
         <v>205.9</v>
       </c>
       <c r="AG31">
-        <v>6.15</v>
+        <v>6.12</v>
       </c>
       <c r="AH31">
         <v>0.84</v>
@@ -25510,7 +25510,7 @@
         <v>0.95</v>
       </c>
       <c r="AK31">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="AL31">
         <v>0.15</v>
@@ -25539,7 +25539,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="E32">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="F32">
         <v>19.34</v>
@@ -25551,7 +25551,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="I32">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="J32">
         <v>19.34</v>
@@ -25575,7 +25575,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q32">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R32">
         <v>57.4</v>
@@ -25617,13 +25617,13 @@
         <v>65.4</v>
       </c>
       <c r="AE32">
-        <v>73.3</v>
+        <v>73.2</v>
       </c>
       <c r="AF32">
         <v>126</v>
       </c>
       <c r="AG32">
-        <v>6.63</v>
+        <v>6.6</v>
       </c>
       <c r="AH32">
         <v>0.88</v>
@@ -25635,7 +25635,7 @@
         <v>0.87</v>
       </c>
       <c r="AK32">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AL32">
         <v>0.15</v>
@@ -25664,7 +25664,7 @@
         <v>BÈ 4</v>
       </c>
       <c r="E33">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="F33">
         <v>11.33</v>
@@ -25676,7 +25676,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="I33">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="J33">
         <v>11.34</v>
@@ -25700,7 +25700,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q33">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="R33">
         <v>79.7</v>
@@ -25742,19 +25742,19 @@
         <v>88.7</v>
       </c>
       <c r="AE33">
-        <v>131.9</v>
+        <v>131.7</v>
       </c>
       <c r="AF33">
         <v>205.9</v>
       </c>
       <c r="AG33">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="AH33">
         <v>0.9</v>
       </c>
       <c r="AI33">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="AJ33">
         <v>0.96</v>
@@ -25801,7 +25801,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="I34">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="J34">
         <v>17.64</v>
@@ -25825,7 +25825,7 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q34">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R34">
         <v>58.5</v>
@@ -25867,19 +25867,19 @@
         <v>65.4</v>
       </c>
       <c r="AE34">
-        <v>74.5</v>
+        <v>74.4</v>
       </c>
       <c r="AF34">
         <v>126</v>
       </c>
       <c r="AG34">
-        <v>6.88</v>
+        <v>6.86</v>
       </c>
       <c r="AH34">
         <v>0.89</v>
       </c>
       <c r="AI34">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="AJ34">
         <v>0.89</v>
@@ -25914,7 +25914,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="E35">
-        <v>58</v>
+        <v>57.9</v>
       </c>
       <c r="F35">
         <v>17.49</v>
@@ -25950,10 +25950,10 @@
         <v>B5-D09 căng (MN cao)</v>
       </c>
       <c r="Q35">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="R35">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="S35">
         <v>2.5</v>
@@ -25992,13 +25992,13 @@
         <v>65.4</v>
       </c>
       <c r="AE35">
-        <v>73.9</v>
+        <v>73.7</v>
       </c>
       <c r="AF35">
         <v>126</v>
       </c>
       <c r="AG35">
-        <v>6.74</v>
+        <v>6.69</v>
       </c>
       <c r="AH35">
         <v>0.63</v>
@@ -26039,7 +26039,7 @@
         <v>BÈ 5</v>
       </c>
       <c r="E36">
-        <v>106.2</v>
+        <v>105.9</v>
       </c>
       <c r="F36">
         <v>23.39</v>
@@ -26051,7 +26051,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="I36">
-        <v>150.4</v>
+        <v>152.1</v>
       </c>
       <c r="J36">
         <v>23.4</v>
@@ -26075,10 +26075,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q36">
-        <v>33.3</v>
+        <v>34.8</v>
       </c>
       <c r="R36">
-        <v>168.5</v>
+        <v>169.4</v>
       </c>
       <c r="S36">
         <v>5.25</v>
@@ -26117,7 +26117,7 @@
         <v>217.7</v>
       </c>
       <c r="AE36">
-        <v>464</v>
+        <v>467.4</v>
       </c>
       <c r="AF36">
         <v>708.9</v>
@@ -26126,13 +26126,13 @@
         <v>0</v>
       </c>
       <c r="AH36">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AI36">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="AJ36">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AK36">
         <v>0</v>
@@ -26164,7 +26164,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="E37">
-        <v>109.9</v>
+        <v>110.8</v>
       </c>
       <c r="F37">
         <v>17.51</v>
@@ -26200,10 +26200,10 @@
         <v>B6-D13 căng (MN cao)</v>
       </c>
       <c r="Q37">
-        <v>70.9</v>
+        <v>71.5</v>
       </c>
       <c r="R37">
-        <v>84</v>
+        <v>84.7</v>
       </c>
       <c r="S37">
         <v>4</v>
@@ -26242,25 +26242,25 @@
         <v>118.1</v>
       </c>
       <c r="AE37">
-        <v>206.9</v>
+        <v>208.6</v>
       </c>
       <c r="AF37">
         <v>318.7</v>
       </c>
       <c r="AG37">
-        <v>4.43</v>
+        <v>4.65</v>
       </c>
       <c r="AH37">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="AI37">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="AJ37">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AK37">
-        <v>0.56</v>
+        <v>0.59</v>
       </c>
       <c r="AL37">
         <v>0.15</v>
@@ -26289,7 +26289,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="E38">
-        <v>113.9</v>
+        <v>114.9</v>
       </c>
       <c r="F38">
         <v>17.51</v>
@@ -26325,34 +26325,34 @@
         <v>B6-D25 căng (MN cao)</v>
       </c>
       <c r="Q38">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="R38">
-        <v>85.5</v>
+        <v>86.5</v>
       </c>
       <c r="S38">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="T38">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="U38">
-        <v>7.01</v>
+        <v>7.21</v>
       </c>
       <c r="V38">
-        <v>175.8</v>
+        <v>180.6</v>
       </c>
       <c r="W38">
-        <v>105.5</v>
+        <v>108.4</v>
       </c>
       <c r="X38">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="Y38" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="Z38">
-        <v>259</v>
+        <v>339</v>
       </c>
       <c r="AA38">
         <v>4</v>
@@ -26361,37 +26361,37 @@
         <v>Ø89×5</v>
       </c>
       <c r="AC38">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD38">
-        <v>126.6</v>
+        <v>129.2</v>
       </c>
       <c r="AE38">
-        <v>209.2</v>
+        <v>225.3</v>
       </c>
       <c r="AF38">
-        <v>316.5</v>
+        <v>364.9</v>
       </c>
       <c r="AG38">
-        <v>4.34</v>
+        <v>2.2</v>
       </c>
       <c r="AH38">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="AI38">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="AJ38">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="AK38">
-        <v>0.55</v>
+        <v>0.28</v>
       </c>
       <c r="AL38">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="AM38">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AN38" t="str">
         <v>ĐẠT</v>
@@ -26414,7 +26414,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="E39">
-        <v>64.6</v>
+        <v>64.9</v>
       </c>
       <c r="F39">
         <v>17.49</v>
@@ -26450,10 +26450,10 @@
         <v>B6-D44 căng (MN cao)</v>
       </c>
       <c r="Q39">
-        <v>46.7</v>
+        <v>47</v>
       </c>
       <c r="R39">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="S39">
         <v>2.75</v>
@@ -26492,25 +26492,25 @@
         <v>72.5</v>
       </c>
       <c r="AE39">
-        <v>87</v>
+        <v>87.5</v>
       </c>
       <c r="AF39">
         <v>149.5</v>
       </c>
       <c r="AG39">
-        <v>5.93</v>
+        <v>6.02</v>
       </c>
       <c r="AH39">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="AI39">
         <v>0.64</v>
       </c>
       <c r="AJ39">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AK39">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AL39">
         <v>0.15</v>
@@ -26539,7 +26539,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="E40">
-        <v>109</v>
+        <v>109.7</v>
       </c>
       <c r="F40">
         <v>17.51</v>
@@ -26575,10 +26575,10 @@
         <v>B6-D46 căng (MN cao)</v>
       </c>
       <c r="Q40">
-        <v>69.8</v>
+        <v>70.2</v>
       </c>
       <c r="R40">
-        <v>83.8</v>
+        <v>84.3</v>
       </c>
       <c r="S40">
         <v>4</v>
@@ -26617,13 +26617,13 @@
         <v>118.1</v>
       </c>
       <c r="AE40">
-        <v>205.9</v>
+        <v>207.2</v>
       </c>
       <c r="AF40">
         <v>318.7</v>
       </c>
       <c r="AG40">
-        <v>4.3</v>
+        <v>4.47</v>
       </c>
       <c r="AH40">
         <v>0.71</v>
@@ -26632,10 +26632,10 @@
         <v>0.67</v>
       </c>
       <c r="AJ40">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AK40">
-        <v>0.54</v>
+        <v>0.56</v>
       </c>
       <c r="AL40">
         <v>0.15</v>
@@ -26708,7 +26708,7 @@
         <v/>
       </c>
       <c r="R42">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="S42" t="str">
         <v/>
@@ -26717,7 +26717,7 @@
         <v/>
       </c>
       <c r="U42">
-        <v>173.3</v>
+        <v>173.6</v>
       </c>
       <c r="V42" t="str">
         <v/>
@@ -26732,7 +26732,7 @@
         <v/>
       </c>
       <c r="Z42">
-        <v>7249</v>
+        <v>7292</v>
       </c>
       <c r="AA42">
         <v>140</v>
@@ -26744,7 +26744,7 @@
         <v/>
       </c>
       <c r="AD42">
-        <v>3457</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="43">
@@ -27046,10 +27046,10 @@
         <v>71.3</v>
       </c>
       <c r="E19">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="F19">
-        <v>5.69</v>
+        <v>5.72</v>
       </c>
       <c r="G19">
         <v>7.92</v>
@@ -27078,7 +27078,7 @@
         <v>27.8</v>
       </c>
       <c r="F20">
-        <v>7.34</v>
+        <v>7.36</v>
       </c>
       <c r="G20">
         <v>7.92</v>
@@ -27107,7 +27107,7 @@
         <v>26.5</v>
       </c>
       <c r="F21">
-        <v>7.06</v>
+        <v>7.07</v>
       </c>
       <c r="G21">
         <v>7.92</v>
@@ -27133,10 +27133,10 @@
         <v>60.8</v>
       </c>
       <c r="E22">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="F22">
-        <v>6.41</v>
+        <v>6.43</v>
       </c>
       <c r="G22">
         <v>7.92</v>
@@ -27156,16 +27156,16 @@
         <v>3.5</v>
       </c>
       <c r="C23">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="D23">
         <v>66.2</v>
       </c>
       <c r="E23">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="G23">
         <v>7.92</v>
@@ -27185,16 +27185,16 @@
         <v>3</v>
       </c>
       <c r="C24">
-        <v>76.4</v>
+        <v>76.5</v>
       </c>
       <c r="D24">
         <v>48.6</v>
       </c>
       <c r="E24">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="F24">
-        <v>7.34</v>
+        <v>7.35</v>
       </c>
       <c r="G24">
         <v>7.92</v>
@@ -27214,7 +27214,7 @@
         <v>3.25</v>
       </c>
       <c r="C25">
-        <v>80.8</v>
+        <v>80.9</v>
       </c>
       <c r="D25">
         <v>57</v>
@@ -27223,13 +27223,13 @@
         <v>23.8</v>
       </c>
       <c r="F25">
-        <v>6.52</v>
+        <v>6.54</v>
       </c>
       <c r="G25">
         <v>7.92</v>
       </c>
       <c r="H25">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="I25" t="str">
         <v>ĐẠT</v>
@@ -27243,16 +27243,16 @@
         <v>3</v>
       </c>
       <c r="C26">
-        <v>76.8</v>
+        <v>76.9</v>
       </c>
       <c r="D26">
         <v>48.6</v>
       </c>
       <c r="E26">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="F26">
-        <v>7.6</v>
+        <v>7.61</v>
       </c>
       <c r="G26">
         <v>7.92</v>
@@ -27272,7 +27272,7 @@
         <v>3.5</v>
       </c>
       <c r="C27">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="D27">
         <v>66.2</v>
@@ -27281,7 +27281,7 @@
         <v>1.1</v>
       </c>
       <c r="F27">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="G27">
         <v>7.92</v>
@@ -27301,22 +27301,22 @@
         <v>3.75</v>
       </c>
       <c r="C28">
-        <v>102.4</v>
+        <v>102.6</v>
       </c>
       <c r="D28">
         <v>94.9</v>
       </c>
       <c r="E28">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="F28">
-        <v>4.31</v>
+        <v>4.37</v>
       </c>
       <c r="G28">
         <v>7.92</v>
       </c>
       <c r="H28">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="I28" t="str">
         <v>ĐẠT</v>
@@ -27330,7 +27330,7 @@
         <v>4.75</v>
       </c>
       <c r="C29">
-        <v>113.1</v>
+        <v>113.3</v>
       </c>
       <c r="D29">
         <v>121.8</v>
@@ -27339,7 +27339,7 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="G29">
         <v>7.92</v>
@@ -27388,22 +27388,22 @@
         <v>4</v>
       </c>
       <c r="C31">
-        <v>133.8</v>
+        <v>133.1</v>
       </c>
       <c r="D31">
         <v>129.6</v>
       </c>
       <c r="E31">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="F31">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="G31">
         <v>7.92</v>
       </c>
       <c r="H31">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="I31" t="str">
         <v>ĐẠT</v>
@@ -27417,22 +27417,22 @@
         <v>4</v>
       </c>
       <c r="C32">
-        <v>116.6</v>
+        <v>116.8</v>
       </c>
       <c r="D32">
         <v>108</v>
       </c>
       <c r="E32">
-        <v>8.6</v>
+        <v>8.8</v>
       </c>
       <c r="F32">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="G32">
         <v>7.92</v>
       </c>
       <c r="H32">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="I32" t="str">
         <v>ĐẠT</v>
@@ -27475,22 +27475,22 @@
         <v>3.5</v>
       </c>
       <c r="C34">
-        <v>77.3</v>
+        <v>77.5</v>
       </c>
       <c r="D34">
         <v>66.2</v>
       </c>
       <c r="E34">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="F34">
-        <v>5.55</v>
+        <v>5.59</v>
       </c>
       <c r="G34">
         <v>7.92</v>
       </c>
       <c r="H34">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="I34" t="str">
         <v>ĐẠT</v>
@@ -27504,16 +27504,16 @@
         <v>3</v>
       </c>
       <c r="C35">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="D35">
         <v>48.6</v>
       </c>
       <c r="E35">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F35">
-        <v>6.16</v>
+        <v>6.19</v>
       </c>
       <c r="G35">
         <v>7.92</v>
@@ -27533,22 +27533,22 @@
         <v>4</v>
       </c>
       <c r="C36">
-        <v>117.6</v>
+        <v>116.7</v>
       </c>
       <c r="D36">
         <v>108</v>
       </c>
       <c r="E36">
-        <v>9.6</v>
+        <v>8.7</v>
       </c>
       <c r="F36">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="G36">
         <v>7.92</v>
       </c>
       <c r="H36">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="I36" t="str">
         <v>ĐẠT</v>
@@ -27562,22 +27562,22 @@
         <v>4</v>
       </c>
       <c r="C37">
-        <v>134.1</v>
+        <v>134.4</v>
       </c>
       <c r="D37">
         <v>129.6</v>
       </c>
       <c r="E37">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="F37">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G37">
         <v>7.92</v>
       </c>
       <c r="H37">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="I37" t="str">
         <v>ĐẠT</v>
@@ -27591,7 +27591,7 @@
         <v>2.5</v>
       </c>
       <c r="C38">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="D38">
         <v>33.8</v>
@@ -27620,22 +27620,22 @@
         <v>2.5</v>
       </c>
       <c r="C39">
-        <v>38.4</v>
+        <v>37.8</v>
       </c>
       <c r="D39">
         <v>33.8</v>
       </c>
       <c r="E39">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="F39">
-        <v>5.77</v>
+        <v>5.55</v>
       </c>
       <c r="G39">
         <v>7.92</v>
       </c>
       <c r="H39">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="I39" t="str">
         <v>ĐẠT</v>
@@ -27658,7 +27658,7 @@
         <v>13.3</v>
       </c>
       <c r="F40">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="G40">
         <v>7.92</v>
@@ -27675,25 +27675,25 @@
         <v>BM-DV023</v>
       </c>
       <c r="B41">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>93.3</v>
+        <v>93.1</v>
       </c>
       <c r="D41">
-        <v>71.3</v>
+        <v>72.9</v>
       </c>
       <c r="E41">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="F41">
-        <v>6.22</v>
+        <v>5.91</v>
       </c>
       <c r="G41">
         <v>7.92</v>
       </c>
       <c r="H41">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="I41" t="str">
         <v>ĐẠT</v>
@@ -27707,7 +27707,7 @@
         <v>2.5</v>
       </c>
       <c r="C42">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="D42">
         <v>33.8</v>
@@ -27716,13 +27716,13 @@
         <v>27.1</v>
       </c>
       <c r="F42">
-        <v>7.32</v>
+        <v>7.33</v>
       </c>
       <c r="G42">
         <v>7.92</v>
       </c>
       <c r="H42">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I42" t="str">
         <v>ĐẠT</v>
@@ -27745,7 +27745,7 @@
         <v>19.7</v>
       </c>
       <c r="F43">
-        <v>5.25</v>
+        <v>5.26</v>
       </c>
       <c r="G43">
         <v>7.92</v>
@@ -27765,7 +27765,7 @@
         <v>3.25</v>
       </c>
       <c r="C44">
-        <v>74.9</v>
+        <v>74.8</v>
       </c>
       <c r="D44">
         <v>57</v>
@@ -27774,13 +27774,13 @@
         <v>17.8</v>
       </c>
       <c r="F44">
-        <v>6.15</v>
+        <v>6.12</v>
       </c>
       <c r="G44">
         <v>7.92</v>
       </c>
       <c r="H44">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I44" t="str">
         <v>ĐẠT</v>
@@ -27803,13 +27803,13 @@
         <v>23.7</v>
       </c>
       <c r="F45">
-        <v>6.63</v>
+        <v>6.6</v>
       </c>
       <c r="G45">
         <v>7.92</v>
       </c>
       <c r="H45">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I45" t="str">
         <v>ĐẠT</v>
@@ -27829,10 +27829,10 @@
         <v>57</v>
       </c>
       <c r="E46">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="F46">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="G46">
         <v>7.92</v>
@@ -27861,7 +27861,7 @@
         <v>24.7</v>
       </c>
       <c r="F47">
-        <v>6.88</v>
+        <v>6.86</v>
       </c>
       <c r="G47">
         <v>7.92</v>
@@ -27881,16 +27881,16 @@
         <v>2.5</v>
       </c>
       <c r="C48">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="D48">
         <v>33.8</v>
       </c>
       <c r="E48">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="F48">
-        <v>6.74</v>
+        <v>6.69</v>
       </c>
       <c r="G48">
         <v>7.92</v>
@@ -27910,7 +27910,7 @@
         <v>5.25</v>
       </c>
       <c r="C49">
-        <v>168.5</v>
+        <v>169.4</v>
       </c>
       <c r="D49">
         <v>186</v>
@@ -27939,7 +27939,7 @@
         <v>4</v>
       </c>
       <c r="C50">
-        <v>84</v>
+        <v>84.7</v>
       </c>
       <c r="D50">
         <v>86.4</v>
@@ -27948,13 +27948,13 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>4.43</v>
+        <v>4.65</v>
       </c>
       <c r="G50">
         <v>7.92</v>
       </c>
       <c r="H50">
-        <v>0.56</v>
+        <v>0.59</v>
       </c>
       <c r="I50" t="str">
         <v>ĐẠT</v>
@@ -27965,25 +27965,25 @@
         <v>BM-DV033</v>
       </c>
       <c r="B51">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="C51">
-        <v>85.5</v>
+        <v>86.5</v>
       </c>
       <c r="D51">
-        <v>94.9</v>
+        <v>97.5</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>4.34</v>
+        <v>2.2</v>
       </c>
       <c r="G51">
         <v>7.92</v>
       </c>
       <c r="H51">
-        <v>0.55</v>
+        <v>0.28</v>
       </c>
       <c r="I51" t="str">
         <v>ĐẠT</v>
@@ -27997,22 +27997,22 @@
         <v>2.75</v>
       </c>
       <c r="C52">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="D52">
         <v>40.8</v>
       </c>
       <c r="E52">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="F52">
-        <v>5.93</v>
+        <v>6.02</v>
       </c>
       <c r="G52">
         <v>7.92</v>
       </c>
       <c r="H52">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="I52" t="str">
         <v>ĐẠT</v>
@@ -28026,7 +28026,7 @@
         <v>4</v>
       </c>
       <c r="C53">
-        <v>83.8</v>
+        <v>84.3</v>
       </c>
       <c r="D53">
         <v>86.4</v>
@@ -28035,13 +28035,13 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>4.3</v>
+        <v>4.47</v>
       </c>
       <c r="G53">
         <v>7.92</v>
       </c>
       <c r="H53">
-        <v>0.54</v>
+        <v>0.56</v>
       </c>
       <c r="I53" t="str">
         <v>ĐẠT</v>
@@ -28144,7 +28144,7 @@
         <v>m³</v>
       </c>
       <c r="D7" s="1">
-        <v>173.3</v>
+        <v>173.6</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
@@ -28167,7 +28167,7 @@
         <v>kg</v>
       </c>
       <c r="D8" s="1">
-        <v>7248.6</v>
+        <v>7291.8</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
@@ -28515,10 +28515,10 @@
         <v>34.1</v>
       </c>
       <c r="F29" s="2">
-        <v>1425</v>
+        <v>1407</v>
       </c>
       <c r="G29" s="1">
-        <v>104.6</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="30">
@@ -28535,13 +28535,13 @@
         <v>5.5</v>
       </c>
       <c r="E30" s="1">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="F30" s="2">
-        <v>976</v>
-      </c>
-      <c r="G30" s="1">
-        <v>81.8</v>
+        <v>958</v>
+      </c>
+      <c r="G30" s="2">
+        <v>82</v>
       </c>
     </row>
     <row r="31">
@@ -28558,13 +28558,13 @@
         <v>4.5</v>
       </c>
       <c r="E31" s="1">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
       <c r="F31" s="2">
-        <v>1239</v>
+        <v>1319</v>
       </c>
       <c r="G31" s="1">
-        <v>67.2</v>
+        <v>66.8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/mat-bang-neo-ban-mong/bang_tinh_neo.xlsx
+++ b/docs/mat-bang-neo-ban-mong/bang_tinh_neo.xlsx
@@ -451,7 +451,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">  Hệ neo: 215 tuyến cáp tại 205 điểm neo = 186 cọc khoan nhồi ven bờ + 19 đế đáy hồ (10 đế dùng chung hai bè).</v>
+        <v xml:space="preserve">  Hệ neo: 215 tuyến cáp tại 205 điểm neo = 188 cọc khoan nhồi ven bờ + 17 đế đáy hồ (10 đế dùng chung hai bè).</v>
       </c>
     </row>
     <row r="9">
@@ -466,7 +466,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">  Kết quả: 6/6 bè đạt; 186/186 cọc bờ đạt; 19/19 đế đạt.</v>
+        <v xml:space="preserve">  Kết quả: 6/6 bè đạt; 188/188 cọc bờ đạt; 17/17 đế đạt.</v>
       </c>
     </row>
     <row r="12">
@@ -641,7 +641,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v xml:space="preserve">  Cả hệ: 186 cọc, tổng dài 1.227,6 m, 118,1 m³ bê tông, 36,2 tấn thép. Lực kiểm tra cọc là toàn bộ lực dây (không giảm theo góc xiên), thiên về an toàn.</v>
+        <v xml:space="preserve">  Cả hệ: 188 cọc, tổng dài 1.240,8 m, 119,4 m³ bê tông, 36,6 tấn thép. Lực kiểm tra cọc là toàn bộ lực dây (không giảm theo góc xiên), thiên về an toàn.</v>
       </c>
     </row>
     <row r="47">
@@ -651,7 +651,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>6. Đế BTCT + vít xoắn (ví dụ BM-DV018, đế làm việc nặng nhất)</v>
+        <v>6. Đế BTCT + vít xoắn (ví dụ BM-DV013, đế làm việc nặng nhất)</v>
       </c>
     </row>
     <row r="49">
@@ -661,7 +661,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">  Đế BM-DV018 giữ hai dây B6-D25 (BÈ 6, T = 112,9 kN, dài 17,51 m). Bích bè cao hơn mặt nước 0,35 m.</v>
+        <v xml:space="preserve">  Đế BM-DV013 giữ hai dây B2-D58 (BÈ 2, T = 114,1 kN, dài 9,52 m) và B3-D02 (BÈ 3, T = 78,7 kN, dài 9,52 m). Bích bè cao hơn mặt nước 0,35 m.</v>
       </c>
     </row>
     <row r="51">
@@ -671,32 +671,32 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v xml:space="preserve">  Tổ hợp chi phối: B6-D25 căng (MN cao). Lực nhổ T_v = 85,0 kN (hai dây cộng lại), lực ngang T_h = 74,3 kN (cộng véc-tơ).</v>
+        <v xml:space="preserve">  Tổ hợp chi phối: cả hai dây căng (MN cao). Lực nhổ T_v = 171,2 kN (hai dây cộng lại), lực ngang T_h = 16,3 kN (cộng véc-tơ).</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v xml:space="preserve">  Đế 4,00 × 4,00 × 0,4 m: thể tích 6,40 m³, nặng 160,0 kN trên cạn, W' = 6,40 × (25 − 10) = 96,0 kN trong nước (đã trừ lực đẩy nổi).</v>
+        <v xml:space="preserve">  Đế 5,75 × 5,75 × 0,4 m: thể tích 13,23 m³, nặng 330,6 kN trên cạn, W' = 13,23 × (25 − 10) = 198,4 kN trong nước (đã trừ lực đẩy nổi).</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v xml:space="preserve">  SV-1 nhổ: T_v ≤ 0,9 × W' + 4 × Q_a = 118,1 kN; mức sử dụng 0,72.</v>
+        <v xml:space="preserve">  SV-1 nhổ: T_v ≤ 0,9 × W' + 4 × Q_a = 210,2 kN; mức sử dụng 0,81.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v xml:space="preserve">  SV-2 trượt: 1,5 × T_h ≤ bám dính đáy + gờ + 4 × H_u. Bám dính đáy = 0,5 × c_u × B² = 160,0 kN (lấy bằng 0 khi T_v &gt; W': đế bị nhấc khỏi bùn); gờ sâu z = 0,15 m: B × (0,5 × γ' × z² + 2 × c_u × z) = 24,3 kN; H_u một vít = 15,0 kN (Broms, đầu tự do ở mặt bùn). 1,5 × 74,3 = 111,5 ≤ 244,2 kN; mức sử dụng 0,69.</v>
+        <v xml:space="preserve">  SV-2 trượt: 1,5 × T_h ≤ bám dính đáy + gờ + 4 × H_u. Bám dính đáy = 0,5 × c_u × B² = 330,6 kN (lấy bằng 0 khi T_v &gt; W': đế bị nhấc khỏi bùn); gờ sâu z = 0,15 m: B × (0,5 × γ' × z² + 2 × c_u × z) = 34,9 kN; H_u một vít = 15,0 kN (Broms, đầu tự do ở mặt bùn). 1,5 × 16,3 = 24,5 ≤ 425,5 kN; mức sử dụng 0,38.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v xml:space="preserve">  SV-3 lật quanh mép đáy phía xa dây: M_lật = T_h × (t + h_tai) + T_v × B / 2 = 74,3 × (0,4 + 0,15) + 85,0 × 4,00 / 2 = 210,8 kNm; M_giữ = W' × B / 2 + (n/2) × Q_u × (B − c) + (n/2) × Q_u × c = 318,7 kNm (c = 0,15 m từ mép đế tới tim lỗ vít). 1,5 × 210,8 = 316,2 ≤ 318,7 kNm; mức sử dụng 0,99.</v>
+        <v xml:space="preserve">  SV-3 lật quanh mép đáy phía xa dây: M_lật = T_h × (t + h_tai) + T_v × B / 2 = 16,3 × (0,4 + 0,15) + 171,2 × 5,75 / 2 = 501,0 kNm; M_giữ = W' × B / 2 + (n/2) × Q_u × (B − c) + (n/2) × Q_u × c = 752,4 kNm (c = 0,15 m từ mép đế tới tim lỗ vít). 1,5 × 501,0 = 751,6 ≤ 752,4 kNm; mức sử dụng 1,00.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v xml:space="preserve">  SV-4 một vít: lực nhổ lên vít chịu nặng nhất N_1 = max[(T_v − 0,9 × W') / n ; (M_lật − 0,9 × W' × B / 2) / (B − c) / (n/2)] = 4,9 kN ≤ Q_a = 7,9 kN; mức sử dụng 0,62.</v>
+        <v xml:space="preserve">  SV-4 một vít: lực nhổ lên vít chịu nặng nhất N_1 = max[(T_v − 0,9 × W') / n ; (M_lật − 0,9 × W' × B / 2) / (B − c) / (n/2)] = 0,0 kN ≤ Q_a = 7,9 kN; mức sử dụng 0,00.</v>
       </c>
     </row>
     <row r="58">
@@ -706,17 +706,17 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v xml:space="preserve">  SV-6 thép bản đế: tai neo kéo lên ở giữa, 4 vít giữ ở các góc; mô-men trên 1 m bản M = (n/2) × Q_u × (s/2) / B = 14,65 kNm/m (s = B − 2c); thép cần A_s = M / (0,9 × h_0 × R_s) = 179 mm²/m, tối thiểu 0,1% = 350 mm²/m; bố trí lưới Ø12 a200 hai lớp = 565 mm²/m; mức sử dụng 0,62.</v>
+        <v xml:space="preserve">  SV-6 thép bản đế: tai neo kéo lên ở giữa, 4 vít giữ ở các góc; mô-men trên 1 m bản M = (n/2) × Q_u × (s/2) / B = 15,01 kNm/m (s = B − 2c); thép cần A_s = M / (0,9 × h_0 × R_s) = 183 mm²/m, tối thiểu 0,1% = 350 mm²/m; bố trí lưới Ø12 a200 hai lớp = 565 mm²/m; mức sử dụng 0,62.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v xml:space="preserve">  Cả hệ: 19 đế (2 đế 2,50 m, 2 đế 2,75 m, 2 đế 3,50 m, 1 đế 3,75 m, 6 đế 4,00 m, 3 đế 4,25 m, 2 đế 5,75 m, 1 đế 6,00 m), 133,2 m³ bê tông, 5,9 tấn thép bản, 76 vít (283 m), đế nặng nhất khi cẩu 36,7 tấn.</v>
+        <v xml:space="preserve">  Cả hệ: 17 đế (2 đế 2,75 m, 2 đế 3,50 m, 1 đế 3,75 m, 6 đế 4,00 m, 3 đế 4,25 m, 2 đế 5,75 m, 1 đế 6,00 m), 128,3 m³ bê tông, 5,6 tấn thép bản, 68 vít (253 m), đế nặng nhất khi cẩu 36,7 tấn.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v xml:space="preserve">  Tổng lực nhổ lên 19 đế 1.798 kN, tổng sức chống nhổ 2.405 kN. Mức sử dụng lớn nhất: nhổ 0,83, trượt 0,76, lật 0,99, một vít 0,78.</v>
+        <v xml:space="preserve">  Tổng lực nhổ lên 17 đế 1.746 kN, tổng sức chống nhổ 2.275 kN. Mức sử dụng lớn nhất: nhổ 0,83, trượt 0,75, lật 1,00, một vít 0,78.</v>
       </c>
     </row>
     <row r="62">
@@ -731,7 +731,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">  Mỗi dây cắt đủ dài cho mực nước làm khoảng cách bích – chốt dài nhất (29 dây đáy ở MNLKT, 186 dây bờ ở MNC). Tổng chiều dài cắt: dây bờ 8.624 m, dây đáy 767 m, chưa gồm đoạn bện đầu và phụ kiện.</v>
+        <v xml:space="preserve">  Mỗi dây cắt đủ dài cho mực nước làm khoảng cách bích – chốt dài nhất (27 dây đáy ở MNLKT, 188 dây bờ ở MNC). Tổng chiều dài cắt: dây bờ 8.716 m, dây đáy 720 m, chưa gồm đoạn bện đầu và phụ kiện.</v>
       </c>
     </row>
     <row r="65">
@@ -756,7 +756,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">  Nếu khóa của thiết bị bù KHÔNG khóa kịp, đối trọng chỉ giữ lực căng 5 kN và hành trình dư 3 m mỗi chiều: bè trôi 3,6–6,7 m (tới hết hành trình rồi dây mới căng) và lực dây vọt tới 89–383 kN (hệ số an toàn cáp chỉ 1,8–4,3; đế và cọc không được tính cho lực này). Đối trọng treo tự do KHÔNG đủ giữ bè: cần bộ khóa / phanh chủ động, dự phòng, kiểm tra định kỳ.</v>
+        <v xml:space="preserve">  Nếu khóa của thiết bị bù KHÔNG khóa kịp, đối trọng chỉ giữ lực căng 5 kN và hành trình dư 3 m mỗi chiều: bè trôi 3,6–6,7 m (tới hết hành trình rồi dây mới căng) và lực dây vọt tới 90–383 kN (hệ số an toàn cáp chỉ 1,8–4,3; đế và cọc không được tính cho lực này). Đối trọng treo tự do KHÔNG đủ giữ bè: cần bộ khóa / phanh chủ động, dự phòng, kiểm tra định kỳ.</v>
       </c>
     </row>
     <row r="70">
@@ -766,7 +766,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">  Đế vít xoắn đặt trên mặt đất IFC tại chỗ (không phải đáy thiết kế chung như Huổi Vanh): 3/19 đế có nền cao hơn MNC (tới 654,44 m) nên lộ khô khi hồ xuống mực nước chết.</v>
+        <v xml:space="preserve">  Đế vít xoắn đặt trên mặt đất IFC tại chỗ (không phải đáy thiết kế chung như Huổi Vanh): 1/17 đế có nền cao hơn MNC (tới 650,48 m) nên lộ khô khi hồ xuống mực nước chết.</v>
       </c>
     </row>
     <row r="72">
@@ -781,12 +781,12 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">  15/186 dây bờ lệch quá 60° so với pháp tuyến mép bè (tới 90°: B1-D06, B1-D24, B1-D38, B2-D09, B2-D11, B2-D16, B2-D49, B2-D54, B3-D05, B5-D05, B5-D18, B5-D23, B5-D29, B6-D15, B6-D26) — do ưu tiên neo bờ thay đế ở các khe giữa bè: cáp chạy xiên dọc mép, tai neo trên bè chịu lực xiên; nhà sản xuất bè cần xác nhận.</v>
+        <v xml:space="preserve">  15/188 dây bờ lệch quá 60° so với pháp tuyến mép bè (tới 90°: B1-D06, B1-D24, B1-D38, B2-D09, B2-D11, B2-D16, B2-D49, B2-D54, B3-D05, B5-D05, B5-D18, B5-D23, B5-D29, B6-D15, B6-D26) — do ưu tiên neo bờ thay đế ở các khe giữa bè: cáp chạy xiên dọc mép, tai neo trên bè chịu lực xiên; nhà sản xuất bè cần xác nhận.</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">  9/19 đế vít xoắn là đế ĐƠN (một dây), ở vùng nước trống xa bờ hơn tầm dây bờ cho phép 80 m hoặc ở khe không đặt được dây đối diện: quy tắc của Huổi Vanh "đế chỉ đặt giữa hai bè" không áp dụng được cho mặt bằng này — cần Chủ đầu tư xác nhận.</v>
+        <v xml:space="preserve">  7/17 đế vít xoắn là đế ĐƠN (một dây), ở vùng nước trống xa bờ hơn tầm dây bờ cho phép 80 m hoặc ở khe không đặt được dây đối diện: quy tắc của Huổi Vanh "đế chỉ đặt giữa hai bè" không áp dụng được cho mặt bằng này — cần Chủ đầu tư xác nhận.</v>
       </c>
     </row>
     <row r="76">
@@ -806,7 +806,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">  Đế đặt trên địa hình IFC tại chỗ, chưa phải khảo sát. 171/186 cọc bờ đứng ở chỗ mặt đất thấp hơn MNDB.</v>
+        <v xml:space="preserve">  Đế đặt trên địa hình IFC tại chỗ, chưa phải khảo sát. 172/188 cọc bờ đứng ở chỗ mặt đất thấp hơn MNDB.</v>
       </c>
     </row>
     <row r="80">
@@ -2073,16 +2073,16 @@
         <v>649.5</v>
       </c>
       <c r="C52">
-        <v>48.8</v>
+        <v>45.6</v>
       </c>
       <c r="D52" t="str">
-        <v>B3-D18</v>
+        <v>B3-D13</v>
       </c>
       <c r="E52">
-        <v>345</v>
+        <v>150</v>
       </c>
       <c r="F52">
-        <v>0.21</v>
+        <v>0.39</v>
       </c>
       <c r="G52">
         <v>7</v>
@@ -2096,16 +2096,16 @@
         <v>650</v>
       </c>
       <c r="C53">
-        <v>48.4</v>
+        <v>45.2</v>
       </c>
       <c r="D53" t="str">
-        <v>B3-D18</v>
+        <v>B3-D13</v>
       </c>
       <c r="E53">
-        <v>345</v>
+        <v>150</v>
       </c>
       <c r="F53">
-        <v>0.21</v>
+        <v>0.39</v>
       </c>
       <c r="G53">
         <v>7</v>
@@ -2119,16 +2119,16 @@
         <v>651</v>
       </c>
       <c r="C54">
-        <v>47.6</v>
+        <v>44.7</v>
       </c>
       <c r="D54" t="str">
-        <v>B3-D18</v>
+        <v>B3-D13</v>
       </c>
       <c r="E54">
-        <v>345</v>
+        <v>150</v>
       </c>
       <c r="F54">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="G54">
         <v>7</v>
@@ -2142,16 +2142,16 @@
         <v>652</v>
       </c>
       <c r="C55">
-        <v>46.8</v>
+        <v>44.4</v>
       </c>
       <c r="D55" t="str">
-        <v>B3-D18</v>
+        <v>B3-D13</v>
       </c>
       <c r="E55">
-        <v>345</v>
+        <v>165</v>
       </c>
       <c r="F55">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="G55">
         <v>7</v>
@@ -2165,16 +2165,16 @@
         <v>653</v>
       </c>
       <c r="C56">
-        <v>46</v>
+        <v>44.5</v>
       </c>
       <c r="D56" t="str">
-        <v>B3-D18</v>
+        <v>B3-D13</v>
       </c>
       <c r="E56">
-        <v>345</v>
+        <v>165</v>
       </c>
       <c r="F56">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -2188,16 +2188,16 @@
         <v>654</v>
       </c>
       <c r="C57">
-        <v>45.2</v>
+        <v>44.8</v>
       </c>
       <c r="D57" t="str">
-        <v>B3-D18</v>
+        <v>B3-D13</v>
       </c>
       <c r="E57">
-        <v>345</v>
+        <v>165</v>
       </c>
       <c r="F57">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="G57">
         <v>7</v>
@@ -2211,16 +2211,16 @@
         <v>655</v>
       </c>
       <c r="C58">
-        <v>44.3</v>
+        <v>45.4</v>
       </c>
       <c r="D58" t="str">
-        <v>B3-D18</v>
+        <v>B3-D13</v>
       </c>
       <c r="E58">
-        <v>345</v>
+        <v>165</v>
       </c>
       <c r="F58">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="G58">
         <v>7</v>
@@ -2234,7 +2234,7 @@
         <v>656</v>
       </c>
       <c r="C59">
-        <v>43.5</v>
+        <v>46.3</v>
       </c>
       <c r="D59" t="str">
         <v>B3-D13</v>
@@ -2243,7 +2243,7 @@
         <v>165</v>
       </c>
       <c r="F59">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -2257,16 +2257,16 @@
         <v>657</v>
       </c>
       <c r="C60">
-        <v>46.2</v>
+        <v>47.4</v>
       </c>
       <c r="D60" t="str">
-        <v>B3-D02</v>
+        <v>B3-D13</v>
       </c>
       <c r="E60">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="F60">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="G60">
         <v>7</v>
@@ -2280,7 +2280,7 @@
         <v>658</v>
       </c>
       <c r="C61">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="D61" t="str">
         <v>B3-D02</v>
@@ -2289,10 +2289,10 @@
         <v>180</v>
       </c>
       <c r="F61">
-        <v>0.21</v>
+        <v>0.32</v>
       </c>
       <c r="G61">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -2303,7 +2303,7 @@
         <v>659</v>
       </c>
       <c r="C62">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="D62" t="str">
         <v>B3-D02</v>
@@ -2312,10 +2312,10 @@
         <v>180</v>
       </c>
       <c r="F62">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="G62">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -2326,7 +2326,7 @@
         <v>660</v>
       </c>
       <c r="C63">
-        <v>54.3</v>
+        <v>54.5</v>
       </c>
       <c r="D63" t="str">
         <v>B3-D02</v>
@@ -2335,10 +2335,10 @@
         <v>180</v>
       </c>
       <c r="F63">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="G63">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
@@ -2349,7 +2349,7 @@
         <v>661</v>
       </c>
       <c r="C64">
-        <v>56.8</v>
+        <v>57.3</v>
       </c>
       <c r="D64" t="str">
         <v>B3-D02</v>
@@ -2358,10 +2358,10 @@
         <v>180</v>
       </c>
       <c r="F64">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="G64">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -2372,7 +2372,7 @@
         <v>662</v>
       </c>
       <c r="C65">
-        <v>59.3</v>
+        <v>60</v>
       </c>
       <c r="D65" t="str">
         <v>B3-D02</v>
@@ -2381,10 +2381,10 @@
         <v>180</v>
       </c>
       <c r="F65">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="G65">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -2395,7 +2395,7 @@
         <v>662.76</v>
       </c>
       <c r="C66">
-        <v>61</v>
+        <v>61.9</v>
       </c>
       <c r="D66" t="str">
         <v>B3-D02</v>
@@ -2404,10 +2404,10 @@
         <v>180</v>
       </c>
       <c r="F66">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="G66">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -2418,7 +2418,7 @@
         <v>663</v>
       </c>
       <c r="C67">
-        <v>61.5</v>
+        <v>62.5</v>
       </c>
       <c r="D67" t="str">
         <v>B3-D02</v>
@@ -2427,10 +2427,10 @@
         <v>180</v>
       </c>
       <c r="F67">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="G67">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
@@ -2441,7 +2441,7 @@
         <v>664</v>
       </c>
       <c r="C68">
-        <v>63.6</v>
+        <v>64.8</v>
       </c>
       <c r="D68" t="str">
         <v>B3-D02</v>
@@ -2450,10 +2450,10 @@
         <v>180</v>
       </c>
       <c r="F68">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="G68">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
@@ -2464,7 +2464,7 @@
         <v>665</v>
       </c>
       <c r="C69">
-        <v>65.6</v>
+        <v>67</v>
       </c>
       <c r="D69" t="str">
         <v>B3-D02</v>
@@ -2473,10 +2473,10 @@
         <v>180</v>
       </c>
       <c r="F69">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="G69">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
@@ -2487,7 +2487,7 @@
         <v>666</v>
       </c>
       <c r="C70">
-        <v>67.3</v>
+        <v>68.9</v>
       </c>
       <c r="D70" t="str">
         <v>B3-D02</v>
@@ -2496,10 +2496,10 @@
         <v>180</v>
       </c>
       <c r="F70">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="G70">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -2510,7 +2510,7 @@
         <v>667</v>
       </c>
       <c r="C71">
-        <v>68.9</v>
+        <v>70.7</v>
       </c>
       <c r="D71" t="str">
         <v>B3-D02</v>
@@ -2519,10 +2519,10 @@
         <v>180</v>
       </c>
       <c r="F71">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="G71">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
@@ -2533,7 +2533,7 @@
         <v>668</v>
       </c>
       <c r="C72">
-        <v>70.3</v>
+        <v>72.2</v>
       </c>
       <c r="D72" t="str">
         <v>B3-D02</v>
@@ -2542,10 +2542,10 @@
         <v>180</v>
       </c>
       <c r="F72">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="G72">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -2556,7 +2556,7 @@
         <v>669</v>
       </c>
       <c r="C73">
-        <v>71.5</v>
+        <v>73.6</v>
       </c>
       <c r="D73" t="str">
         <v>B3-D02</v>
@@ -2565,10 +2565,10 @@
         <v>180</v>
       </c>
       <c r="F73">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="G73">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -2579,7 +2579,7 @@
         <v>669.05</v>
       </c>
       <c r="C74">
-        <v>71.5</v>
+        <v>73.7</v>
       </c>
       <c r="D74" t="str">
         <v>B3-D02</v>
@@ -2588,10 +2588,10 @@
         <v>180</v>
       </c>
       <c r="F74">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="G74">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -5204,10 +5204,10 @@
         <v>19</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <v>700</v>
@@ -5243,10 +5243,10 @@
         <v>Cân bằng tĩnh theo mực nước</v>
       </c>
       <c r="R8">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="S8">
-        <v>113.7</v>
+        <v>120.6</v>
       </c>
       <c r="T8" t="str">
         <v>PES-32</v>
@@ -5255,10 +5255,10 @@
         <v>305</v>
       </c>
       <c r="V8">
-        <v>3.99</v>
+        <v>3.88</v>
       </c>
       <c r="W8">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="X8" t="str">
         <v>ĐẠT</v>
@@ -5760,7 +5760,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>0.35</v>
@@ -5781,7 +5781,7 @@
         <v>Đai xoắn Φ8 a150</v>
       </c>
       <c r="I8">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="J8">
         <v>290.2</v>
@@ -5790,19 +5790,19 @@
         <v>116.1</v>
       </c>
       <c r="L8">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="M8">
-        <v>71.1</v>
+        <v>73.7</v>
       </c>
       <c r="N8">
-        <v>85.3</v>
+        <v>88.5</v>
       </c>
       <c r="O8">
         <v>93.3</v>
       </c>
       <c r="P8">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="Q8">
         <v>81.9</v>
@@ -5814,13 +5814,13 @@
         <v>207.6</v>
       </c>
       <c r="T8">
-        <v>99</v>
+        <v>112.2</v>
       </c>
       <c r="U8">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="V8">
-        <v>3114</v>
+        <v>3529</v>
       </c>
       <c r="W8" t="str">
         <v>ĐẠT</v>
@@ -6044,7 +6044,7 @@
         <v>TỔNG</v>
       </c>
       <c r="B12">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -6098,13 +6098,13 @@
         <v/>
       </c>
       <c r="T12">
-        <v>1227.6</v>
+        <v>1240.8</v>
       </c>
       <c r="U12">
-        <v>118.1</v>
+        <v>119.4</v>
       </c>
       <c r="V12">
-        <v>36170</v>
+        <v>36585</v>
       </c>
       <c r="W12" t="str">
         <v/>
@@ -6119,7 +6119,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB191"/>
+  <dimension ref="A1:AB193"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -6153,7 +6153,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>THỐNG KÊ VÀ TÍNH TOÁN TỪNG CỌC KHOAN NHỒI VEN BỜ (186 CỌC) — BM-FPV-2026</v>
+        <v>THỐNG KÊ VÀ TÍNH TOÁN TỪNG CỌC KHOAN NHỒI VEN BỜ (188 CỌC) — BM-FPV-2026</v>
       </c>
     </row>
     <row r="2">
@@ -12763,16 +12763,16 @@
         <v>69</v>
       </c>
       <c r="S81">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T81">
         <v>81.9</v>
       </c>
       <c r="U81">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V81">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W81">
         <v>1</v>
@@ -12849,16 +12849,16 @@
         <v>269</v>
       </c>
       <c r="S82">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T82">
         <v>81.9</v>
       </c>
       <c r="U82">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V82">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W82">
         <v>1</v>
@@ -12935,16 +12935,16 @@
         <v>94</v>
       </c>
       <c r="S83">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T83">
         <v>81.9</v>
       </c>
       <c r="U83">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V83">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W83">
         <v>1</v>
@@ -13021,16 +13021,16 @@
         <v>84</v>
       </c>
       <c r="S84">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T84">
         <v>81.9</v>
       </c>
       <c r="U84">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V84">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W84">
         <v>1</v>
@@ -13107,16 +13107,16 @@
         <v>254</v>
       </c>
       <c r="S85">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T85">
         <v>81.9</v>
       </c>
       <c r="U85">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V85">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W85">
         <v>1</v>
@@ -13193,16 +13193,16 @@
         <v>229</v>
       </c>
       <c r="S86">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T86">
         <v>81.9</v>
       </c>
       <c r="U86">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V86">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W86">
         <v>1</v>
@@ -13279,16 +13279,16 @@
         <v>94</v>
       </c>
       <c r="S87">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T87">
         <v>81.9</v>
       </c>
       <c r="U87">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V87">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W87">
         <v>1</v>
@@ -13365,16 +13365,16 @@
         <v>264</v>
       </c>
       <c r="S88">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T88">
         <v>81.9</v>
       </c>
       <c r="U88">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V88">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W88">
         <v>1</v>
@@ -13451,16 +13451,16 @@
         <v>84</v>
       </c>
       <c r="S89">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T89">
         <v>81.9</v>
       </c>
       <c r="U89">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V89">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W89">
         <v>1</v>
@@ -13537,16 +13537,16 @@
         <v>84</v>
       </c>
       <c r="S90">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T90">
         <v>81.9</v>
       </c>
       <c r="U90">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V90">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W90">
         <v>1</v>
@@ -13623,16 +13623,16 @@
         <v>229</v>
       </c>
       <c r="S91">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T91">
         <v>81.9</v>
       </c>
       <c r="U91">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V91">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W91">
         <v>1</v>
@@ -13709,16 +13709,16 @@
         <v>239</v>
       </c>
       <c r="S92">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T92">
         <v>81.9</v>
       </c>
       <c r="U92">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V92">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W92">
         <v>1</v>
@@ -13795,16 +13795,16 @@
         <v>109</v>
       </c>
       <c r="S93">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T93">
         <v>81.9</v>
       </c>
       <c r="U93">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V93">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W93">
         <v>1</v>
@@ -13830,10 +13830,10 @@
         <v>89</v>
       </c>
       <c r="B94" t="str">
-        <v>BM-P112</v>
+        <v>BM-P111</v>
       </c>
       <c r="C94" t="str">
-        <v>B3-D17</v>
+        <v>B3-D16</v>
       </c>
       <c r="D94" t="str">
         <v>BÈ 3</v>
@@ -13842,13 +13842,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F94">
-        <v>49.61</v>
+        <v>44</v>
       </c>
       <c r="G94">
-        <v>130.87</v>
+        <v>147</v>
       </c>
       <c r="H94">
-        <v>662.26</v>
+        <v>663.08</v>
       </c>
       <c r="I94">
         <v>0.35</v>
@@ -13875,40 +13875,40 @@
         <v>207.6</v>
       </c>
       <c r="Q94">
-        <v>30.5</v>
+        <v>46.16</v>
       </c>
       <c r="R94">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="S94">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T94">
         <v>81.9</v>
       </c>
       <c r="U94">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V94">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W94">
         <v>1</v>
       </c>
       <c r="X94">
-        <v>-22.3</v>
+        <v>-16.1</v>
       </c>
       <c r="Y94">
-        <v>13</v>
+        <v>7.7</v>
       </c>
       <c r="Z94" t="str">
-        <v>CÓ</v>
+        <v>không</v>
       </c>
       <c r="AA94" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB94" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="95">
@@ -13916,10 +13916,10 @@
         <v>90</v>
       </c>
       <c r="B95" t="str">
-        <v>BM-P114</v>
+        <v>BM-P112</v>
       </c>
       <c r="C95" t="str">
-        <v>B3-D19</v>
+        <v>B3-D17</v>
       </c>
       <c r="D95" t="str">
         <v>BÈ 3</v>
@@ -13928,13 +13928,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F95">
-        <v>48.41</v>
+        <v>49.61</v>
       </c>
       <c r="G95">
-        <v>140.31</v>
+        <v>130.87</v>
       </c>
       <c r="H95">
-        <v>662.32</v>
+        <v>662.26</v>
       </c>
       <c r="I95">
         <v>0.35</v>
@@ -13961,31 +13961,31 @@
         <v>207.6</v>
       </c>
       <c r="Q95">
-        <v>33.5</v>
+        <v>30.5</v>
       </c>
       <c r="R95">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="S95">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="T95">
         <v>81.9</v>
       </c>
       <c r="U95">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="V95">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="W95">
         <v>1</v>
       </c>
       <c r="X95">
-        <v>-20.6</v>
+        <v>-22.3</v>
       </c>
       <c r="Y95">
-        <v>11.8</v>
+        <v>13</v>
       </c>
       <c r="Z95" t="str">
         <v>CÓ</v>
@@ -14002,25 +14002,25 @@
         <v>91</v>
       </c>
       <c r="B96" t="str">
-        <v>BM-P115</v>
+        <v>BM-P113</v>
       </c>
       <c r="C96" t="str">
-        <v>B4-D01</v>
+        <v>B3-D18</v>
       </c>
       <c r="D96" t="str">
-        <v>BÈ 4</v>
+        <v>BÈ 3</v>
       </c>
       <c r="E96" t="str">
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F96">
-        <v>-18.45</v>
+        <v>88.96</v>
       </c>
       <c r="G96">
-        <v>-8.61</v>
+        <v>48.33</v>
       </c>
       <c r="H96">
-        <v>662.34</v>
+        <v>662.32</v>
       </c>
       <c r="I96">
         <v>0.35</v>
@@ -14032,7 +14032,7 @@
         <v>6.6</v>
       </c>
       <c r="L96" t="str">
-        <v>6Φ25</v>
+        <v>6Φ28</v>
       </c>
       <c r="M96" t="str">
         <v>CB400-V</v>
@@ -14044,34 +14044,34 @@
         <v>0.635</v>
       </c>
       <c r="P96">
-        <v>168.8</v>
+        <v>207.6</v>
       </c>
       <c r="Q96">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="R96">
-        <v>94.9</v>
+        <v>204</v>
       </c>
       <c r="S96">
-        <v>64.5</v>
+        <v>78.7</v>
       </c>
       <c r="T96">
-        <v>69</v>
+        <v>81.9</v>
       </c>
       <c r="U96">
-        <v>0.56</v>
+        <v>0.68</v>
       </c>
       <c r="V96">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="W96">
         <v>1</v>
       </c>
       <c r="X96">
-        <v>-29.8</v>
+        <v>-16.7</v>
       </c>
       <c r="Y96">
-        <v>17.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z96" t="str">
         <v>CÓ</v>
@@ -14080,7 +14080,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB96" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="97">
@@ -14088,25 +14088,25 @@
         <v>92</v>
       </c>
       <c r="B97" t="str">
-        <v>BM-P116</v>
+        <v>BM-P114</v>
       </c>
       <c r="C97" t="str">
-        <v>B4-D03</v>
+        <v>B3-D19</v>
       </c>
       <c r="D97" t="str">
-        <v>BÈ 4</v>
+        <v>BÈ 3</v>
       </c>
       <c r="E97" t="str">
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F97">
-        <v>22.11</v>
+        <v>48.41</v>
       </c>
       <c r="G97">
-        <v>87.6</v>
+        <v>140.31</v>
       </c>
       <c r="H97">
-        <v>662.4</v>
+        <v>662.32</v>
       </c>
       <c r="I97">
         <v>0.35</v>
@@ -14118,7 +14118,7 @@
         <v>6.6</v>
       </c>
       <c r="L97" t="str">
-        <v>6Φ25</v>
+        <v>6Φ28</v>
       </c>
       <c r="M97" t="str">
         <v>CB400-V</v>
@@ -14130,34 +14130,34 @@
         <v>0.635</v>
       </c>
       <c r="P97">
-        <v>168.8</v>
+        <v>207.6</v>
       </c>
       <c r="Q97">
-        <v>36</v>
+        <v>33.5</v>
       </c>
       <c r="R97">
-        <v>84.9</v>
+        <v>259</v>
       </c>
       <c r="S97">
-        <v>64.5</v>
+        <v>78.7</v>
       </c>
       <c r="T97">
-        <v>69</v>
+        <v>81.9</v>
       </c>
       <c r="U97">
-        <v>0.56</v>
+        <v>0.68</v>
       </c>
       <c r="V97">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="W97">
         <v>1</v>
       </c>
       <c r="X97">
-        <v>-19.4</v>
+        <v>-20.6</v>
       </c>
       <c r="Y97">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Z97" t="str">
         <v>CÓ</v>
@@ -14174,10 +14174,10 @@
         <v>93</v>
       </c>
       <c r="B98" t="str">
-        <v>BM-P117</v>
+        <v>BM-P115</v>
       </c>
       <c r="C98" t="str">
-        <v>B4-D06</v>
+        <v>B4-D01</v>
       </c>
       <c r="D98" t="str">
         <v>BÈ 4</v>
@@ -14186,13 +14186,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F98">
-        <v>-159.5</v>
+        <v>-18.45</v>
       </c>
       <c r="G98">
-        <v>133.5</v>
+        <v>-8.61</v>
       </c>
       <c r="H98">
-        <v>663.53</v>
+        <v>662.34</v>
       </c>
       <c r="I98">
         <v>0.35</v>
@@ -14219,10 +14219,10 @@
         <v>168.8</v>
       </c>
       <c r="Q98">
-        <v>68.66</v>
+        <v>22</v>
       </c>
       <c r="R98">
-        <v>267.7</v>
+        <v>94.9</v>
       </c>
       <c r="S98">
         <v>64.5</v>
@@ -14240,19 +14240,19 @@
         <v>1</v>
       </c>
       <c r="X98">
-        <v>-11.3</v>
+        <v>-29.8</v>
       </c>
       <c r="Y98">
-        <v>4.8</v>
+        <v>17.6</v>
       </c>
       <c r="Z98" t="str">
-        <v>không</v>
+        <v>CÓ</v>
       </c>
       <c r="AA98" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB98" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
       </c>
     </row>
     <row r="99">
@@ -14260,10 +14260,10 @@
         <v>94</v>
       </c>
       <c r="B99" t="str">
-        <v>BM-P118</v>
+        <v>BM-P116</v>
       </c>
       <c r="C99" t="str">
-        <v>B4-D07</v>
+        <v>B4-D03</v>
       </c>
       <c r="D99" t="str">
         <v>BÈ 4</v>
@@ -14272,13 +14272,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F99">
-        <v>-6.61</v>
+        <v>22.11</v>
       </c>
       <c r="G99">
-        <v>18.31</v>
+        <v>87.6</v>
       </c>
       <c r="H99">
-        <v>662.34</v>
+        <v>662.4</v>
       </c>
       <c r="I99">
         <v>0.35</v>
@@ -14305,10 +14305,10 @@
         <v>168.8</v>
       </c>
       <c r="Q99">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R99">
-        <v>135</v>
+        <v>84.9</v>
       </c>
       <c r="S99">
         <v>64.5</v>
@@ -14326,10 +14326,10 @@
         <v>1</v>
       </c>
       <c r="X99">
-        <v>-20.3</v>
+        <v>-19.4</v>
       </c>
       <c r="Y99">
-        <v>11.6</v>
+        <v>10.9</v>
       </c>
       <c r="Z99" t="str">
         <v>CÓ</v>
@@ -14346,10 +14346,10 @@
         <v>95</v>
       </c>
       <c r="B100" t="str">
-        <v>BM-P119</v>
+        <v>BM-P117</v>
       </c>
       <c r="C100" t="str">
-        <v>B4-D08</v>
+        <v>B4-D06</v>
       </c>
       <c r="D100" t="str">
         <v>BÈ 4</v>
@@ -14358,13 +14358,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F100">
-        <v>8.15</v>
+        <v>-159.5</v>
       </c>
       <c r="G100">
-        <v>148.59</v>
+        <v>133.5</v>
       </c>
       <c r="H100">
-        <v>662.4</v>
+        <v>663.53</v>
       </c>
       <c r="I100">
         <v>0.35</v>
@@ -14391,10 +14391,10 @@
         <v>168.8</v>
       </c>
       <c r="Q100">
-        <v>27.5</v>
+        <v>68.66</v>
       </c>
       <c r="R100">
-        <v>85</v>
+        <v>267.7</v>
       </c>
       <c r="S100">
         <v>64.5</v>
@@ -14412,19 +14412,19 @@
         <v>1</v>
       </c>
       <c r="X100">
-        <v>-24.7</v>
+        <v>-11.3</v>
       </c>
       <c r="Y100">
-        <v>14.1</v>
+        <v>4.8</v>
       </c>
       <c r="Z100" t="str">
-        <v>CÓ</v>
+        <v>không</v>
       </c>
       <c r="AA100" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB100" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="101">
@@ -14432,10 +14432,10 @@
         <v>96</v>
       </c>
       <c r="B101" t="str">
-        <v>BM-P120</v>
+        <v>BM-P118</v>
       </c>
       <c r="C101" t="str">
-        <v>B4-D09</v>
+        <v>B4-D07</v>
       </c>
       <c r="D101" t="str">
         <v>BÈ 4</v>
@@ -14444,13 +14444,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F101">
-        <v>-11.91</v>
+        <v>-6.61</v>
       </c>
       <c r="G101">
-        <v>6.21</v>
+        <v>18.31</v>
       </c>
       <c r="H101">
-        <v>662.36</v>
+        <v>662.34</v>
       </c>
       <c r="I101">
         <v>0.35</v>
@@ -14477,10 +14477,10 @@
         <v>168.8</v>
       </c>
       <c r="Q101">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="R101">
-        <v>119.9</v>
+        <v>135</v>
       </c>
       <c r="S101">
         <v>64.5</v>
@@ -14498,10 +14498,10 @@
         <v>1</v>
       </c>
       <c r="X101">
-        <v>-19.3</v>
+        <v>-20.3</v>
       </c>
       <c r="Y101">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="Z101" t="str">
         <v>CÓ</v>
@@ -14518,10 +14518,10 @@
         <v>97</v>
       </c>
       <c r="B102" t="str">
-        <v>BM-P121</v>
+        <v>BM-P119</v>
       </c>
       <c r="C102" t="str">
-        <v>B4-D11</v>
+        <v>B4-D08</v>
       </c>
       <c r="D102" t="str">
         <v>BÈ 4</v>
@@ -14530,13 +14530,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F102">
-        <v>13.05</v>
+        <v>8.15</v>
       </c>
       <c r="G102">
-        <v>120.54</v>
+        <v>148.59</v>
       </c>
       <c r="H102">
-        <v>662.52</v>
+        <v>662.4</v>
       </c>
       <c r="I102">
         <v>0.35</v>
@@ -14563,10 +14563,10 @@
         <v>168.8</v>
       </c>
       <c r="Q102">
-        <v>30</v>
+        <v>27.5</v>
       </c>
       <c r="R102">
-        <v>79.9</v>
+        <v>85</v>
       </c>
       <c r="S102">
         <v>64.5</v>
@@ -14584,10 +14584,10 @@
         <v>1</v>
       </c>
       <c r="X102">
-        <v>-23.1</v>
+        <v>-24.7</v>
       </c>
       <c r="Y102">
-        <v>12.7</v>
+        <v>14.1</v>
       </c>
       <c r="Z102" t="str">
         <v>CÓ</v>
@@ -14604,10 +14604,10 @@
         <v>98</v>
       </c>
       <c r="B103" t="str">
-        <v>BM-P122</v>
+        <v>BM-P120</v>
       </c>
       <c r="C103" t="str">
-        <v>B4-D13</v>
+        <v>B4-D09</v>
       </c>
       <c r="D103" t="str">
         <v>BÈ 4</v>
@@ -14616,13 +14616,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F103">
-        <v>-20.53</v>
+        <v>-11.91</v>
       </c>
       <c r="G103">
-        <v>-41.32</v>
+        <v>6.21</v>
       </c>
       <c r="H103">
-        <v>666.83</v>
+        <v>662.36</v>
       </c>
       <c r="I103">
         <v>0.35</v>
@@ -14649,10 +14649,10 @@
         <v>168.8</v>
       </c>
       <c r="Q103">
-        <v>59.5</v>
+        <v>36</v>
       </c>
       <c r="R103">
-        <v>122.4</v>
+        <v>119.9</v>
       </c>
       <c r="S103">
         <v>64.5</v>
@@ -14670,19 +14670,19 @@
         <v>1</v>
       </c>
       <c r="X103">
-        <v>-16</v>
+        <v>-19.3</v>
       </c>
       <c r="Y103">
-        <v>2.4</v>
+        <v>10.9</v>
       </c>
       <c r="Z103" t="str">
-        <v>không</v>
+        <v>CÓ</v>
       </c>
       <c r="AA103" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB103" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="104">
@@ -14690,10 +14690,10 @@
         <v>99</v>
       </c>
       <c r="B104" t="str">
-        <v>BM-P123</v>
+        <v>BM-P121</v>
       </c>
       <c r="C104" t="str">
-        <v>B4-D14</v>
+        <v>B4-D11</v>
       </c>
       <c r="D104" t="str">
         <v>BÈ 4</v>
@@ -14702,13 +14702,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F104">
-        <v>-153.9</v>
+        <v>13.05</v>
       </c>
       <c r="G104">
-        <v>125.01</v>
+        <v>120.54</v>
       </c>
       <c r="H104">
-        <v>662.27</v>
+        <v>662.52</v>
       </c>
       <c r="I104">
         <v>0.35</v>
@@ -14735,10 +14735,10 @@
         <v>168.8</v>
       </c>
       <c r="Q104">
-        <v>68.63</v>
+        <v>30</v>
       </c>
       <c r="R104">
-        <v>286.7</v>
+        <v>79.9</v>
       </c>
       <c r="S104">
         <v>64.5</v>
@@ -14756,10 +14756,10 @@
         <v>1</v>
       </c>
       <c r="X104">
-        <v>-10.3</v>
+        <v>-23.1</v>
       </c>
       <c r="Y104">
-        <v>5.8</v>
+        <v>12.7</v>
       </c>
       <c r="Z104" t="str">
         <v>CÓ</v>
@@ -14776,10 +14776,10 @@
         <v>100</v>
       </c>
       <c r="B105" t="str">
-        <v>BM-P124</v>
+        <v>BM-P122</v>
       </c>
       <c r="C105" t="str">
-        <v>B4-D15</v>
+        <v>B4-D13</v>
       </c>
       <c r="D105" t="str">
         <v>BÈ 4</v>
@@ -14788,13 +14788,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F105">
-        <v>5.82</v>
+        <v>-20.53</v>
       </c>
       <c r="G105">
-        <v>50.02</v>
+        <v>-41.32</v>
       </c>
       <c r="H105">
-        <v>662.29</v>
+        <v>666.83</v>
       </c>
       <c r="I105">
         <v>0.35</v>
@@ -14821,10 +14821,10 @@
         <v>168.8</v>
       </c>
       <c r="Q105">
-        <v>17.5</v>
+        <v>59.5</v>
       </c>
       <c r="R105">
-        <v>104.9</v>
+        <v>122.4</v>
       </c>
       <c r="S105">
         <v>64.5</v>
@@ -14842,19 +14842,19 @@
         <v>1</v>
       </c>
       <c r="X105">
-        <v>-35.6</v>
+        <v>-16</v>
       </c>
       <c r="Y105">
-        <v>21.8</v>
+        <v>2.4</v>
       </c>
       <c r="Z105" t="str">
-        <v>CÓ</v>
+        <v>không</v>
       </c>
       <c r="AA105" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB105" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="106">
@@ -14862,10 +14862,10 @@
         <v>101</v>
       </c>
       <c r="B106" t="str">
-        <v>BM-P125</v>
+        <v>BM-P123</v>
       </c>
       <c r="C106" t="str">
-        <v>B4-D17</v>
+        <v>B4-D14</v>
       </c>
       <c r="D106" t="str">
         <v>BÈ 4</v>
@@ -14874,13 +14874,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F106">
-        <v>10.15</v>
+        <v>-153.9</v>
       </c>
       <c r="G106">
-        <v>136.21</v>
+        <v>125.01</v>
       </c>
       <c r="H106">
-        <v>662.26</v>
+        <v>662.27</v>
       </c>
       <c r="I106">
         <v>0.35</v>
@@ -14907,10 +14907,10 @@
         <v>168.8</v>
       </c>
       <c r="Q106">
-        <v>28.5</v>
+        <v>68.63</v>
       </c>
       <c r="R106">
-        <v>79.9</v>
+        <v>286.7</v>
       </c>
       <c r="S106">
         <v>64.5</v>
@@ -14928,10 +14928,10 @@
         <v>1</v>
       </c>
       <c r="X106">
-        <v>-23.7</v>
+        <v>-10.3</v>
       </c>
       <c r="Y106">
-        <v>13.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z106" t="str">
         <v>CÓ</v>
@@ -14948,10 +14948,10 @@
         <v>102</v>
       </c>
       <c r="B107" t="str">
-        <v>BM-P126</v>
+        <v>BM-P124</v>
       </c>
       <c r="C107" t="str">
-        <v>B4-D19</v>
+        <v>B4-D15</v>
       </c>
       <c r="D107" t="str">
         <v>BÈ 4</v>
@@ -14960,13 +14960,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F107">
-        <v>-8.4</v>
+        <v>5.82</v>
       </c>
       <c r="G107">
-        <v>12.44</v>
+        <v>50.02</v>
       </c>
       <c r="H107">
-        <v>662.58</v>
+        <v>662.29</v>
       </c>
       <c r="I107">
         <v>0.35</v>
@@ -14993,10 +14993,10 @@
         <v>168.8</v>
       </c>
       <c r="Q107">
-        <v>45.5</v>
+        <v>17.5</v>
       </c>
       <c r="R107">
-        <v>127.4</v>
+        <v>104.9</v>
       </c>
       <c r="S107">
         <v>64.5</v>
@@ -15014,10 +15014,10 @@
         <v>1</v>
       </c>
       <c r="X107">
-        <v>-15.7</v>
+        <v>-35.6</v>
       </c>
       <c r="Y107">
-        <v>8.4</v>
+        <v>21.8</v>
       </c>
       <c r="Z107" t="str">
         <v>CÓ</v>
@@ -15026,7 +15026,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB107" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
       </c>
     </row>
     <row r="108">
@@ -15034,10 +15034,10 @@
         <v>103</v>
       </c>
       <c r="B108" t="str">
-        <v>BM-P127</v>
+        <v>BM-P125</v>
       </c>
       <c r="C108" t="str">
-        <v>B4-D20</v>
+        <v>B4-D17</v>
       </c>
       <c r="D108" t="str">
         <v>BÈ 4</v>
@@ -15046,13 +15046,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F108">
-        <v>-155.96</v>
+        <v>10.15</v>
       </c>
       <c r="G108">
-        <v>134.01</v>
+        <v>136.21</v>
       </c>
       <c r="H108">
-        <v>662.36</v>
+        <v>662.26</v>
       </c>
       <c r="I108">
         <v>0.35</v>
@@ -15079,10 +15079,10 @@
         <v>168.8</v>
       </c>
       <c r="Q108">
-        <v>66</v>
+        <v>28.5</v>
       </c>
       <c r="R108">
-        <v>254.9</v>
+        <v>79.9</v>
       </c>
       <c r="S108">
         <v>64.5</v>
@@ -15100,10 +15100,10 @@
         <v>1</v>
       </c>
       <c r="X108">
-        <v>-10.8</v>
+        <v>-23.7</v>
       </c>
       <c r="Y108">
-        <v>6</v>
+        <v>13.9</v>
       </c>
       <c r="Z108" t="str">
         <v>CÓ</v>
@@ -15120,10 +15120,10 @@
         <v>104</v>
       </c>
       <c r="B109" t="str">
-        <v>BM-P128</v>
+        <v>BM-P126</v>
       </c>
       <c r="C109" t="str">
-        <v>B4-D21</v>
+        <v>B4-D19</v>
       </c>
       <c r="D109" t="str">
         <v>BÈ 4</v>
@@ -15132,13 +15132,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F109">
-        <v>7.25</v>
+        <v>-8.4</v>
       </c>
       <c r="G109">
-        <v>159.7</v>
+        <v>12.44</v>
       </c>
       <c r="H109">
-        <v>662.3</v>
+        <v>662.58</v>
       </c>
       <c r="I109">
         <v>0.35</v>
@@ -15165,10 +15165,10 @@
         <v>168.8</v>
       </c>
       <c r="Q109">
-        <v>28</v>
+        <v>45.5</v>
       </c>
       <c r="R109">
-        <v>94.9</v>
+        <v>127.4</v>
       </c>
       <c r="S109">
         <v>64.5</v>
@@ -15186,10 +15186,10 @@
         <v>1</v>
       </c>
       <c r="X109">
-        <v>-24.1</v>
+        <v>-15.7</v>
       </c>
       <c r="Y109">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="Z109" t="str">
         <v>CÓ</v>
@@ -15206,10 +15206,10 @@
         <v>105</v>
       </c>
       <c r="B110" t="str">
-        <v>BM-P129</v>
+        <v>BM-P127</v>
       </c>
       <c r="C110" t="str">
-        <v>B4-D22</v>
+        <v>B4-D20</v>
       </c>
       <c r="D110" t="str">
         <v>BÈ 4</v>
@@ -15218,13 +15218,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F110">
-        <v>-156.76</v>
+        <v>-155.96</v>
       </c>
       <c r="G110">
-        <v>123.62</v>
+        <v>134.01</v>
       </c>
       <c r="H110">
-        <v>662.73</v>
+        <v>662.36</v>
       </c>
       <c r="I110">
         <v>0.35</v>
@@ -15251,10 +15251,10 @@
         <v>168.8</v>
       </c>
       <c r="Q110">
-        <v>77.43</v>
+        <v>66</v>
       </c>
       <c r="R110">
-        <v>295.4</v>
+        <v>254.9</v>
       </c>
       <c r="S110">
         <v>64.5</v>
@@ -15272,10 +15272,10 @@
         <v>1</v>
       </c>
       <c r="X110">
-        <v>-9.5</v>
+        <v>-10.8</v>
       </c>
       <c r="Y110">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="Z110" t="str">
         <v>CÓ</v>
@@ -15292,10 +15292,10 @@
         <v>106</v>
       </c>
       <c r="B111" t="str">
-        <v>BM-P130</v>
+        <v>BM-P128</v>
       </c>
       <c r="C111" t="str">
-        <v>B4-D23</v>
+        <v>B4-D21</v>
       </c>
       <c r="D111" t="str">
         <v>BÈ 4</v>
@@ -15304,13 +15304,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F111">
-        <v>1.58</v>
+        <v>7.25</v>
       </c>
       <c r="G111">
-        <v>36.17</v>
+        <v>159.7</v>
       </c>
       <c r="H111">
-        <v>662.27</v>
+        <v>662.3</v>
       </c>
       <c r="I111">
         <v>0.35</v>
@@ -15337,10 +15337,10 @@
         <v>168.8</v>
       </c>
       <c r="Q111">
-        <v>17.99</v>
+        <v>28</v>
       </c>
       <c r="R111">
-        <v>114.9</v>
+        <v>94.9</v>
       </c>
       <c r="S111">
         <v>64.5</v>
@@ -15358,10 +15358,10 @@
         <v>1</v>
       </c>
       <c r="X111">
-        <v>-34.8</v>
+        <v>-24.1</v>
       </c>
       <c r="Y111">
-        <v>21.3</v>
+        <v>14</v>
       </c>
       <c r="Z111" t="str">
         <v>CÓ</v>
@@ -15370,7 +15370,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB111" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="112">
@@ -15378,10 +15378,10 @@
         <v>107</v>
       </c>
       <c r="B112" t="str">
-        <v>BM-P131</v>
+        <v>BM-P129</v>
       </c>
       <c r="C112" t="str">
-        <v>B4-D26</v>
+        <v>B4-D22</v>
       </c>
       <c r="D112" t="str">
         <v>BÈ 4</v>
@@ -15390,13 +15390,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F112">
-        <v>16.3</v>
+        <v>-156.76</v>
       </c>
       <c r="G112">
-        <v>111.85</v>
+        <v>123.62</v>
       </c>
       <c r="H112">
-        <v>662.34</v>
+        <v>662.73</v>
       </c>
       <c r="I112">
         <v>0.35</v>
@@ -15423,10 +15423,10 @@
         <v>168.8</v>
       </c>
       <c r="Q112">
-        <v>33.5</v>
+        <v>77.43</v>
       </c>
       <c r="R112">
-        <v>69.9</v>
+        <v>295.4</v>
       </c>
       <c r="S112">
         <v>64.5</v>
@@ -15444,10 +15444,10 @@
         <v>1</v>
       </c>
       <c r="X112">
-        <v>-20.6</v>
+        <v>-9.5</v>
       </c>
       <c r="Y112">
-        <v>11.7</v>
+        <v>4.9</v>
       </c>
       <c r="Z112" t="str">
         <v>CÓ</v>
@@ -15464,10 +15464,10 @@
         <v>108</v>
       </c>
       <c r="B113" t="str">
-        <v>BM-P132</v>
+        <v>BM-P130</v>
       </c>
       <c r="C113" t="str">
-        <v>B4-D27</v>
+        <v>B4-D23</v>
       </c>
       <c r="D113" t="str">
         <v>BÈ 4</v>
@@ -15476,13 +15476,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F113">
-        <v>-15.85</v>
+        <v>1.58</v>
       </c>
       <c r="G113">
-        <v>-1.15</v>
+        <v>36.17</v>
       </c>
       <c r="H113">
-        <v>662.48</v>
+        <v>662.27</v>
       </c>
       <c r="I113">
         <v>0.35</v>
@@ -15509,10 +15509,10 @@
         <v>168.8</v>
       </c>
       <c r="Q113">
-        <v>27.5</v>
+        <v>17.99</v>
       </c>
       <c r="R113">
-        <v>109.9</v>
+        <v>114.9</v>
       </c>
       <c r="S113">
         <v>64.5</v>
@@ -15530,10 +15530,10 @@
         <v>1</v>
       </c>
       <c r="X113">
-        <v>-24.8</v>
+        <v>-34.8</v>
       </c>
       <c r="Y113">
-        <v>13.9</v>
+        <v>21.3</v>
       </c>
       <c r="Z113" t="str">
         <v>CÓ</v>
@@ -15542,7 +15542,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB113" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
       </c>
     </row>
     <row r="114">
@@ -15550,10 +15550,10 @@
         <v>109</v>
       </c>
       <c r="B114" t="str">
-        <v>BM-P133</v>
+        <v>BM-P131</v>
       </c>
       <c r="C114" t="str">
-        <v>B4-D28</v>
+        <v>B4-D26</v>
       </c>
       <c r="D114" t="str">
         <v>BÈ 4</v>
@@ -15562,13 +15562,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F114">
-        <v>-22.46</v>
+        <v>16.3</v>
       </c>
       <c r="G114">
-        <v>-36.01</v>
+        <v>111.85</v>
       </c>
       <c r="H114">
-        <v>662.6</v>
+        <v>662.34</v>
       </c>
       <c r="I114">
         <v>0.35</v>
@@ -15595,10 +15595,10 @@
         <v>168.8</v>
       </c>
       <c r="Q114">
-        <v>43.5</v>
+        <v>33.5</v>
       </c>
       <c r="R114">
-        <v>129.9</v>
+        <v>69.9</v>
       </c>
       <c r="S114">
         <v>64.5</v>
@@ -15616,10 +15616,10 @@
         <v>1</v>
       </c>
       <c r="X114">
-        <v>-16.5</v>
+        <v>-20.6</v>
       </c>
       <c r="Y114">
-        <v>8.8</v>
+        <v>11.7</v>
       </c>
       <c r="Z114" t="str">
         <v>CÓ</v>
@@ -15636,10 +15636,10 @@
         <v>110</v>
       </c>
       <c r="B115" t="str">
-        <v>BM-P134</v>
+        <v>BM-P132</v>
       </c>
       <c r="C115" t="str">
-        <v>B4-D30</v>
+        <v>B4-D27</v>
       </c>
       <c r="D115" t="str">
         <v>BÈ 4</v>
@@ -15648,13 +15648,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F115">
-        <v>8.49</v>
+        <v>-15.85</v>
       </c>
       <c r="G115">
-        <v>54.87</v>
+        <v>-1.15</v>
       </c>
       <c r="H115">
-        <v>662.4</v>
+        <v>662.48</v>
       </c>
       <c r="I115">
         <v>0.35</v>
@@ -15681,10 +15681,10 @@
         <v>168.8</v>
       </c>
       <c r="Q115">
-        <v>25.5</v>
+        <v>27.5</v>
       </c>
       <c r="R115">
-        <v>124.9</v>
+        <v>109.9</v>
       </c>
       <c r="S115">
         <v>64.5</v>
@@ -15702,10 +15702,10 @@
         <v>1</v>
       </c>
       <c r="X115">
-        <v>-26.4</v>
+        <v>-24.8</v>
       </c>
       <c r="Y115">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="Z115" t="str">
         <v>CÓ</v>
@@ -15714,7 +15714,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB115" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="116">
@@ -15722,10 +15722,10 @@
         <v>111</v>
       </c>
       <c r="B116" t="str">
-        <v>BM-P135</v>
+        <v>BM-P133</v>
       </c>
       <c r="C116" t="str">
-        <v>B4-D32</v>
+        <v>B4-D28</v>
       </c>
       <c r="D116" t="str">
         <v>BÈ 4</v>
@@ -15734,13 +15734,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F116">
-        <v>-155.29</v>
+        <v>-22.46</v>
       </c>
       <c r="G116">
-        <v>129.79</v>
+        <v>-36.01</v>
       </c>
       <c r="H116">
-        <v>662.45</v>
+        <v>662.6</v>
       </c>
       <c r="I116">
         <v>0.35</v>
@@ -15767,10 +15767,10 @@
         <v>168.8</v>
       </c>
       <c r="Q116">
-        <v>66.28</v>
+        <v>43.5</v>
       </c>
       <c r="R116">
-        <v>277.4</v>
+        <v>129.9</v>
       </c>
       <c r="S116">
         <v>64.5</v>
@@ -15788,10 +15788,10 @@
         <v>1</v>
       </c>
       <c r="X116">
-        <v>-10.8</v>
+        <v>-16.5</v>
       </c>
       <c r="Y116">
-        <v>5.9</v>
+        <v>8.8</v>
       </c>
       <c r="Z116" t="str">
         <v>CÓ</v>
@@ -15808,10 +15808,10 @@
         <v>112</v>
       </c>
       <c r="B117" t="str">
-        <v>BM-P136</v>
+        <v>BM-P134</v>
       </c>
       <c r="C117" t="str">
-        <v>B4-D34</v>
+        <v>B4-D30</v>
       </c>
       <c r="D117" t="str">
         <v>BÈ 4</v>
@@ -15820,13 +15820,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F117">
-        <v>-159.58</v>
+        <v>8.49</v>
       </c>
       <c r="G117">
-        <v>142.25</v>
+        <v>54.87</v>
       </c>
       <c r="H117">
-        <v>662.34</v>
+        <v>662.4</v>
       </c>
       <c r="I117">
         <v>0.35</v>
@@ -15853,10 +15853,10 @@
         <v>168.8</v>
       </c>
       <c r="Q117">
-        <v>69.5</v>
+        <v>25.5</v>
       </c>
       <c r="R117">
-        <v>252.5</v>
+        <v>124.9</v>
       </c>
       <c r="S117">
         <v>64.5</v>
@@ -15874,10 +15874,10 @@
         <v>1</v>
       </c>
       <c r="X117">
-        <v>-10.3</v>
+        <v>-26.4</v>
       </c>
       <c r="Y117">
-        <v>5.7</v>
+        <v>15.2</v>
       </c>
       <c r="Z117" t="str">
         <v>CÓ</v>
@@ -15886,7 +15886,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB117" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
       </c>
     </row>
     <row r="118">
@@ -15894,25 +15894,25 @@
         <v>113</v>
       </c>
       <c r="B118" t="str">
-        <v>BM-P137</v>
+        <v>BM-P135</v>
       </c>
       <c r="C118" t="str">
-        <v>B5-D01</v>
+        <v>B4-D32</v>
       </c>
       <c r="D118" t="str">
-        <v>BÈ 5</v>
+        <v>BÈ 4</v>
       </c>
       <c r="E118" t="str">
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F118">
-        <v>-285.42</v>
+        <v>-155.29</v>
       </c>
       <c r="G118">
-        <v>33.43</v>
+        <v>129.79</v>
       </c>
       <c r="H118">
-        <v>662.33</v>
+        <v>662.45</v>
       </c>
       <c r="I118">
         <v>0.35</v>
@@ -15924,7 +15924,7 @@
         <v>6.6</v>
       </c>
       <c r="L118" t="str">
-        <v>6Φ28</v>
+        <v>6Φ25</v>
       </c>
       <c r="M118" t="str">
         <v>CB400-V</v>
@@ -15936,34 +15936,34 @@
         <v>0.635</v>
       </c>
       <c r="P118">
-        <v>207.6</v>
+        <v>168.8</v>
       </c>
       <c r="Q118">
-        <v>71.5</v>
+        <v>66.28</v>
       </c>
       <c r="R118">
-        <v>265.3</v>
+        <v>277.4</v>
       </c>
       <c r="S118">
+        <v>64.5</v>
+      </c>
+      <c r="T118">
         <v>69</v>
       </c>
-      <c r="T118">
-        <v>81.9</v>
-      </c>
       <c r="U118">
-        <v>0.59</v>
+        <v>0.56</v>
       </c>
       <c r="V118">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="W118">
         <v>1</v>
       </c>
       <c r="X118">
-        <v>-10</v>
+        <v>-10.8</v>
       </c>
       <c r="Y118">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="Z118" t="str">
         <v>CÓ</v>
@@ -15980,25 +15980,25 @@
         <v>114</v>
       </c>
       <c r="B119" t="str">
-        <v>BM-P138</v>
+        <v>BM-P136</v>
       </c>
       <c r="C119" t="str">
-        <v>B5-D02</v>
+        <v>B4-D34</v>
       </c>
       <c r="D119" t="str">
-        <v>BÈ 5</v>
+        <v>BÈ 4</v>
       </c>
       <c r="E119" t="str">
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F119">
-        <v>-83.14</v>
+        <v>-159.58</v>
       </c>
       <c r="G119">
-        <v>-94.28</v>
+        <v>142.25</v>
       </c>
       <c r="H119">
-        <v>662.27</v>
+        <v>662.34</v>
       </c>
       <c r="I119">
         <v>0.35</v>
@@ -16010,7 +16010,7 @@
         <v>6.6</v>
       </c>
       <c r="L119" t="str">
-        <v>6Φ28</v>
+        <v>6Φ25</v>
       </c>
       <c r="M119" t="str">
         <v>CB400-V</v>
@@ -16022,34 +16022,34 @@
         <v>0.635</v>
       </c>
       <c r="P119">
-        <v>207.6</v>
+        <v>168.8</v>
       </c>
       <c r="Q119">
-        <v>35</v>
+        <v>69.5</v>
       </c>
       <c r="R119">
-        <v>130.3</v>
+        <v>252.5</v>
       </c>
       <c r="S119">
+        <v>64.5</v>
+      </c>
+      <c r="T119">
         <v>69</v>
       </c>
-      <c r="T119">
-        <v>81.9</v>
-      </c>
       <c r="U119">
-        <v>0.59</v>
+        <v>0.56</v>
       </c>
       <c r="V119">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="W119">
         <v>1</v>
       </c>
       <c r="X119">
-        <v>-19.7</v>
+        <v>-10.3</v>
       </c>
       <c r="Y119">
-        <v>11.4</v>
+        <v>5.7</v>
       </c>
       <c r="Z119" t="str">
         <v>CÓ</v>
@@ -16066,10 +16066,10 @@
         <v>115</v>
       </c>
       <c r="B120" t="str">
-        <v>BM-P139</v>
+        <v>BM-P137</v>
       </c>
       <c r="C120" t="str">
-        <v>B5-D03</v>
+        <v>B5-D01</v>
       </c>
       <c r="D120" t="str">
         <v>BÈ 5</v>
@@ -16078,13 +16078,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F120">
-        <v>-244.09</v>
+        <v>-285.42</v>
       </c>
       <c r="G120">
-        <v>-78.78</v>
+        <v>33.43</v>
       </c>
       <c r="H120">
-        <v>662.31</v>
+        <v>662.33</v>
       </c>
       <c r="I120">
         <v>0.35</v>
@@ -16111,10 +16111,10 @@
         <v>207.6</v>
       </c>
       <c r="Q120">
-        <v>47.5</v>
+        <v>71.5</v>
       </c>
       <c r="R120">
-        <v>245.3</v>
+        <v>265.3</v>
       </c>
       <c r="S120">
         <v>69</v>
@@ -16132,10 +16132,10 @@
         <v>1</v>
       </c>
       <c r="X120">
-        <v>-14.8</v>
+        <v>-10</v>
       </c>
       <c r="Y120">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="Z120" t="str">
         <v>CÓ</v>
@@ -16152,10 +16152,10 @@
         <v>116</v>
       </c>
       <c r="B121" t="str">
-        <v>BM-P140</v>
+        <v>BM-P138</v>
       </c>
       <c r="C121" t="str">
-        <v>B5-D05</v>
+        <v>B5-D02</v>
       </c>
       <c r="D121" t="str">
         <v>BÈ 5</v>
@@ -16164,13 +16164,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F121">
-        <v>-271.2</v>
+        <v>-83.14</v>
       </c>
       <c r="G121">
-        <v>-27.86</v>
+        <v>-94.28</v>
       </c>
       <c r="H121">
-        <v>663.51</v>
+        <v>662.27</v>
       </c>
       <c r="I121">
         <v>0.35</v>
@@ -16197,10 +16197,10 @@
         <v>207.6</v>
       </c>
       <c r="Q121">
-        <v>64.3</v>
+        <v>35</v>
       </c>
       <c r="R121">
-        <v>252.8</v>
+        <v>130.3</v>
       </c>
       <c r="S121">
         <v>69</v>
@@ -16218,19 +16218,19 @@
         <v>1</v>
       </c>
       <c r="X121">
-        <v>-12.1</v>
+        <v>-19.7</v>
       </c>
       <c r="Y121">
-        <v>5.1</v>
+        <v>11.4</v>
       </c>
       <c r="Z121" t="str">
-        <v>không</v>
+        <v>CÓ</v>
       </c>
       <c r="AA121" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB121" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="122">
@@ -16238,10 +16238,10 @@
         <v>117</v>
       </c>
       <c r="B122" t="str">
-        <v>BM-P141</v>
+        <v>BM-P139</v>
       </c>
       <c r="C122" t="str">
-        <v>B5-D06</v>
+        <v>B5-D03</v>
       </c>
       <c r="D122" t="str">
         <v>BÈ 5</v>
@@ -16250,13 +16250,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F122">
-        <v>-26.58</v>
+        <v>-244.09</v>
       </c>
       <c r="G122">
-        <v>-41.62</v>
+        <v>-78.78</v>
       </c>
       <c r="H122">
-        <v>662.36</v>
+        <v>662.31</v>
       </c>
       <c r="I122">
         <v>0.35</v>
@@ -16283,10 +16283,10 @@
         <v>207.6</v>
       </c>
       <c r="Q122">
-        <v>65.5</v>
+        <v>47.5</v>
       </c>
       <c r="R122">
-        <v>100.3</v>
+        <v>245.3</v>
       </c>
       <c r="S122">
         <v>69</v>
@@ -16304,10 +16304,10 @@
         <v>1</v>
       </c>
       <c r="X122">
-        <v>-10.9</v>
+        <v>-14.8</v>
       </c>
       <c r="Y122">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="Z122" t="str">
         <v>CÓ</v>
@@ -16324,10 +16324,10 @@
         <v>118</v>
       </c>
       <c r="B123" t="str">
-        <v>BM-P142</v>
+        <v>BM-P140</v>
       </c>
       <c r="C123" t="str">
-        <v>B5-D07</v>
+        <v>B5-D05</v>
       </c>
       <c r="D123" t="str">
         <v>BÈ 5</v>
@@ -16336,13 +16336,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F123">
-        <v>-164.96</v>
+        <v>-271.2</v>
       </c>
       <c r="G123">
-        <v>-120.25</v>
+        <v>-27.86</v>
       </c>
       <c r="H123">
-        <v>662.32</v>
+        <v>663.51</v>
       </c>
       <c r="I123">
         <v>0.35</v>
@@ -16369,10 +16369,10 @@
         <v>207.6</v>
       </c>
       <c r="Q123">
-        <v>16.5</v>
+        <v>64.3</v>
       </c>
       <c r="R123">
-        <v>175.3</v>
+        <v>252.8</v>
       </c>
       <c r="S123">
         <v>69</v>
@@ -16390,19 +16390,19 @@
         <v>1</v>
       </c>
       <c r="X123">
-        <v>-37.3</v>
+        <v>-12.1</v>
       </c>
       <c r="Y123">
-        <v>22.9</v>
+        <v>5.1</v>
       </c>
       <c r="Z123" t="str">
-        <v>CÓ</v>
+        <v>không</v>
       </c>
       <c r="AA123" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB123" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="124">
@@ -16410,10 +16410,10 @@
         <v>119</v>
       </c>
       <c r="B124" t="str">
-        <v>BM-P143</v>
+        <v>BM-P141</v>
       </c>
       <c r="C124" t="str">
-        <v>B5-D08</v>
+        <v>B5-D06</v>
       </c>
       <c r="D124" t="str">
         <v>BÈ 5</v>
@@ -16422,13 +16422,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F124">
-        <v>-161.8</v>
+        <v>-26.58</v>
       </c>
       <c r="G124">
-        <v>119.68</v>
+        <v>-41.62</v>
       </c>
       <c r="H124">
-        <v>662.32</v>
+        <v>662.36</v>
       </c>
       <c r="I124">
         <v>0.35</v>
@@ -16455,10 +16455,10 @@
         <v>207.6</v>
       </c>
       <c r="Q124">
-        <v>48.5</v>
+        <v>65.5</v>
       </c>
       <c r="R124">
-        <v>355.3</v>
+        <v>100.3</v>
       </c>
       <c r="S124">
         <v>69</v>
@@ -16476,10 +16476,10 @@
         <v>1</v>
       </c>
       <c r="X124">
-        <v>-14.5</v>
+        <v>-10.9</v>
       </c>
       <c r="Y124">
-        <v>8.2</v>
+        <v>6</v>
       </c>
       <c r="Z124" t="str">
         <v>CÓ</v>
@@ -16496,10 +16496,10 @@
         <v>120</v>
       </c>
       <c r="B125" t="str">
-        <v>BM-P144</v>
+        <v>BM-P142</v>
       </c>
       <c r="C125" t="str">
-        <v>B5-D09</v>
+        <v>B5-D07</v>
       </c>
       <c r="D125" t="str">
         <v>BÈ 5</v>
@@ -16508,13 +16508,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F125">
-        <v>-272.4</v>
+        <v>-164.96</v>
       </c>
       <c r="G125">
-        <v>-22.55</v>
+        <v>-120.25</v>
       </c>
       <c r="H125">
-        <v>662.43</v>
+        <v>662.32</v>
       </c>
       <c r="I125">
         <v>0.35</v>
@@ -16541,10 +16541,10 @@
         <v>207.6</v>
       </c>
       <c r="Q125">
-        <v>81.5</v>
+        <v>16.5</v>
       </c>
       <c r="R125">
-        <v>245.3</v>
+        <v>175.3</v>
       </c>
       <c r="S125">
         <v>69</v>
@@ -16562,10 +16562,10 @@
         <v>1</v>
       </c>
       <c r="X125">
-        <v>-8.8</v>
+        <v>-37.3</v>
       </c>
       <c r="Y125">
-        <v>4.8</v>
+        <v>22.9</v>
       </c>
       <c r="Z125" t="str">
         <v>CÓ</v>
@@ -16574,7 +16574,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB125" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
       </c>
     </row>
     <row r="126">
@@ -16582,10 +16582,10 @@
         <v>121</v>
       </c>
       <c r="B126" t="str">
-        <v>BM-P145</v>
+        <v>BM-P143</v>
       </c>
       <c r="C126" t="str">
-        <v>B5-D10</v>
+        <v>B5-D08</v>
       </c>
       <c r="D126" t="str">
         <v>BÈ 5</v>
@@ -16594,13 +16594,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F126">
-        <v>-145.22</v>
+        <v>-161.8</v>
       </c>
       <c r="G126">
-        <v>-124.85</v>
+        <v>119.68</v>
       </c>
       <c r="H126">
-        <v>662.46</v>
+        <v>662.32</v>
       </c>
       <c r="I126">
         <v>0.35</v>
@@ -16627,10 +16627,10 @@
         <v>207.6</v>
       </c>
       <c r="Q126">
-        <v>37.5</v>
+        <v>48.5</v>
       </c>
       <c r="R126">
-        <v>190.3</v>
+        <v>355.3</v>
       </c>
       <c r="S126">
         <v>69</v>
@@ -16648,10 +16648,10 @@
         <v>1</v>
       </c>
       <c r="X126">
-        <v>-18.7</v>
+        <v>-14.5</v>
       </c>
       <c r="Y126">
-        <v>10.3</v>
+        <v>8.2</v>
       </c>
       <c r="Z126" t="str">
         <v>CÓ</v>
@@ -16668,10 +16668,10 @@
         <v>122</v>
       </c>
       <c r="B127" t="str">
-        <v>BM-P146</v>
+        <v>BM-P144</v>
       </c>
       <c r="C127" t="str">
-        <v>B5-D12</v>
+        <v>B5-D09</v>
       </c>
       <c r="D127" t="str">
         <v>BÈ 5</v>
@@ -16680,13 +16680,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F127">
-        <v>-173.38</v>
+        <v>-272.4</v>
       </c>
       <c r="G127">
-        <v>122.89</v>
+        <v>-22.55</v>
       </c>
       <c r="H127">
-        <v>662.37</v>
+        <v>662.43</v>
       </c>
       <c r="I127">
         <v>0.35</v>
@@ -16713,10 +16713,10 @@
         <v>207.6</v>
       </c>
       <c r="Q127">
-        <v>68.5</v>
+        <v>81.5</v>
       </c>
       <c r="R127">
-        <v>10.3</v>
+        <v>245.3</v>
       </c>
       <c r="S127">
         <v>69</v>
@@ -16734,10 +16734,10 @@
         <v>1</v>
       </c>
       <c r="X127">
-        <v>-10.4</v>
+        <v>-8.8</v>
       </c>
       <c r="Y127">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="Z127" t="str">
         <v>CÓ</v>
@@ -16754,10 +16754,10 @@
         <v>123</v>
       </c>
       <c r="B128" t="str">
-        <v>BM-P147</v>
+        <v>BM-P145</v>
       </c>
       <c r="C128" t="str">
-        <v>B5-D14</v>
+        <v>B5-D10</v>
       </c>
       <c r="D128" t="str">
         <v>BÈ 5</v>
@@ -16766,13 +16766,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F128">
-        <v>-64.46</v>
+        <v>-145.22</v>
       </c>
       <c r="G128">
-        <v>-76.96</v>
+        <v>-124.85</v>
       </c>
       <c r="H128">
-        <v>662.44</v>
+        <v>662.46</v>
       </c>
       <c r="I128">
         <v>0.35</v>
@@ -16799,10 +16799,10 @@
         <v>207.6</v>
       </c>
       <c r="Q128">
-        <v>27.5</v>
+        <v>37.5</v>
       </c>
       <c r="R128">
-        <v>140.3</v>
+        <v>190.3</v>
       </c>
       <c r="S128">
         <v>69</v>
@@ -16820,10 +16820,10 @@
         <v>1</v>
       </c>
       <c r="X128">
-        <v>-24.8</v>
+        <v>-18.7</v>
       </c>
       <c r="Y128">
-        <v>14</v>
+        <v>10.3</v>
       </c>
       <c r="Z128" t="str">
         <v>CÓ</v>
@@ -16840,10 +16840,10 @@
         <v>124</v>
       </c>
       <c r="B129" t="str">
-        <v>BM-P148</v>
+        <v>BM-P146</v>
       </c>
       <c r="C129" t="str">
-        <v>B5-D15</v>
+        <v>B5-D12</v>
       </c>
       <c r="D129" t="str">
         <v>BÈ 5</v>
@@ -16852,13 +16852,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F129">
-        <v>-196.39</v>
+        <v>-173.38</v>
       </c>
       <c r="G129">
-        <v>-117.23</v>
+        <v>122.89</v>
       </c>
       <c r="H129">
-        <v>662.31</v>
+        <v>662.37</v>
       </c>
       <c r="I129">
         <v>0.35</v>
@@ -16885,10 +16885,10 @@
         <v>207.6</v>
       </c>
       <c r="Q129">
-        <v>32.5</v>
+        <v>68.5</v>
       </c>
       <c r="R129">
-        <v>200.3</v>
+        <v>10.3</v>
       </c>
       <c r="S129">
         <v>69</v>
@@ -16906,10 +16906,10 @@
         <v>1</v>
       </c>
       <c r="X129">
-        <v>-21.1</v>
+        <v>-10.4</v>
       </c>
       <c r="Y129">
-        <v>12.1</v>
+        <v>5.8</v>
       </c>
       <c r="Z129" t="str">
         <v>CÓ</v>
@@ -16926,10 +16926,10 @@
         <v>125</v>
       </c>
       <c r="B130" t="str">
-        <v>BM-P149</v>
+        <v>BM-P147</v>
       </c>
       <c r="C130" t="str">
-        <v>B5-D16</v>
+        <v>B5-D14</v>
       </c>
       <c r="D130" t="str">
         <v>BÈ 5</v>
@@ -16938,13 +16938,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F130">
-        <v>-257.2</v>
+        <v>-64.46</v>
       </c>
       <c r="G130">
-        <v>-49.7</v>
+        <v>-76.96</v>
       </c>
       <c r="H130">
-        <v>662.27</v>
+        <v>662.44</v>
       </c>
       <c r="I130">
         <v>0.35</v>
@@ -16971,10 +16971,10 @@
         <v>207.6</v>
       </c>
       <c r="Q130">
-        <v>44.5</v>
+        <v>27.5</v>
       </c>
       <c r="R130">
-        <v>245.3</v>
+        <v>140.3</v>
       </c>
       <c r="S130">
         <v>69</v>
@@ -16992,10 +16992,10 @@
         <v>1</v>
       </c>
       <c r="X130">
-        <v>-15.7</v>
+        <v>-24.8</v>
       </c>
       <c r="Y130">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z130" t="str">
         <v>CÓ</v>
@@ -17012,10 +17012,10 @@
         <v>126</v>
       </c>
       <c r="B131" t="str">
-        <v>BM-P151</v>
+        <v>BM-P148</v>
       </c>
       <c r="C131" t="str">
-        <v>B5-D18</v>
+        <v>B5-D15</v>
       </c>
       <c r="D131" t="str">
         <v>BÈ 5</v>
@@ -17024,13 +17024,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F131">
-        <v>-270.24</v>
+        <v>-196.39</v>
       </c>
       <c r="G131">
-        <v>-24.68</v>
+        <v>-117.23</v>
       </c>
       <c r="H131">
-        <v>662.36</v>
+        <v>662.31</v>
       </c>
       <c r="I131">
         <v>0.35</v>
@@ -17057,10 +17057,10 @@
         <v>207.6</v>
       </c>
       <c r="Q131">
-        <v>78.07</v>
+        <v>32.5</v>
       </c>
       <c r="R131">
-        <v>252.3</v>
+        <v>200.3</v>
       </c>
       <c r="S131">
         <v>69</v>
@@ -17078,10 +17078,10 @@
         <v>1</v>
       </c>
       <c r="X131">
-        <v>-9.2</v>
+        <v>-21.1</v>
       </c>
       <c r="Y131">
-        <v>5.1</v>
+        <v>12.1</v>
       </c>
       <c r="Z131" t="str">
         <v>CÓ</v>
@@ -17098,10 +17098,10 @@
         <v>127</v>
       </c>
       <c r="B132" t="str">
-        <v>BM-P152</v>
+        <v>BM-P149</v>
       </c>
       <c r="C132" t="str">
-        <v>B5-D19</v>
+        <v>B5-D16</v>
       </c>
       <c r="D132" t="str">
         <v>BÈ 5</v>
@@ -17110,13 +17110,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F132">
-        <v>-157.06</v>
+        <v>-257.2</v>
       </c>
       <c r="G132">
-        <v>-121.46</v>
+        <v>-49.7</v>
       </c>
       <c r="H132">
-        <v>662.39</v>
+        <v>662.27</v>
       </c>
       <c r="I132">
         <v>0.35</v>
@@ -17143,10 +17143,10 @@
         <v>207.6</v>
       </c>
       <c r="Q132">
-        <v>26</v>
+        <v>44.5</v>
       </c>
       <c r="R132">
-        <v>190.3</v>
+        <v>245.3</v>
       </c>
       <c r="S132">
         <v>69</v>
@@ -17164,10 +17164,10 @@
         <v>1</v>
       </c>
       <c r="X132">
-        <v>-25.9</v>
+        <v>-15.7</v>
       </c>
       <c r="Y132">
-        <v>14.9</v>
+        <v>9</v>
       </c>
       <c r="Z132" t="str">
         <v>CÓ</v>
@@ -17176,7 +17176,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB132" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="133">
@@ -17184,10 +17184,10 @@
         <v>128</v>
       </c>
       <c r="B133" t="str">
-        <v>BM-P153</v>
+        <v>BM-P151</v>
       </c>
       <c r="C133" t="str">
-        <v>B5-D20</v>
+        <v>B5-D18</v>
       </c>
       <c r="D133" t="str">
         <v>BÈ 5</v>
@@ -17196,13 +17196,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F133">
-        <v>-200.97</v>
+        <v>-270.24</v>
       </c>
       <c r="G133">
-        <v>-116.63</v>
+        <v>-24.68</v>
       </c>
       <c r="H133">
-        <v>662.29</v>
+        <v>662.36</v>
       </c>
       <c r="I133">
         <v>0.35</v>
@@ -17229,10 +17229,10 @@
         <v>207.6</v>
       </c>
       <c r="Q133">
-        <v>44.5</v>
+        <v>78.07</v>
       </c>
       <c r="R133">
-        <v>190.3</v>
+        <v>252.3</v>
       </c>
       <c r="S133">
         <v>69</v>
@@ -17250,10 +17250,10 @@
         <v>1</v>
       </c>
       <c r="X133">
-        <v>-15.7</v>
+        <v>-9.2</v>
       </c>
       <c r="Y133">
-        <v>8.9</v>
+        <v>5.1</v>
       </c>
       <c r="Z133" t="str">
         <v>CÓ</v>
@@ -17270,10 +17270,10 @@
         <v>129</v>
       </c>
       <c r="B134" t="str">
-        <v>BM-P154</v>
+        <v>BM-P152</v>
       </c>
       <c r="C134" t="str">
-        <v>B5-D21</v>
+        <v>B5-D19</v>
       </c>
       <c r="D134" t="str">
         <v>BÈ 5</v>
@@ -17282,13 +17282,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F134">
-        <v>-76.13</v>
+        <v>-157.06</v>
       </c>
       <c r="G134">
-        <v>-87.58</v>
+        <v>-121.46</v>
       </c>
       <c r="H134">
-        <v>662.36</v>
+        <v>662.39</v>
       </c>
       <c r="I134">
         <v>0.35</v>
@@ -17315,10 +17315,10 @@
         <v>207.6</v>
       </c>
       <c r="Q134">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="R134">
-        <v>140.4</v>
+        <v>190.3</v>
       </c>
       <c r="S134">
         <v>69</v>
@@ -17336,10 +17336,10 @@
         <v>1</v>
       </c>
       <c r="X134">
-        <v>-22.1</v>
+        <v>-25.9</v>
       </c>
       <c r="Y134">
-        <v>12.6</v>
+        <v>14.9</v>
       </c>
       <c r="Z134" t="str">
         <v>CÓ</v>
@@ -17348,7 +17348,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB134" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
       </c>
     </row>
     <row r="135">
@@ -17356,10 +17356,10 @@
         <v>130</v>
       </c>
       <c r="B135" t="str">
-        <v>BM-P155</v>
+        <v>BM-P153</v>
       </c>
       <c r="C135" t="str">
-        <v>B5-D23</v>
+        <v>B5-D20</v>
       </c>
       <c r="D135" t="str">
         <v>BÈ 5</v>
@@ -17368,13 +17368,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F135">
-        <v>-155.77</v>
+        <v>-200.97</v>
       </c>
       <c r="G135">
-        <v>120.08</v>
+        <v>-116.63</v>
       </c>
       <c r="H135">
-        <v>662.35</v>
+        <v>662.29</v>
       </c>
       <c r="I135">
         <v>0.35</v>
@@ -17401,10 +17401,10 @@
         <v>207.6</v>
       </c>
       <c r="Q135">
-        <v>52.5</v>
+        <v>44.5</v>
       </c>
       <c r="R135">
-        <v>350.3</v>
+        <v>190.3</v>
       </c>
       <c r="S135">
         <v>69</v>
@@ -17422,10 +17422,10 @@
         <v>1</v>
       </c>
       <c r="X135">
-        <v>-13.5</v>
+        <v>-15.7</v>
       </c>
       <c r="Y135">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="Z135" t="str">
         <v>CÓ</v>
@@ -17442,10 +17442,10 @@
         <v>131</v>
       </c>
       <c r="B136" t="str">
-        <v>BM-P156</v>
+        <v>BM-P154</v>
       </c>
       <c r="C136" t="str">
-        <v>B5-D24</v>
+        <v>B5-D21</v>
       </c>
       <c r="D136" t="str">
         <v>BÈ 5</v>
@@ -17454,13 +17454,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F136">
-        <v>-23.74</v>
+        <v>-76.13</v>
       </c>
       <c r="G136">
-        <v>-40.16</v>
+        <v>-87.58</v>
       </c>
       <c r="H136">
-        <v>663.65</v>
+        <v>662.36</v>
       </c>
       <c r="I136">
         <v>0.35</v>
@@ -17487,10 +17487,10 @@
         <v>207.6</v>
       </c>
       <c r="Q136">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="R136">
-        <v>107.8</v>
+        <v>140.4</v>
       </c>
       <c r="S136">
         <v>69</v>
@@ -17508,19 +17508,19 @@
         <v>1</v>
       </c>
       <c r="X136">
-        <v>-10</v>
+        <v>-22.1</v>
       </c>
       <c r="Y136">
-        <v>4.1</v>
+        <v>12.6</v>
       </c>
       <c r="Z136" t="str">
-        <v>không</v>
+        <v>CÓ</v>
       </c>
       <c r="AA136" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB136" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="137">
@@ -17528,10 +17528,10 @@
         <v>132</v>
       </c>
       <c r="B137" t="str">
-        <v>BM-P157</v>
+        <v>BM-P155</v>
       </c>
       <c r="C137" t="str">
-        <v>B5-D25</v>
+        <v>B5-D23</v>
       </c>
       <c r="D137" t="str">
         <v>BÈ 5</v>
@@ -17540,13 +17540,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F137">
-        <v>-51.6</v>
+        <v>-155.77</v>
       </c>
       <c r="G137">
-        <v>-62.2</v>
+        <v>120.08</v>
       </c>
       <c r="H137">
-        <v>662.28</v>
+        <v>662.35</v>
       </c>
       <c r="I137">
         <v>0.35</v>
@@ -17573,10 +17573,10 @@
         <v>207.6</v>
       </c>
       <c r="Q137">
-        <v>36.5</v>
+        <v>52.5</v>
       </c>
       <c r="R137">
-        <v>120.3</v>
+        <v>350.3</v>
       </c>
       <c r="S137">
         <v>69</v>
@@ -17594,10 +17594,10 @@
         <v>1</v>
       </c>
       <c r="X137">
-        <v>-18.9</v>
+        <v>-13.5</v>
       </c>
       <c r="Y137">
-        <v>10.9</v>
+        <v>7.5</v>
       </c>
       <c r="Z137" t="str">
         <v>CÓ</v>
@@ -17614,10 +17614,10 @@
         <v>133</v>
       </c>
       <c r="B138" t="str">
-        <v>BM-P158</v>
+        <v>BM-P156</v>
       </c>
       <c r="C138" t="str">
-        <v>B5-D27</v>
+        <v>B5-D24</v>
       </c>
       <c r="D138" t="str">
         <v>BÈ 5</v>
@@ -17626,13 +17626,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F138">
-        <v>-90.74</v>
+        <v>-23.74</v>
       </c>
       <c r="G138">
-        <v>-104.05</v>
+        <v>-40.16</v>
       </c>
       <c r="H138">
-        <v>662.47</v>
+        <v>663.65</v>
       </c>
       <c r="I138">
         <v>0.35</v>
@@ -17659,10 +17659,10 @@
         <v>207.6</v>
       </c>
       <c r="Q138">
-        <v>41.5</v>
+        <v>79</v>
       </c>
       <c r="R138">
-        <v>125.3</v>
+        <v>107.8</v>
       </c>
       <c r="S138">
         <v>69</v>
@@ -17680,19 +17680,19 @@
         <v>1</v>
       </c>
       <c r="X138">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="Y138">
-        <v>9.3</v>
+        <v>4.1</v>
       </c>
       <c r="Z138" t="str">
-        <v>CÓ</v>
+        <v>không</v>
       </c>
       <c r="AA138" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB138" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="139">
@@ -17700,10 +17700,10 @@
         <v>134</v>
       </c>
       <c r="B139" t="str">
-        <v>BM-P159</v>
+        <v>BM-P157</v>
       </c>
       <c r="C139" t="str">
-        <v>B5-D28</v>
+        <v>B5-D25</v>
       </c>
       <c r="D139" t="str">
         <v>BÈ 5</v>
@@ -17712,13 +17712,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F139">
-        <v>-180.49</v>
+        <v>-51.6</v>
       </c>
       <c r="G139">
-        <v>-118.86</v>
+        <v>-62.2</v>
       </c>
       <c r="H139">
-        <v>662.3</v>
+        <v>662.28</v>
       </c>
       <c r="I139">
         <v>0.35</v>
@@ -17745,10 +17745,10 @@
         <v>207.6</v>
       </c>
       <c r="Q139">
-        <v>18.5</v>
+        <v>36.5</v>
       </c>
       <c r="R139">
-        <v>190.3</v>
+        <v>120.3</v>
       </c>
       <c r="S139">
         <v>69</v>
@@ -17766,10 +17766,10 @@
         <v>1</v>
       </c>
       <c r="X139">
-        <v>-34.2</v>
+        <v>-18.9</v>
       </c>
       <c r="Y139">
-        <v>20.7</v>
+        <v>10.9</v>
       </c>
       <c r="Z139" t="str">
         <v>CÓ</v>
@@ -17778,7 +17778,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB139" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="140">
@@ -17786,10 +17786,10 @@
         <v>135</v>
       </c>
       <c r="B140" t="str">
-        <v>BM-P160</v>
+        <v>BM-P158</v>
       </c>
       <c r="C140" t="str">
-        <v>B5-D29</v>
+        <v>B5-D27</v>
       </c>
       <c r="D140" t="str">
         <v>BÈ 5</v>
@@ -17798,13 +17798,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F140">
-        <v>-267.59</v>
+        <v>-90.74</v>
       </c>
       <c r="G140">
-        <v>-28.54</v>
+        <v>-104.05</v>
       </c>
       <c r="H140">
-        <v>662.32</v>
+        <v>662.47</v>
       </c>
       <c r="I140">
         <v>0.35</v>
@@ -17831,10 +17831,10 @@
         <v>207.6</v>
       </c>
       <c r="Q140">
-        <v>44.5</v>
+        <v>41.5</v>
       </c>
       <c r="R140">
-        <v>255.3</v>
+        <v>125.3</v>
       </c>
       <c r="S140">
         <v>69</v>
@@ -17852,10 +17852,10 @@
         <v>1</v>
       </c>
       <c r="X140">
-        <v>-15.8</v>
+        <v>-17</v>
       </c>
       <c r="Y140">
-        <v>8.9</v>
+        <v>9.3</v>
       </c>
       <c r="Z140" t="str">
         <v>CÓ</v>
@@ -17872,10 +17872,10 @@
         <v>136</v>
       </c>
       <c r="B141" t="str">
-        <v>BM-P161</v>
+        <v>BM-P159</v>
       </c>
       <c r="C141" t="str">
-        <v>B5-D30</v>
+        <v>B5-D28</v>
       </c>
       <c r="D141" t="str">
         <v>BÈ 5</v>
@@ -17884,13 +17884,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F141">
-        <v>-248.38</v>
+        <v>-180.49</v>
       </c>
       <c r="G141">
-        <v>-67.56</v>
+        <v>-118.86</v>
       </c>
       <c r="H141">
-        <v>662.29</v>
+        <v>662.3</v>
       </c>
       <c r="I141">
         <v>0.35</v>
@@ -17917,10 +17917,10 @@
         <v>207.6</v>
       </c>
       <c r="Q141">
-        <v>45.5</v>
+        <v>18.5</v>
       </c>
       <c r="R141">
-        <v>240.3</v>
+        <v>190.3</v>
       </c>
       <c r="S141">
         <v>69</v>
@@ -17938,10 +17938,10 @@
         <v>1</v>
       </c>
       <c r="X141">
-        <v>-15.4</v>
+        <v>-34.2</v>
       </c>
       <c r="Y141">
-        <v>8.8</v>
+        <v>20.7</v>
       </c>
       <c r="Z141" t="str">
         <v>CÓ</v>
@@ -17950,7 +17950,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB141" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
       </c>
     </row>
     <row r="142">
@@ -17958,10 +17958,10 @@
         <v>137</v>
       </c>
       <c r="B142" t="str">
-        <v>BM-P162</v>
+        <v>BM-P160</v>
       </c>
       <c r="C142" t="str">
-        <v>B5-D31</v>
+        <v>B5-D29</v>
       </c>
       <c r="D142" t="str">
         <v>BÈ 5</v>
@@ -17970,13 +17970,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F142">
-        <v>-284.12</v>
+        <v>-267.59</v>
       </c>
       <c r="G142">
-        <v>12.11</v>
+        <v>-28.54</v>
       </c>
       <c r="H142">
-        <v>662.29</v>
+        <v>662.32</v>
       </c>
       <c r="I142">
         <v>0.35</v>
@@ -18003,10 +18003,10 @@
         <v>207.6</v>
       </c>
       <c r="Q142">
-        <v>79</v>
+        <v>44.5</v>
       </c>
       <c r="R142">
-        <v>260.3</v>
+        <v>255.3</v>
       </c>
       <c r="S142">
         <v>69</v>
@@ -18024,10 +18024,10 @@
         <v>1</v>
       </c>
       <c r="X142">
-        <v>-9</v>
+        <v>-15.8</v>
       </c>
       <c r="Y142">
-        <v>5.1</v>
+        <v>8.9</v>
       </c>
       <c r="Z142" t="str">
         <v>CÓ</v>
@@ -18044,10 +18044,10 @@
         <v>138</v>
       </c>
       <c r="B143" t="str">
-        <v>BM-P163</v>
+        <v>BM-P161</v>
       </c>
       <c r="C143" t="str">
-        <v>B5-D32</v>
+        <v>B5-D30</v>
       </c>
       <c r="D143" t="str">
         <v>BÈ 5</v>
@@ -18056,13 +18056,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F143">
-        <v>-166.36</v>
+        <v>-248.38</v>
       </c>
       <c r="G143">
-        <v>121.17</v>
+        <v>-67.56</v>
       </c>
       <c r="H143">
-        <v>662.34</v>
+        <v>662.29</v>
       </c>
       <c r="I143">
         <v>0.35</v>
@@ -18089,10 +18089,10 @@
         <v>207.6</v>
       </c>
       <c r="Q143">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="R143">
-        <v>5.3</v>
+        <v>240.3</v>
       </c>
       <c r="S143">
         <v>69</v>
@@ -18110,10 +18110,10 @@
         <v>1</v>
       </c>
       <c r="X143">
-        <v>-12.2</v>
+        <v>-15.4</v>
       </c>
       <c r="Y143">
-        <v>6.8</v>
+        <v>8.8</v>
       </c>
       <c r="Z143" t="str">
         <v>CÓ</v>
@@ -18130,10 +18130,10 @@
         <v>139</v>
       </c>
       <c r="B144" t="str">
-        <v>BM-P164</v>
+        <v>BM-P162</v>
       </c>
       <c r="C144" t="str">
-        <v>B5-D33</v>
+        <v>B5-D31</v>
       </c>
       <c r="D144" t="str">
         <v>BÈ 5</v>
@@ -18142,13 +18142,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F144">
-        <v>-79.68</v>
+        <v>-284.12</v>
       </c>
       <c r="G144">
-        <v>-91.14</v>
+        <v>12.11</v>
       </c>
       <c r="H144">
-        <v>662.46</v>
+        <v>662.29</v>
       </c>
       <c r="I144">
         <v>0.35</v>
@@ -18175,10 +18175,10 @@
         <v>207.6</v>
       </c>
       <c r="Q144">
-        <v>32.99</v>
+        <v>79</v>
       </c>
       <c r="R144">
-        <v>135.3</v>
+        <v>260.3</v>
       </c>
       <c r="S144">
         <v>69</v>
@@ -18196,10 +18196,10 @@
         <v>1</v>
       </c>
       <c r="X144">
-        <v>-21.1</v>
+        <v>-9</v>
       </c>
       <c r="Y144">
-        <v>11.7</v>
+        <v>5.1</v>
       </c>
       <c r="Z144" t="str">
         <v>CÓ</v>
@@ -18216,10 +18216,10 @@
         <v>140</v>
       </c>
       <c r="B145" t="str">
-        <v>BM-P165</v>
+        <v>BM-P163</v>
       </c>
       <c r="C145" t="str">
-        <v>B5-D35</v>
+        <v>B5-D32</v>
       </c>
       <c r="D145" t="str">
         <v>BÈ 5</v>
@@ -18228,13 +18228,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F145">
-        <v>-252.34</v>
+        <v>-166.36</v>
       </c>
       <c r="G145">
-        <v>-60.61</v>
+        <v>121.17</v>
       </c>
       <c r="H145">
-        <v>662.29</v>
+        <v>662.34</v>
       </c>
       <c r="I145">
         <v>0.35</v>
@@ -18261,10 +18261,10 @@
         <v>207.6</v>
       </c>
       <c r="Q145">
-        <v>45.5</v>
+        <v>58</v>
       </c>
       <c r="R145">
-        <v>240.3</v>
+        <v>5.3</v>
       </c>
       <c r="S145">
         <v>69</v>
@@ -18282,10 +18282,10 @@
         <v>1</v>
       </c>
       <c r="X145">
-        <v>-15.4</v>
+        <v>-12.2</v>
       </c>
       <c r="Y145">
-        <v>8.8</v>
+        <v>6.8</v>
       </c>
       <c r="Z145" t="str">
         <v>CÓ</v>
@@ -18302,25 +18302,25 @@
         <v>141</v>
       </c>
       <c r="B146" t="str">
-        <v>BM-P166</v>
+        <v>BM-P164</v>
       </c>
       <c r="C146" t="str">
-        <v>B6-D01</v>
+        <v>B5-D33</v>
       </c>
       <c r="D146" t="str">
-        <v>BÈ 6</v>
+        <v>BÈ 5</v>
       </c>
       <c r="E146" t="str">
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F146">
-        <v>-316.94</v>
+        <v>-79.68</v>
       </c>
       <c r="G146">
-        <v>62.16</v>
+        <v>-91.14</v>
       </c>
       <c r="H146">
-        <v>662.4</v>
+        <v>662.46</v>
       </c>
       <c r="I146">
         <v>0.35</v>
@@ -18347,31 +18347,31 @@
         <v>207.6</v>
       </c>
       <c r="Q146">
-        <v>24</v>
+        <v>32.99</v>
       </c>
       <c r="R146">
-        <v>185</v>
+        <v>135.3</v>
       </c>
       <c r="S146">
-        <v>75.1</v>
+        <v>69</v>
       </c>
       <c r="T146">
         <v>81.9</v>
       </c>
       <c r="U146">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="V146">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="W146">
         <v>1</v>
       </c>
       <c r="X146">
-        <v>-27.8</v>
+        <v>-21.1</v>
       </c>
       <c r="Y146">
-        <v>16</v>
+        <v>11.7</v>
       </c>
       <c r="Z146" t="str">
         <v>CÓ</v>
@@ -18380,7 +18380,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB146" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="147">
@@ -18388,25 +18388,25 @@
         <v>142</v>
       </c>
       <c r="B147" t="str">
-        <v>BM-P167</v>
+        <v>BM-P165</v>
       </c>
       <c r="C147" t="str">
-        <v>B6-D02</v>
+        <v>B5-D35</v>
       </c>
       <c r="D147" t="str">
-        <v>BÈ 6</v>
+        <v>BÈ 5</v>
       </c>
       <c r="E147" t="str">
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F147">
-        <v>-352.96</v>
+        <v>-252.34</v>
       </c>
       <c r="G147">
-        <v>286.03</v>
+        <v>-60.61</v>
       </c>
       <c r="H147">
-        <v>662.26</v>
+        <v>662.29</v>
       </c>
       <c r="I147">
         <v>0.35</v>
@@ -18433,31 +18433,31 @@
         <v>207.6</v>
       </c>
       <c r="Q147">
-        <v>64</v>
+        <v>45.5</v>
       </c>
       <c r="R147">
-        <v>35</v>
+        <v>240.3</v>
       </c>
       <c r="S147">
-        <v>75.1</v>
+        <v>69</v>
       </c>
       <c r="T147">
         <v>81.9</v>
       </c>
       <c r="U147">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="V147">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="W147">
         <v>1</v>
       </c>
       <c r="X147">
-        <v>-11.1</v>
+        <v>-15.4</v>
       </c>
       <c r="Y147">
-        <v>6.3</v>
+        <v>8.8</v>
       </c>
       <c r="Z147" t="str">
         <v>CÓ</v>
@@ -18474,10 +18474,10 @@
         <v>143</v>
       </c>
       <c r="B148" t="str">
-        <v>BM-P168</v>
+        <v>BM-P166</v>
       </c>
       <c r="C148" t="str">
-        <v>B6-D03</v>
+        <v>B6-D01</v>
       </c>
       <c r="D148" t="str">
         <v>BÈ 6</v>
@@ -18486,13 +18486,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F148">
-        <v>-186.38</v>
+        <v>-316.94</v>
       </c>
       <c r="G148">
-        <v>152.59</v>
+        <v>62.16</v>
       </c>
       <c r="H148">
-        <v>662.31</v>
+        <v>662.4</v>
       </c>
       <c r="I148">
         <v>0.35</v>
@@ -18519,10 +18519,10 @@
         <v>207.6</v>
       </c>
       <c r="Q148">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="R148">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="S148">
         <v>75.1</v>
@@ -18540,10 +18540,10 @@
         <v>1</v>
       </c>
       <c r="X148">
-        <v>-12.2</v>
+        <v>-27.8</v>
       </c>
       <c r="Y148">
-        <v>6.9</v>
+        <v>16</v>
       </c>
       <c r="Z148" t="str">
         <v>CÓ</v>
@@ -18552,7 +18552,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AB148" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ; Cáp chúc xuống dốc khi nước thấp: kiểm tra cáp không tì vào mặt đất / mũ cọc</v>
       </c>
     </row>
     <row r="149">
@@ -18560,10 +18560,10 @@
         <v>144</v>
       </c>
       <c r="B149" t="str">
-        <v>BM-P169</v>
+        <v>BM-P167</v>
       </c>
       <c r="C149" t="str">
-        <v>B6-D04</v>
+        <v>B6-D02</v>
       </c>
       <c r="D149" t="str">
         <v>BÈ 6</v>
@@ -18572,13 +18572,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F149">
-        <v>-469.17</v>
+        <v>-352.96</v>
       </c>
       <c r="G149">
-        <v>155</v>
+        <v>286.03</v>
       </c>
       <c r="H149">
-        <v>662.32</v>
+        <v>662.26</v>
       </c>
       <c r="I149">
         <v>0.35</v>
@@ -18605,10 +18605,10 @@
         <v>207.6</v>
       </c>
       <c r="Q149">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="R149">
-        <v>185</v>
+        <v>35</v>
       </c>
       <c r="S149">
         <v>75.1</v>
@@ -18626,10 +18626,10 @@
         <v>1</v>
       </c>
       <c r="X149">
-        <v>-18.8</v>
+        <v>-11.1</v>
       </c>
       <c r="Y149">
-        <v>10.7</v>
+        <v>6.3</v>
       </c>
       <c r="Z149" t="str">
         <v>CÓ</v>
@@ -18646,10 +18646,10 @@
         <v>145</v>
       </c>
       <c r="B150" t="str">
-        <v>BM-P170</v>
+        <v>BM-P168</v>
       </c>
       <c r="C150" t="str">
-        <v>B6-D05</v>
+        <v>B6-D03</v>
       </c>
       <c r="D150" t="str">
         <v>BÈ 6</v>
@@ -18658,13 +18658,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F150">
-        <v>-425.91</v>
+        <v>-186.38</v>
       </c>
       <c r="G150">
-        <v>122.6</v>
+        <v>152.59</v>
       </c>
       <c r="H150">
-        <v>662.26</v>
+        <v>662.31</v>
       </c>
       <c r="I150">
         <v>0.35</v>
@@ -18691,10 +18691,10 @@
         <v>207.6</v>
       </c>
       <c r="Q150">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="R150">
-        <v>245</v>
+        <v>65</v>
       </c>
       <c r="S150">
         <v>75.1</v>
@@ -18712,10 +18712,10 @@
         <v>1</v>
       </c>
       <c r="X150">
-        <v>-17.8</v>
+        <v>-12.2</v>
       </c>
       <c r="Y150">
-        <v>10.2</v>
+        <v>6.9</v>
       </c>
       <c r="Z150" t="str">
         <v>CÓ</v>
@@ -18732,10 +18732,10 @@
         <v>146</v>
       </c>
       <c r="B151" t="str">
-        <v>BM-P172</v>
+        <v>BM-P169</v>
       </c>
       <c r="C151" t="str">
-        <v>B6-D07</v>
+        <v>B6-D04</v>
       </c>
       <c r="D151" t="str">
         <v>BÈ 6</v>
@@ -18744,13 +18744,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F151">
-        <v>-297.12</v>
+        <v>-469.17</v>
       </c>
       <c r="G151">
-        <v>245.07</v>
+        <v>155</v>
       </c>
       <c r="H151">
-        <v>662.51</v>
+        <v>662.32</v>
       </c>
       <c r="I151">
         <v>0.35</v>
@@ -18777,10 +18777,10 @@
         <v>207.6</v>
       </c>
       <c r="Q151">
-        <v>66.5</v>
+        <v>37</v>
       </c>
       <c r="R151">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="S151">
         <v>75.1</v>
@@ -18798,10 +18798,10 @@
         <v>1</v>
       </c>
       <c r="X151">
-        <v>-10.9</v>
+        <v>-18.8</v>
       </c>
       <c r="Y151">
-        <v>5.8</v>
+        <v>10.7</v>
       </c>
       <c r="Z151" t="str">
         <v>CÓ</v>
@@ -18818,10 +18818,10 @@
         <v>147</v>
       </c>
       <c r="B152" t="str">
-        <v>BM-P173</v>
+        <v>BM-P170</v>
       </c>
       <c r="C152" t="str">
-        <v>B6-D08</v>
+        <v>B6-D05</v>
       </c>
       <c r="D152" t="str">
         <v>BÈ 6</v>
@@ -18830,13 +18830,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F152">
-        <v>-453.74</v>
+        <v>-425.91</v>
       </c>
       <c r="G152">
-        <v>332.65</v>
+        <v>122.6</v>
       </c>
       <c r="H152">
-        <v>662.5</v>
+        <v>662.26</v>
       </c>
       <c r="I152">
         <v>0.35</v>
@@ -18863,10 +18863,10 @@
         <v>207.6</v>
       </c>
       <c r="Q152">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="R152">
-        <v>5</v>
+        <v>245</v>
       </c>
       <c r="S152">
         <v>75.1</v>
@@ -18884,10 +18884,10 @@
         <v>1</v>
       </c>
       <c r="X152">
-        <v>-9.8</v>
+        <v>-17.8</v>
       </c>
       <c r="Y152">
-        <v>5.3</v>
+        <v>10.2</v>
       </c>
       <c r="Z152" t="str">
         <v>CÓ</v>
@@ -18904,10 +18904,10 @@
         <v>148</v>
       </c>
       <c r="B153" t="str">
-        <v>BM-P174</v>
+        <v>BM-P172</v>
       </c>
       <c r="C153" t="str">
-        <v>B6-D09</v>
+        <v>B6-D07</v>
       </c>
       <c r="D153" t="str">
         <v>BÈ 6</v>
@@ -18916,13 +18916,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F153">
-        <v>-297.58</v>
+        <v>-297.12</v>
       </c>
       <c r="G153">
-        <v>51.33</v>
+        <v>245.07</v>
       </c>
       <c r="H153">
-        <v>662.43</v>
+        <v>662.51</v>
       </c>
       <c r="I153">
         <v>0.35</v>
@@ -18949,10 +18949,10 @@
         <v>207.6</v>
       </c>
       <c r="Q153">
-        <v>30.49</v>
+        <v>66.5</v>
       </c>
       <c r="R153">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="S153">
         <v>75.1</v>
@@ -18970,10 +18970,10 @@
         <v>1</v>
       </c>
       <c r="X153">
-        <v>-22.6</v>
+        <v>-10.9</v>
       </c>
       <c r="Y153">
-        <v>12.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z153" t="str">
         <v>CÓ</v>
@@ -18990,10 +18990,10 @@
         <v>149</v>
       </c>
       <c r="B154" t="str">
-        <v>BM-P175</v>
+        <v>BM-P173</v>
       </c>
       <c r="C154" t="str">
-        <v>B6-D10</v>
+        <v>B6-D08</v>
       </c>
       <c r="D154" t="str">
         <v>BÈ 6</v>
@@ -19002,13 +19002,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F154">
-        <v>-343.33</v>
+        <v>-453.74</v>
       </c>
       <c r="G154">
-        <v>58.55</v>
+        <v>332.65</v>
       </c>
       <c r="H154">
-        <v>662.33</v>
+        <v>662.5</v>
       </c>
       <c r="I154">
         <v>0.35</v>
@@ -19035,10 +19035,10 @@
         <v>207.6</v>
       </c>
       <c r="Q154">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="R154">
-        <v>170</v>
+        <v>5</v>
       </c>
       <c r="S154">
         <v>75.1</v>
@@ -19056,10 +19056,10 @@
         <v>1</v>
       </c>
       <c r="X154">
-        <v>-12.9</v>
+        <v>-9.8</v>
       </c>
       <c r="Y154">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z154" t="str">
         <v>CÓ</v>
@@ -19076,10 +19076,10 @@
         <v>150</v>
       </c>
       <c r="B155" t="str">
-        <v>BM-P176</v>
+        <v>BM-P174</v>
       </c>
       <c r="C155" t="str">
-        <v>B6-D11</v>
+        <v>B6-D09</v>
       </c>
       <c r="D155" t="str">
         <v>BÈ 6</v>
@@ -19088,13 +19088,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F155">
-        <v>-313.09</v>
+        <v>-297.58</v>
       </c>
       <c r="G155">
-        <v>253.55</v>
+        <v>51.33</v>
       </c>
       <c r="H155">
-        <v>662.29</v>
+        <v>662.43</v>
       </c>
       <c r="I155">
         <v>0.35</v>
@@ -19121,10 +19121,10 @@
         <v>207.6</v>
       </c>
       <c r="Q155">
-        <v>60.5</v>
+        <v>30.49</v>
       </c>
       <c r="R155">
-        <v>40</v>
+        <v>215</v>
       </c>
       <c r="S155">
         <v>75.1</v>
@@ -19142,10 +19142,10 @@
         <v>1</v>
       </c>
       <c r="X155">
-        <v>-11.7</v>
+        <v>-22.6</v>
       </c>
       <c r="Y155">
-        <v>6.6</v>
+        <v>12.7</v>
       </c>
       <c r="Z155" t="str">
         <v>CÓ</v>
@@ -19162,10 +19162,10 @@
         <v>151</v>
       </c>
       <c r="B156" t="str">
-        <v>BM-P177</v>
+        <v>BM-P175</v>
       </c>
       <c r="C156" t="str">
-        <v>B6-D12</v>
+        <v>B6-D10</v>
       </c>
       <c r="D156" t="str">
         <v>BÈ 6</v>
@@ -19174,13 +19174,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F156">
-        <v>-391.49</v>
+        <v>-343.33</v>
       </c>
       <c r="G156">
-        <v>311.18</v>
+        <v>58.55</v>
       </c>
       <c r="H156">
-        <v>662.54</v>
+        <v>662.33</v>
       </c>
       <c r="I156">
         <v>0.35</v>
@@ -19207,10 +19207,10 @@
         <v>207.6</v>
       </c>
       <c r="Q156">
-        <v>62.5</v>
+        <v>55</v>
       </c>
       <c r="R156">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="S156">
         <v>75.1</v>
@@ -19228,10 +19228,10 @@
         <v>1</v>
       </c>
       <c r="X156">
-        <v>-11.6</v>
+        <v>-12.9</v>
       </c>
       <c r="Y156">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="Z156" t="str">
         <v>CÓ</v>
@@ -19248,10 +19248,10 @@
         <v>152</v>
       </c>
       <c r="B157" t="str">
-        <v>BM-P179</v>
+        <v>BM-P176</v>
       </c>
       <c r="C157" t="str">
-        <v>B6-D14</v>
+        <v>B6-D11</v>
       </c>
       <c r="D157" t="str">
         <v>BÈ 6</v>
@@ -19260,13 +19260,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F157">
-        <v>-444.01</v>
+        <v>-313.09</v>
       </c>
       <c r="G157">
-        <v>142.95</v>
+        <v>253.55</v>
       </c>
       <c r="H157">
-        <v>662.33</v>
+        <v>662.29</v>
       </c>
       <c r="I157">
         <v>0.35</v>
@@ -19293,10 +19293,10 @@
         <v>207.6</v>
       </c>
       <c r="Q157">
-        <v>27.5</v>
+        <v>60.5</v>
       </c>
       <c r="R157">
-        <v>215</v>
+        <v>40</v>
       </c>
       <c r="S157">
         <v>75.1</v>
@@ -19314,10 +19314,10 @@
         <v>1</v>
       </c>
       <c r="X157">
-        <v>-24.6</v>
+        <v>-11.7</v>
       </c>
       <c r="Y157">
-        <v>14.2</v>
+        <v>6.6</v>
       </c>
       <c r="Z157" t="str">
         <v>CÓ</v>
@@ -19334,10 +19334,10 @@
         <v>153</v>
       </c>
       <c r="B158" t="str">
-        <v>BM-P180</v>
+        <v>BM-P177</v>
       </c>
       <c r="C158" t="str">
-        <v>B6-D15</v>
+        <v>B6-D12</v>
       </c>
       <c r="D158" t="str">
         <v>BÈ 6</v>
@@ -19346,13 +19346,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F158">
-        <v>-180.83</v>
+        <v>-391.49</v>
       </c>
       <c r="G158">
-        <v>129.89</v>
+        <v>311.18</v>
       </c>
       <c r="H158">
-        <v>662.43</v>
+        <v>662.54</v>
       </c>
       <c r="I158">
         <v>0.35</v>
@@ -19379,10 +19379,10 @@
         <v>207.6</v>
       </c>
       <c r="Q158">
-        <v>48.5</v>
+        <v>62.5</v>
       </c>
       <c r="R158">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="S158">
         <v>75.1</v>
@@ -19400,10 +19400,10 @@
         <v>1</v>
       </c>
       <c r="X158">
-        <v>-14.7</v>
+        <v>-11.6</v>
       </c>
       <c r="Y158">
-        <v>8.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z158" t="str">
         <v>CÓ</v>
@@ -19420,10 +19420,10 @@
         <v>154</v>
       </c>
       <c r="B159" t="str">
-        <v>BM-P181</v>
+        <v>BM-P179</v>
       </c>
       <c r="C159" t="str">
-        <v>B6-D16</v>
+        <v>B6-D14</v>
       </c>
       <c r="D159" t="str">
         <v>BÈ 6</v>
@@ -19432,13 +19432,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F159">
-        <v>-201.45</v>
+        <v>-444.01</v>
       </c>
       <c r="G159">
-        <v>181.83</v>
+        <v>142.95</v>
       </c>
       <c r="H159">
-        <v>662.32</v>
+        <v>662.33</v>
       </c>
       <c r="I159">
         <v>0.35</v>
@@ -19465,10 +19465,10 @@
         <v>207.6</v>
       </c>
       <c r="Q159">
-        <v>80</v>
+        <v>27.5</v>
       </c>
       <c r="R159">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="S159">
         <v>75.1</v>
@@ -19486,10 +19486,10 @@
         <v>1</v>
       </c>
       <c r="X159">
-        <v>-8.9</v>
+        <v>-24.6</v>
       </c>
       <c r="Y159">
-        <v>5</v>
+        <v>14.2</v>
       </c>
       <c r="Z159" t="str">
         <v>CÓ</v>
@@ -19506,10 +19506,10 @@
         <v>155</v>
       </c>
       <c r="B160" t="str">
-        <v>BM-P182</v>
+        <v>BM-P180</v>
       </c>
       <c r="C160" t="str">
-        <v>B6-D17</v>
+        <v>B6-D15</v>
       </c>
       <c r="D160" t="str">
         <v>BÈ 6</v>
@@ -19518,13 +19518,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F160">
-        <v>-302.89</v>
+        <v>-180.83</v>
       </c>
       <c r="G160">
-        <v>246.42</v>
+        <v>129.89</v>
       </c>
       <c r="H160">
-        <v>662.45</v>
+        <v>662.43</v>
       </c>
       <c r="I160">
         <v>0.35</v>
@@ -19551,10 +19551,10 @@
         <v>207.6</v>
       </c>
       <c r="Q160">
-        <v>60.5</v>
+        <v>48.5</v>
       </c>
       <c r="R160">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="S160">
         <v>75.1</v>
@@ -19572,10 +19572,10 @@
         <v>1</v>
       </c>
       <c r="X160">
-        <v>-11.9</v>
+        <v>-14.7</v>
       </c>
       <c r="Y160">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="Z160" t="str">
         <v>CÓ</v>
@@ -19592,10 +19592,10 @@
         <v>156</v>
       </c>
       <c r="B161" t="str">
-        <v>BM-P183</v>
+        <v>BM-P181</v>
       </c>
       <c r="C161" t="str">
-        <v>B6-D18</v>
+        <v>B6-D16</v>
       </c>
       <c r="D161" t="str">
         <v>BÈ 6</v>
@@ -19604,13 +19604,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F161">
-        <v>-312.26</v>
+        <v>-201.45</v>
       </c>
       <c r="G161">
-        <v>60.96</v>
+        <v>181.83</v>
       </c>
       <c r="H161">
-        <v>662.34</v>
+        <v>662.32</v>
       </c>
       <c r="I161">
         <v>0.35</v>
@@ -19637,10 +19637,10 @@
         <v>207.6</v>
       </c>
       <c r="Q161">
-        <v>31.5</v>
+        <v>80</v>
       </c>
       <c r="R161">
-        <v>205</v>
+        <v>70</v>
       </c>
       <c r="S161">
         <v>75.1</v>
@@ -19658,10 +19658,10 @@
         <v>1</v>
       </c>
       <c r="X161">
-        <v>-21.8</v>
+        <v>-8.9</v>
       </c>
       <c r="Y161">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="Z161" t="str">
         <v>CÓ</v>
@@ -19678,10 +19678,10 @@
         <v>157</v>
       </c>
       <c r="B162" t="str">
-        <v>BM-P184</v>
+        <v>BM-P182</v>
       </c>
       <c r="C162" t="str">
-        <v>B6-D19</v>
+        <v>B6-D17</v>
       </c>
       <c r="D162" t="str">
         <v>BÈ 6</v>
@@ -19690,13 +19690,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F162">
-        <v>-420.67</v>
+        <v>-302.89</v>
       </c>
       <c r="G162">
-        <v>103.07</v>
+        <v>246.42</v>
       </c>
       <c r="H162">
-        <v>662.35</v>
+        <v>662.45</v>
       </c>
       <c r="I162">
         <v>0.35</v>
@@ -19723,10 +19723,10 @@
         <v>207.6</v>
       </c>
       <c r="Q162">
-        <v>54</v>
+        <v>60.5</v>
       </c>
       <c r="R162">
-        <v>245</v>
+        <v>30</v>
       </c>
       <c r="S162">
         <v>75.1</v>
@@ -19744,10 +19744,10 @@
         <v>1</v>
       </c>
       <c r="X162">
-        <v>-13.1</v>
+        <v>-11.9</v>
       </c>
       <c r="Y162">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="Z162" t="str">
         <v>CÓ</v>
@@ -19764,10 +19764,10 @@
         <v>158</v>
       </c>
       <c r="B163" t="str">
-        <v>BM-P185</v>
+        <v>BM-P183</v>
       </c>
       <c r="C163" t="str">
-        <v>B6-D20</v>
+        <v>B6-D18</v>
       </c>
       <c r="D163" t="str">
         <v>BÈ 6</v>
@@ -19776,13 +19776,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F163">
-        <v>-185.46</v>
+        <v>-312.26</v>
       </c>
       <c r="G163">
-        <v>134.87</v>
+        <v>60.96</v>
       </c>
       <c r="H163">
-        <v>662.32</v>
+        <v>662.34</v>
       </c>
       <c r="I163">
         <v>0.35</v>
@@ -19809,10 +19809,10 @@
         <v>207.6</v>
       </c>
       <c r="Q163">
-        <v>40</v>
+        <v>31.5</v>
       </c>
       <c r="R163">
-        <v>60</v>
+        <v>205</v>
       </c>
       <c r="S163">
         <v>75.1</v>
@@ -19830,10 +19830,10 @@
         <v>1</v>
       </c>
       <c r="X163">
-        <v>-17.4</v>
+        <v>-21.8</v>
       </c>
       <c r="Y163">
-        <v>9.9</v>
+        <v>12.5</v>
       </c>
       <c r="Z163" t="str">
         <v>CÓ</v>
@@ -19850,10 +19850,10 @@
         <v>159</v>
       </c>
       <c r="B164" t="str">
-        <v>BM-P186</v>
+        <v>BM-P184</v>
       </c>
       <c r="C164" t="str">
-        <v>B6-D21</v>
+        <v>B6-D19</v>
       </c>
       <c r="D164" t="str">
         <v>BÈ 6</v>
@@ -19862,13 +19862,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F164">
-        <v>-475.49</v>
+        <v>-420.67</v>
       </c>
       <c r="G164">
-        <v>152.36</v>
+        <v>103.07</v>
       </c>
       <c r="H164">
-        <v>662.34</v>
+        <v>662.35</v>
       </c>
       <c r="I164">
         <v>0.35</v>
@@ -19895,10 +19895,10 @@
         <v>207.6</v>
       </c>
       <c r="Q164">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="R164">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="S164">
         <v>75.1</v>
@@ -19916,10 +19916,10 @@
         <v>1</v>
       </c>
       <c r="X164">
-        <v>-13.2</v>
+        <v>-13.1</v>
       </c>
       <c r="Y164">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="Z164" t="str">
         <v>CÓ</v>
@@ -19936,10 +19936,10 @@
         <v>160</v>
       </c>
       <c r="B165" t="str">
-        <v>BM-P187</v>
+        <v>BM-P185</v>
       </c>
       <c r="C165" t="str">
-        <v>B6-D22</v>
+        <v>B6-D20</v>
       </c>
       <c r="D165" t="str">
         <v>BÈ 6</v>
@@ -19948,13 +19948,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F165">
-        <v>-376.99</v>
+        <v>-185.46</v>
       </c>
       <c r="G165">
-        <v>301.35</v>
+        <v>134.87</v>
       </c>
       <c r="H165">
-        <v>662.3</v>
+        <v>662.32</v>
       </c>
       <c r="I165">
         <v>0.35</v>
@@ -19981,10 +19981,10 @@
         <v>207.6</v>
       </c>
       <c r="Q165">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="R165">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="S165">
         <v>75.1</v>
@@ -20002,10 +20002,10 @@
         <v>1</v>
       </c>
       <c r="X165">
-        <v>-11.3</v>
+        <v>-17.4</v>
       </c>
       <c r="Y165">
-        <v>6.3</v>
+        <v>9.9</v>
       </c>
       <c r="Z165" t="str">
         <v>CÓ</v>
@@ -20022,10 +20022,10 @@
         <v>161</v>
       </c>
       <c r="B166" t="str">
-        <v>BM-P188</v>
+        <v>BM-P186</v>
       </c>
       <c r="C166" t="str">
-        <v>B6-D23</v>
+        <v>B6-D21</v>
       </c>
       <c r="D166" t="str">
         <v>BÈ 6</v>
@@ -20034,13 +20034,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F166">
-        <v>-431.32</v>
+        <v>-475.49</v>
       </c>
       <c r="G166">
-        <v>130.36</v>
+        <v>152.36</v>
       </c>
       <c r="H166">
-        <v>662.3</v>
+        <v>662.34</v>
       </c>
       <c r="I166">
         <v>0.35</v>
@@ -20067,10 +20067,10 @@
         <v>207.6</v>
       </c>
       <c r="Q166">
-        <v>31</v>
+        <v>53.5</v>
       </c>
       <c r="R166">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="S166">
         <v>75.1</v>
@@ -20088,10 +20088,10 @@
         <v>1</v>
       </c>
       <c r="X166">
-        <v>-22</v>
+        <v>-13.2</v>
       </c>
       <c r="Y166">
-        <v>12.7</v>
+        <v>7.4</v>
       </c>
       <c r="Z166" t="str">
         <v>CÓ</v>
@@ -20108,10 +20108,10 @@
         <v>162</v>
       </c>
       <c r="B167" t="str">
-        <v>BM-P189</v>
+        <v>BM-P187</v>
       </c>
       <c r="C167" t="str">
-        <v>B6-D24</v>
+        <v>B6-D22</v>
       </c>
       <c r="D167" t="str">
         <v>BÈ 6</v>
@@ -20120,13 +20120,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F167">
-        <v>-289.1</v>
+        <v>-376.99</v>
       </c>
       <c r="G167">
-        <v>43.62</v>
+        <v>301.35</v>
       </c>
       <c r="H167">
-        <v>662.33</v>
+        <v>662.3</v>
       </c>
       <c r="I167">
         <v>0.35</v>
@@ -20153,10 +20153,10 @@
         <v>207.6</v>
       </c>
       <c r="Q167">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="R167">
-        <v>235</v>
+        <v>30</v>
       </c>
       <c r="S167">
         <v>75.1</v>
@@ -20174,10 +20174,10 @@
         <v>1</v>
       </c>
       <c r="X167">
-        <v>-20.3</v>
+        <v>-11.3</v>
       </c>
       <c r="Y167">
-        <v>11.6</v>
+        <v>6.3</v>
       </c>
       <c r="Z167" t="str">
         <v>CÓ</v>
@@ -20194,10 +20194,10 @@
         <v>163</v>
       </c>
       <c r="B168" t="str">
-        <v>BM-P191</v>
+        <v>BM-P188</v>
       </c>
       <c r="C168" t="str">
-        <v>B6-D26</v>
+        <v>B6-D23</v>
       </c>
       <c r="D168" t="str">
         <v>BÈ 6</v>
@@ -20206,13 +20206,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F168">
-        <v>-176.01</v>
+        <v>-431.32</v>
       </c>
       <c r="G168">
-        <v>126.16</v>
+        <v>130.36</v>
       </c>
       <c r="H168">
-        <v>662.45</v>
+        <v>662.3</v>
       </c>
       <c r="I168">
         <v>0.35</v>
@@ -20239,10 +20239,10 @@
         <v>207.6</v>
       </c>
       <c r="Q168">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="R168">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="S168">
         <v>75.1</v>
@@ -20260,10 +20260,10 @@
         <v>1</v>
       </c>
       <c r="X168">
-        <v>-10</v>
+        <v>-22</v>
       </c>
       <c r="Y168">
-        <v>5.4</v>
+        <v>12.7</v>
       </c>
       <c r="Z168" t="str">
         <v>CÓ</v>
@@ -20280,10 +20280,10 @@
         <v>164</v>
       </c>
       <c r="B169" t="str">
-        <v>BM-P192</v>
+        <v>BM-P189</v>
       </c>
       <c r="C169" t="str">
-        <v>B6-D27</v>
+        <v>B6-D24</v>
       </c>
       <c r="D169" t="str">
         <v>BÈ 6</v>
@@ -20292,13 +20292,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F169">
-        <v>-197.6</v>
+        <v>-289.1</v>
       </c>
       <c r="G169">
-        <v>176.02</v>
+        <v>43.62</v>
       </c>
       <c r="H169">
-        <v>662.3</v>
+        <v>662.33</v>
       </c>
       <c r="I169">
         <v>0.35</v>
@@ -20325,10 +20325,10 @@
         <v>207.6</v>
       </c>
       <c r="Q169">
-        <v>69.5</v>
+        <v>34</v>
       </c>
       <c r="R169">
-        <v>60</v>
+        <v>235</v>
       </c>
       <c r="S169">
         <v>75.1</v>
@@ -20346,10 +20346,10 @@
         <v>1</v>
       </c>
       <c r="X169">
-        <v>-10.2</v>
+        <v>-20.3</v>
       </c>
       <c r="Y169">
-        <v>5.8</v>
+        <v>11.6</v>
       </c>
       <c r="Z169" t="str">
         <v>CÓ</v>
@@ -20366,10 +20366,10 @@
         <v>165</v>
       </c>
       <c r="B170" t="str">
-        <v>BM-P193</v>
+        <v>BM-P191</v>
       </c>
       <c r="C170" t="str">
-        <v>B6-D28</v>
+        <v>B6-D26</v>
       </c>
       <c r="D170" t="str">
         <v>BÈ 6</v>
@@ -20378,13 +20378,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F170">
-        <v>-436.03</v>
+        <v>-176.01</v>
       </c>
       <c r="G170">
-        <v>330.79</v>
+        <v>126.16</v>
       </c>
       <c r="H170">
-        <v>662.28</v>
+        <v>662.45</v>
       </c>
       <c r="I170">
         <v>0.35</v>
@@ -20411,10 +20411,10 @@
         <v>207.6</v>
       </c>
       <c r="Q170">
-        <v>58.5</v>
+        <v>72</v>
       </c>
       <c r="R170">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="S170">
         <v>75.1</v>
@@ -20432,10 +20432,10 @@
         <v>1</v>
       </c>
       <c r="X170">
-        <v>-12.1</v>
+        <v>-10</v>
       </c>
       <c r="Y170">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="Z170" t="str">
         <v>CÓ</v>
@@ -20452,10 +20452,10 @@
         <v>166</v>
       </c>
       <c r="B171" t="str">
-        <v>BM-P194</v>
+        <v>BM-P192</v>
       </c>
       <c r="C171" t="str">
-        <v>B6-D29</v>
+        <v>B6-D27</v>
       </c>
       <c r="D171" t="str">
         <v>BÈ 6</v>
@@ -20464,13 +20464,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F171">
-        <v>-337.48</v>
+        <v>-197.6</v>
       </c>
       <c r="G171">
-        <v>60.17</v>
+        <v>176.02</v>
       </c>
       <c r="H171">
-        <v>662.31</v>
+        <v>662.3</v>
       </c>
       <c r="I171">
         <v>0.35</v>
@@ -20497,10 +20497,10 @@
         <v>207.6</v>
       </c>
       <c r="Q171">
-        <v>39.5</v>
+        <v>69.5</v>
       </c>
       <c r="R171">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="S171">
         <v>75.1</v>
@@ -20518,10 +20518,10 @@
         <v>1</v>
       </c>
       <c r="X171">
-        <v>-17.6</v>
+        <v>-10.2</v>
       </c>
       <c r="Y171">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="Z171" t="str">
         <v>CÓ</v>
@@ -20538,10 +20538,10 @@
         <v>167</v>
       </c>
       <c r="B172" t="str">
-        <v>BM-P195</v>
+        <v>BM-P193</v>
       </c>
       <c r="C172" t="str">
-        <v>B6-D30</v>
+        <v>B6-D28</v>
       </c>
       <c r="D172" t="str">
         <v>BÈ 6</v>
@@ -20550,13 +20550,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F172">
-        <v>-457.18</v>
+        <v>-436.03</v>
       </c>
       <c r="G172">
-        <v>150.95</v>
+        <v>330.79</v>
       </c>
       <c r="H172">
-        <v>662.34</v>
+        <v>662.28</v>
       </c>
       <c r="I172">
         <v>0.35</v>
@@ -20583,10 +20583,10 @@
         <v>207.6</v>
       </c>
       <c r="Q172">
-        <v>29.5</v>
+        <v>58.5</v>
       </c>
       <c r="R172">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="S172">
         <v>75.1</v>
@@ -20604,10 +20604,10 @@
         <v>1</v>
       </c>
       <c r="X172">
-        <v>-23.1</v>
+        <v>-12.1</v>
       </c>
       <c r="Y172">
-        <v>13.3</v>
+        <v>6.8</v>
       </c>
       <c r="Z172" t="str">
         <v>CÓ</v>
@@ -20624,10 +20624,10 @@
         <v>168</v>
       </c>
       <c r="B173" t="str">
-        <v>BM-P196</v>
+        <v>BM-P194</v>
       </c>
       <c r="C173" t="str">
-        <v>B6-D31</v>
+        <v>B6-D29</v>
       </c>
       <c r="D173" t="str">
         <v>BÈ 6</v>
@@ -20636,13 +20636,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F173">
-        <v>-330.66</v>
+        <v>-337.48</v>
       </c>
       <c r="G173">
-        <v>268.29</v>
+        <v>60.17</v>
       </c>
       <c r="H173">
-        <v>662.32</v>
+        <v>662.31</v>
       </c>
       <c r="I173">
         <v>0.35</v>
@@ -20669,10 +20669,10 @@
         <v>207.6</v>
       </c>
       <c r="Q173">
-        <v>62.5</v>
+        <v>39.5</v>
       </c>
       <c r="R173">
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="S173">
         <v>75.1</v>
@@ -20690,10 +20690,10 @@
         <v>1</v>
       </c>
       <c r="X173">
-        <v>-11.4</v>
+        <v>-17.6</v>
       </c>
       <c r="Y173">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="Z173" t="str">
         <v>CÓ</v>
@@ -20710,10 +20710,10 @@
         <v>169</v>
       </c>
       <c r="B174" t="str">
-        <v>BM-P197</v>
+        <v>BM-P195</v>
       </c>
       <c r="C174" t="str">
-        <v>B6-D32</v>
+        <v>B6-D30</v>
       </c>
       <c r="D174" t="str">
         <v>BÈ 6</v>
@@ -20722,13 +20722,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F174">
-        <v>-288.83</v>
+        <v>-457.18</v>
       </c>
       <c r="G174">
-        <v>243.85</v>
+        <v>150.95</v>
       </c>
       <c r="H174">
-        <v>662.28</v>
+        <v>662.34</v>
       </c>
       <c r="I174">
         <v>0.35</v>
@@ -20755,10 +20755,10 @@
         <v>207.6</v>
       </c>
       <c r="Q174">
-        <v>76.5</v>
+        <v>29.5</v>
       </c>
       <c r="R174">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="S174">
         <v>75.1</v>
@@ -20776,10 +20776,10 @@
         <v>1</v>
       </c>
       <c r="X174">
-        <v>-9.3</v>
+        <v>-23.1</v>
       </c>
       <c r="Y174">
-        <v>5.2</v>
+        <v>13.3</v>
       </c>
       <c r="Z174" t="str">
         <v>CÓ</v>
@@ -20796,10 +20796,10 @@
         <v>170</v>
       </c>
       <c r="B175" t="str">
-        <v>BM-P198</v>
+        <v>BM-P196</v>
       </c>
       <c r="C175" t="str">
-        <v>B6-D33</v>
+        <v>B6-D31</v>
       </c>
       <c r="D175" t="str">
         <v>BÈ 6</v>
@@ -20808,13 +20808,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F175">
-        <v>-324.22</v>
+        <v>-330.66</v>
       </c>
       <c r="G175">
-        <v>63.13</v>
+        <v>268.29</v>
       </c>
       <c r="H175">
-        <v>662.31</v>
+        <v>662.32</v>
       </c>
       <c r="I175">
         <v>0.35</v>
@@ -20841,10 +20841,10 @@
         <v>207.6</v>
       </c>
       <c r="Q175">
-        <v>29.5</v>
+        <v>62.5</v>
       </c>
       <c r="R175">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="S175">
         <v>75.1</v>
@@ -20862,10 +20862,10 @@
         <v>1</v>
       </c>
       <c r="X175">
-        <v>-23.1</v>
+        <v>-11.4</v>
       </c>
       <c r="Y175">
-        <v>13.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z175" t="str">
         <v>CÓ</v>
@@ -20882,10 +20882,10 @@
         <v>171</v>
       </c>
       <c r="B176" t="str">
-        <v>BM-P199</v>
+        <v>BM-P197</v>
       </c>
       <c r="C176" t="str">
-        <v>B6-D34</v>
+        <v>B6-D32</v>
       </c>
       <c r="D176" t="str">
         <v>BÈ 6</v>
@@ -20894,13 +20894,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F176">
-        <v>-300.75</v>
+        <v>-288.83</v>
       </c>
       <c r="G176">
-        <v>249.16</v>
+        <v>243.85</v>
       </c>
       <c r="H176">
-        <v>664.44</v>
+        <v>662.28</v>
       </c>
       <c r="I176">
         <v>0.35</v>
@@ -20927,10 +20927,10 @@
         <v>207.6</v>
       </c>
       <c r="Q176">
-        <v>66</v>
+        <v>76.5</v>
       </c>
       <c r="R176">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="S176">
         <v>75.1</v>
@@ -20948,19 +20948,19 @@
         <v>1</v>
       </c>
       <c r="X176">
-        <v>-12.5</v>
+        <v>-9.3</v>
       </c>
       <c r="Y176">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="Z176" t="str">
-        <v>không</v>
+        <v>CÓ</v>
       </c>
       <c r="AA176" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB176" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="177">
@@ -20968,10 +20968,10 @@
         <v>172</v>
       </c>
       <c r="B177" t="str">
-        <v>BM-P200</v>
+        <v>BM-P198</v>
       </c>
       <c r="C177" t="str">
-        <v>B6-D35</v>
+        <v>B6-D33</v>
       </c>
       <c r="D177" t="str">
         <v>BÈ 6</v>
@@ -20980,13 +20980,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F177">
-        <v>-428.65</v>
+        <v>-324.22</v>
       </c>
       <c r="G177">
-        <v>126.18</v>
+        <v>63.13</v>
       </c>
       <c r="H177">
-        <v>662.43</v>
+        <v>662.31</v>
       </c>
       <c r="I177">
         <v>0.35</v>
@@ -21013,10 +21013,10 @@
         <v>207.6</v>
       </c>
       <c r="Q177">
-        <v>34.5</v>
+        <v>29.5</v>
       </c>
       <c r="R177">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="S177">
         <v>75.1</v>
@@ -21034,10 +21034,10 @@
         <v>1</v>
       </c>
       <c r="X177">
-        <v>-20.2</v>
+        <v>-23.1</v>
       </c>
       <c r="Y177">
-        <v>11.3</v>
+        <v>13.3</v>
       </c>
       <c r="Z177" t="str">
         <v>CÓ</v>
@@ -21054,10 +21054,10 @@
         <v>173</v>
       </c>
       <c r="B178" t="str">
-        <v>BM-P201</v>
+        <v>BM-P199</v>
       </c>
       <c r="C178" t="str">
-        <v>B6-D36</v>
+        <v>B6-D34</v>
       </c>
       <c r="D178" t="str">
         <v>BÈ 6</v>
@@ -21066,13 +21066,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F178">
-        <v>-362.49</v>
+        <v>-300.75</v>
       </c>
       <c r="G178">
-        <v>293.31</v>
+        <v>249.16</v>
       </c>
       <c r="H178">
-        <v>662.35</v>
+        <v>664.44</v>
       </c>
       <c r="I178">
         <v>0.35</v>
@@ -21099,10 +21099,10 @@
         <v>207.6</v>
       </c>
       <c r="Q178">
-        <v>64.5</v>
+        <v>66</v>
       </c>
       <c r="R178">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="S178">
         <v>75.1</v>
@@ -21120,19 +21120,19 @@
         <v>1</v>
       </c>
       <c r="X178">
-        <v>-11.1</v>
+        <v>-12.5</v>
       </c>
       <c r="Y178">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z178" t="str">
-        <v>CÓ</v>
+        <v>không</v>
       </c>
       <c r="AA178" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB178" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="179">
@@ -21140,10 +21140,10 @@
         <v>174</v>
       </c>
       <c r="B179" t="str">
-        <v>BM-P202</v>
+        <v>BM-P200</v>
       </c>
       <c r="C179" t="str">
-        <v>B6-D37</v>
+        <v>B6-D35</v>
       </c>
       <c r="D179" t="str">
         <v>BÈ 6</v>
@@ -21152,13 +21152,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F179">
-        <v>-292.07</v>
+        <v>-428.65</v>
       </c>
       <c r="G179">
-        <v>244.36</v>
+        <v>126.18</v>
       </c>
       <c r="H179">
-        <v>662.53</v>
+        <v>662.43</v>
       </c>
       <c r="I179">
         <v>0.35</v>
@@ -21185,10 +21185,10 @@
         <v>207.6</v>
       </c>
       <c r="Q179">
-        <v>71.5</v>
+        <v>34.5</v>
       </c>
       <c r="R179">
-        <v>10</v>
+        <v>235</v>
       </c>
       <c r="S179">
         <v>75.1</v>
@@ -21206,10 +21206,10 @@
         <v>1</v>
       </c>
       <c r="X179">
-        <v>-10.1</v>
+        <v>-20.2</v>
       </c>
       <c r="Y179">
-        <v>5.4</v>
+        <v>11.3</v>
       </c>
       <c r="Z179" t="str">
         <v>CÓ</v>
@@ -21226,10 +21226,10 @@
         <v>175</v>
       </c>
       <c r="B180" t="str">
-        <v>BM-P203</v>
+        <v>BM-P201</v>
       </c>
       <c r="C180" t="str">
-        <v>B6-D38</v>
+        <v>B6-D36</v>
       </c>
       <c r="D180" t="str">
         <v>BÈ 6</v>
@@ -21238,13 +21238,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F180">
-        <v>-314.53</v>
+        <v>-362.49</v>
       </c>
       <c r="G180">
-        <v>58.38</v>
+        <v>293.31</v>
       </c>
       <c r="H180">
-        <v>663.82</v>
+        <v>662.35</v>
       </c>
       <c r="I180">
         <v>0.35</v>
@@ -21271,10 +21271,10 @@
         <v>207.6</v>
       </c>
       <c r="Q180">
-        <v>38</v>
+        <v>64.5</v>
       </c>
       <c r="R180">
-        <v>190</v>
+        <v>35</v>
       </c>
       <c r="S180">
         <v>75.1</v>
@@ -21292,19 +21292,19 @@
         <v>1</v>
       </c>
       <c r="X180">
-        <v>-20.3</v>
+        <v>-11.1</v>
       </c>
       <c r="Y180">
-        <v>8.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z180" t="str">
-        <v>không</v>
+        <v>CÓ</v>
       </c>
       <c r="AA180" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB180" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="181">
@@ -21312,10 +21312,10 @@
         <v>176</v>
       </c>
       <c r="B181" t="str">
-        <v>BM-P204</v>
+        <v>BM-P202</v>
       </c>
       <c r="C181" t="str">
-        <v>B6-D39</v>
+        <v>B6-D37</v>
       </c>
       <c r="D181" t="str">
         <v>BÈ 6</v>
@@ -21324,13 +21324,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F181">
-        <v>-308.55</v>
+        <v>-292.07</v>
       </c>
       <c r="G181">
-        <v>250.05</v>
+        <v>244.36</v>
       </c>
       <c r="H181">
-        <v>662.43</v>
+        <v>662.53</v>
       </c>
       <c r="I181">
         <v>0.35</v>
@@ -21357,10 +21357,10 @@
         <v>207.6</v>
       </c>
       <c r="Q181">
-        <v>60</v>
+        <v>71.5</v>
       </c>
       <c r="R181">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="S181">
         <v>75.1</v>
@@ -21378,10 +21378,10 @@
         <v>1</v>
       </c>
       <c r="X181">
-        <v>-11.9</v>
+        <v>-10.1</v>
       </c>
       <c r="Y181">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z181" t="str">
         <v>CÓ</v>
@@ -21398,10 +21398,10 @@
         <v>177</v>
       </c>
       <c r="B182" t="str">
-        <v>BM-P205</v>
+        <v>BM-P203</v>
       </c>
       <c r="C182" t="str">
-        <v>B6-D40</v>
+        <v>B6-D38</v>
       </c>
       <c r="D182" t="str">
         <v>BÈ 6</v>
@@ -21410,13 +21410,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F182">
-        <v>-439.03</v>
+        <v>-314.53</v>
       </c>
       <c r="G182">
-        <v>139.36</v>
+        <v>58.38</v>
       </c>
       <c r="H182">
-        <v>662.27</v>
+        <v>663.82</v>
       </c>
       <c r="I182">
         <v>0.35</v>
@@ -21443,10 +21443,10 @@
         <v>207.6</v>
       </c>
       <c r="Q182">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="R182">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="S182">
         <v>75.1</v>
@@ -21464,19 +21464,19 @@
         <v>1</v>
       </c>
       <c r="X182">
-        <v>-24.1</v>
+        <v>-20.3</v>
       </c>
       <c r="Y182">
-        <v>14.1</v>
+        <v>8.2</v>
       </c>
       <c r="Z182" t="str">
-        <v>CÓ</v>
+        <v>không</v>
       </c>
       <c r="AA182" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AB182" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="183">
@@ -21484,10 +21484,10 @@
         <v>178</v>
       </c>
       <c r="B183" t="str">
-        <v>BM-P206</v>
+        <v>BM-P204</v>
       </c>
       <c r="C183" t="str">
-        <v>B6-D41</v>
+        <v>B6-D39</v>
       </c>
       <c r="D183" t="str">
         <v>BÈ 6</v>
@@ -21496,13 +21496,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F183">
-        <v>-187.88</v>
+        <v>-308.55</v>
       </c>
       <c r="G183">
-        <v>140.43</v>
+        <v>250.05</v>
       </c>
       <c r="H183">
-        <v>662.27</v>
+        <v>662.43</v>
       </c>
       <c r="I183">
         <v>0.35</v>
@@ -21529,10 +21529,10 @@
         <v>207.6</v>
       </c>
       <c r="Q183">
-        <v>45.5</v>
+        <v>60</v>
       </c>
       <c r="R183">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="S183">
         <v>75.1</v>
@@ -21550,10 +21550,10 @@
         <v>1</v>
       </c>
       <c r="X183">
-        <v>-15.4</v>
+        <v>-11.9</v>
       </c>
       <c r="Y183">
-        <v>8.8</v>
+        <v>6.5</v>
       </c>
       <c r="Z183" t="str">
         <v>CÓ</v>
@@ -21570,10 +21570,10 @@
         <v>179</v>
       </c>
       <c r="B184" t="str">
-        <v>BM-P207</v>
+        <v>BM-P205</v>
       </c>
       <c r="C184" t="str">
-        <v>B6-D42</v>
+        <v>B6-D40</v>
       </c>
       <c r="D184" t="str">
         <v>BÈ 6</v>
@@ -21582,13 +21582,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F184">
-        <v>-411.87</v>
+        <v>-439.03</v>
       </c>
       <c r="G184">
-        <v>85.19</v>
+        <v>139.36</v>
       </c>
       <c r="H184">
-        <v>662.34</v>
+        <v>662.27</v>
       </c>
       <c r="I184">
         <v>0.35</v>
@@ -21615,10 +21615,10 @@
         <v>207.6</v>
       </c>
       <c r="Q184">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="R184">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="S184">
         <v>75.1</v>
@@ -21636,10 +21636,10 @@
         <v>1</v>
       </c>
       <c r="X184">
-        <v>-11.9</v>
+        <v>-24.1</v>
       </c>
       <c r="Y184">
-        <v>6.6</v>
+        <v>14.1</v>
       </c>
       <c r="Z184" t="str">
         <v>CÓ</v>
@@ -21656,10 +21656,10 @@
         <v>180</v>
       </c>
       <c r="B185" t="str">
-        <v>BM-P208</v>
+        <v>BM-P206</v>
       </c>
       <c r="C185" t="str">
-        <v>B6-D43</v>
+        <v>B6-D41</v>
       </c>
       <c r="D185" t="str">
         <v>BÈ 6</v>
@@ -21668,13 +21668,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F185">
-        <v>-382.48</v>
+        <v>-187.88</v>
       </c>
       <c r="G185">
-        <v>304.87</v>
+        <v>140.43</v>
       </c>
       <c r="H185">
-        <v>662.37</v>
+        <v>662.27</v>
       </c>
       <c r="I185">
         <v>0.35</v>
@@ -21701,10 +21701,10 @@
         <v>207.6</v>
       </c>
       <c r="Q185">
-        <v>62.5</v>
+        <v>45.5</v>
       </c>
       <c r="R185">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="S185">
         <v>75.1</v>
@@ -21722,10 +21722,10 @@
         <v>1</v>
       </c>
       <c r="X185">
-        <v>-11.4</v>
+        <v>-15.4</v>
       </c>
       <c r="Y185">
-        <v>6.3</v>
+        <v>8.8</v>
       </c>
       <c r="Z185" t="str">
         <v>CÓ</v>
@@ -21742,10 +21742,10 @@
         <v>181</v>
       </c>
       <c r="B186" t="str">
-        <v>BM-P209</v>
+        <v>BM-P207</v>
       </c>
       <c r="C186" t="str">
-        <v>B6-D44</v>
+        <v>B6-D42</v>
       </c>
       <c r="D186" t="str">
         <v>BÈ 6</v>
@@ -21754,13 +21754,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F186">
-        <v>-271.32</v>
+        <v>-411.87</v>
       </c>
       <c r="G186">
-        <v>242.01</v>
+        <v>85.19</v>
       </c>
       <c r="H186">
-        <v>662.31</v>
+        <v>662.34</v>
       </c>
       <c r="I186">
         <v>0.35</v>
@@ -21787,10 +21787,10 @@
         <v>207.6</v>
       </c>
       <c r="Q186">
-        <v>82.5</v>
+        <v>60</v>
       </c>
       <c r="R186">
-        <v>10</v>
+        <v>235</v>
       </c>
       <c r="S186">
         <v>75.1</v>
@@ -21808,10 +21808,10 @@
         <v>1</v>
       </c>
       <c r="X186">
-        <v>-8.7</v>
+        <v>-11.9</v>
       </c>
       <c r="Y186">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z186" t="str">
         <v>CÓ</v>
@@ -21828,10 +21828,10 @@
         <v>182</v>
       </c>
       <c r="B187" t="str">
-        <v>BM-P210</v>
+        <v>BM-P208</v>
       </c>
       <c r="C187" t="str">
-        <v>B6-D45</v>
+        <v>B6-D43</v>
       </c>
       <c r="D187" t="str">
         <v>BÈ 6</v>
@@ -21840,13 +21840,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F187">
-        <v>-286.77</v>
+        <v>-382.48</v>
       </c>
       <c r="G187">
-        <v>39.76</v>
+        <v>304.87</v>
       </c>
       <c r="H187">
-        <v>662.27</v>
+        <v>662.37</v>
       </c>
       <c r="I187">
         <v>0.35</v>
@@ -21873,10 +21873,10 @@
         <v>207.6</v>
       </c>
       <c r="Q187">
-        <v>39</v>
+        <v>62.5</v>
       </c>
       <c r="R187">
-        <v>245</v>
+        <v>35</v>
       </c>
       <c r="S187">
         <v>75.1</v>
@@ -21894,10 +21894,10 @@
         <v>1</v>
       </c>
       <c r="X187">
-        <v>-17.8</v>
+        <v>-11.4</v>
       </c>
       <c r="Y187">
-        <v>10.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z187" t="str">
         <v>CÓ</v>
@@ -21914,10 +21914,10 @@
         <v>183</v>
       </c>
       <c r="B188" t="str">
-        <v>BM-P212</v>
+        <v>BM-P209</v>
       </c>
       <c r="C188" t="str">
-        <v>B6-D47</v>
+        <v>B6-D44</v>
       </c>
       <c r="D188" t="str">
         <v>BÈ 6</v>
@@ -21926,13 +21926,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F188">
-        <v>-303.42</v>
+        <v>-271.32</v>
       </c>
       <c r="G188">
-        <v>55.13</v>
+        <v>242.01</v>
       </c>
       <c r="H188">
-        <v>662.27</v>
+        <v>662.31</v>
       </c>
       <c r="I188">
         <v>0.35</v>
@@ -21959,10 +21959,10 @@
         <v>207.6</v>
       </c>
       <c r="Q188">
-        <v>31</v>
+        <v>82.5</v>
       </c>
       <c r="R188">
-        <v>207.5</v>
+        <v>10</v>
       </c>
       <c r="S188">
         <v>75.1</v>
@@ -21980,10 +21980,10 @@
         <v>1</v>
       </c>
       <c r="X188">
-        <v>-22</v>
+        <v>-8.7</v>
       </c>
       <c r="Y188">
-        <v>12.8</v>
+        <v>4.8</v>
       </c>
       <c r="Z188" t="str">
         <v>CÓ</v>
@@ -22000,10 +22000,10 @@
         <v>184</v>
       </c>
       <c r="B189" t="str">
-        <v>BM-P213</v>
+        <v>BM-P210</v>
       </c>
       <c r="C189" t="str">
-        <v>B6-D48</v>
+        <v>B6-D45</v>
       </c>
       <c r="D189" t="str">
         <v>BÈ 6</v>
@@ -22012,13 +22012,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F189">
-        <v>-322.29</v>
+        <v>-286.77</v>
       </c>
       <c r="G189">
-        <v>261.21</v>
+        <v>39.76</v>
       </c>
       <c r="H189">
-        <v>662.42</v>
+        <v>662.27</v>
       </c>
       <c r="I189">
         <v>0.35</v>
@@ -22045,10 +22045,10 @@
         <v>207.6</v>
       </c>
       <c r="Q189">
-        <v>61.5</v>
+        <v>39</v>
       </c>
       <c r="R189">
-        <v>40</v>
+        <v>245</v>
       </c>
       <c r="S189">
         <v>75.1</v>
@@ -22066,10 +22066,10 @@
         <v>1</v>
       </c>
       <c r="X189">
-        <v>-11.6</v>
+        <v>-17.8</v>
       </c>
       <c r="Y189">
-        <v>6.4</v>
+        <v>10.2</v>
       </c>
       <c r="Z189" t="str">
         <v>CÓ</v>
@@ -22086,10 +22086,10 @@
         <v>185</v>
       </c>
       <c r="B190" t="str">
-        <v>BM-P214</v>
+        <v>BM-P212</v>
       </c>
       <c r="C190" t="str">
-        <v>B6-D49</v>
+        <v>B6-D47</v>
       </c>
       <c r="D190" t="str">
         <v>BÈ 6</v>
@@ -22098,13 +22098,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F190">
-        <v>-451.83</v>
+        <v>-303.42</v>
       </c>
       <c r="G190">
-        <v>148.54</v>
+        <v>55.13</v>
       </c>
       <c r="H190">
-        <v>662.29</v>
+        <v>662.27</v>
       </c>
       <c r="I190">
         <v>0.35</v>
@@ -22131,10 +22131,10 @@
         <v>207.6</v>
       </c>
       <c r="Q190">
-        <v>27.5</v>
+        <v>31</v>
       </c>
       <c r="R190">
-        <v>210</v>
+        <v>207.5</v>
       </c>
       <c r="S190">
         <v>75.1</v>
@@ -22152,10 +22152,10 @@
         <v>1</v>
       </c>
       <c r="X190">
-        <v>-24.5</v>
+        <v>-22</v>
       </c>
       <c r="Y190">
-        <v>14.3</v>
+        <v>12.8</v>
       </c>
       <c r="Z190" t="str">
         <v>CÓ</v>
@@ -22172,10 +22172,10 @@
         <v>186</v>
       </c>
       <c r="B191" t="str">
-        <v>BM-P215</v>
+        <v>BM-P213</v>
       </c>
       <c r="C191" t="str">
-        <v>B6-D50</v>
+        <v>B6-D48</v>
       </c>
       <c r="D191" t="str">
         <v>BÈ 6</v>
@@ -22184,13 +22184,13 @@
         <v>Cọc mới (ven bờ)</v>
       </c>
       <c r="F191">
-        <v>-424.31</v>
+        <v>-322.29</v>
       </c>
       <c r="G191">
-        <v>117.21</v>
+        <v>261.21</v>
       </c>
       <c r="H191">
-        <v>662.38</v>
+        <v>662.42</v>
       </c>
       <c r="I191">
         <v>0.35</v>
@@ -22217,10 +22217,10 @@
         <v>207.6</v>
       </c>
       <c r="Q191">
-        <v>45.5</v>
+        <v>61.5</v>
       </c>
       <c r="R191">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="S191">
         <v>75.1</v>
@@ -22238,10 +22238,10 @@
         <v>1</v>
       </c>
       <c r="X191">
-        <v>-15.5</v>
+        <v>-11.6</v>
       </c>
       <c r="Y191">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z191" t="str">
         <v>CÓ</v>
@@ -22253,16 +22253,188 @@
         <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
+    <row r="192">
+      <c r="A192">
+        <v>187</v>
+      </c>
+      <c r="B192" t="str">
+        <v>BM-P214</v>
+      </c>
+      <c r="C192" t="str">
+        <v>B6-D49</v>
+      </c>
+      <c r="D192" t="str">
+        <v>BÈ 6</v>
+      </c>
+      <c r="E192" t="str">
+        <v>Cọc mới (ven bờ)</v>
+      </c>
+      <c r="F192">
+        <v>-451.83</v>
+      </c>
+      <c r="G192">
+        <v>148.54</v>
+      </c>
+      <c r="H192">
+        <v>662.29</v>
+      </c>
+      <c r="I192">
+        <v>0.35</v>
+      </c>
+      <c r="J192">
+        <v>6.5</v>
+      </c>
+      <c r="K192">
+        <v>6.6</v>
+      </c>
+      <c r="L192" t="str">
+        <v>6Φ28</v>
+      </c>
+      <c r="M192" t="str">
+        <v>CB400-V</v>
+      </c>
+      <c r="N192" t="str">
+        <v>Đai xoắn Φ8 a150</v>
+      </c>
+      <c r="O192">
+        <v>0.635</v>
+      </c>
+      <c r="P192">
+        <v>207.6</v>
+      </c>
+      <c r="Q192">
+        <v>27.5</v>
+      </c>
+      <c r="R192">
+        <v>210</v>
+      </c>
+      <c r="S192">
+        <v>75.1</v>
+      </c>
+      <c r="T192">
+        <v>81.9</v>
+      </c>
+      <c r="U192">
+        <v>0.65</v>
+      </c>
+      <c r="V192">
+        <v>0.89</v>
+      </c>
+      <c r="W192">
+        <v>1</v>
+      </c>
+      <c r="X192">
+        <v>-24.5</v>
+      </c>
+      <c r="Y192">
+        <v>14.3</v>
+      </c>
+      <c r="Z192" t="str">
+        <v>CÓ</v>
+      </c>
+      <c r="AA192" t="str">
+        <v>ĐẠT</v>
+      </c>
+      <c r="AB192" t="str">
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>188</v>
+      </c>
+      <c r="B193" t="str">
+        <v>BM-P215</v>
+      </c>
+      <c r="C193" t="str">
+        <v>B6-D50</v>
+      </c>
+      <c r="D193" t="str">
+        <v>BÈ 6</v>
+      </c>
+      <c r="E193" t="str">
+        <v>Cọc mới (ven bờ)</v>
+      </c>
+      <c r="F193">
+        <v>-424.31</v>
+      </c>
+      <c r="G193">
+        <v>117.21</v>
+      </c>
+      <c r="H193">
+        <v>662.38</v>
+      </c>
+      <c r="I193">
+        <v>0.35</v>
+      </c>
+      <c r="J193">
+        <v>6.5</v>
+      </c>
+      <c r="K193">
+        <v>6.6</v>
+      </c>
+      <c r="L193" t="str">
+        <v>6Φ28</v>
+      </c>
+      <c r="M193" t="str">
+        <v>CB400-V</v>
+      </c>
+      <c r="N193" t="str">
+        <v>Đai xoắn Φ8 a150</v>
+      </c>
+      <c r="O193">
+        <v>0.635</v>
+      </c>
+      <c r="P193">
+        <v>207.6</v>
+      </c>
+      <c r="Q193">
+        <v>45.5</v>
+      </c>
+      <c r="R193">
+        <v>250</v>
+      </c>
+      <c r="S193">
+        <v>75.1</v>
+      </c>
+      <c r="T193">
+        <v>81.9</v>
+      </c>
+      <c r="U193">
+        <v>0.65</v>
+      </c>
+      <c r="V193">
+        <v>0.89</v>
+      </c>
+      <c r="W193">
+        <v>1</v>
+      </c>
+      <c r="X193">
+        <v>-15.5</v>
+      </c>
+      <c r="Y193">
+        <v>8.6</v>
+      </c>
+      <c r="Z193" t="str">
+        <v>CÓ</v>
+      </c>
+      <c r="AA193" t="str">
+        <v>ĐẠT</v>
+      </c>
+      <c r="AB193" t="str">
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB191"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB193"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO27"/>
+  <dimension ref="A1:AO25"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -22309,7 +22481,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>THỐNG KÊ VÀ TÍNH TOÁN TỪNG ĐẾ NEO ĐÁY: ĐẾ BTCT + 4 VÍT XOẮN (19 ĐẾ) — BM-FPV-2026</v>
+        <v>THỐNG KÊ VÀ TÍNH TOÁN TỪNG ĐẾ NEO ĐÁY: ĐẾ BTCT + 4 VÍT XOẮN (17 ĐẾ) — BM-FPV-2026</v>
       </c>
     </row>
     <row r="2">
@@ -23728,7 +23900,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="I16">
-        <v>67.5</v>
+        <v>70.3</v>
       </c>
       <c r="J16">
         <v>8.35</v>
@@ -23752,10 +23924,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q16">
-        <v>20.7</v>
+        <v>19.7</v>
       </c>
       <c r="R16">
-        <v>175.1</v>
+        <v>177.7</v>
       </c>
       <c r="S16">
         <v>6</v>
@@ -23794,7 +23966,7 @@
         <v>226.1</v>
       </c>
       <c r="AE16">
-        <v>536.8</v>
+        <v>543.9</v>
       </c>
       <c r="AF16">
         <v>838</v>
@@ -23803,13 +23975,13 @@
         <v>0</v>
       </c>
       <c r="AH16">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AI16">
         <v>0.38</v>
       </c>
       <c r="AJ16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AK16">
         <v>0</v>
@@ -23978,7 +24150,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="I18">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="J18">
         <v>9.52</v>
@@ -24002,10 +24174,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q18">
-        <v>17.3</v>
+        <v>16.3</v>
       </c>
       <c r="R18">
-        <v>169.3</v>
+        <v>171.2</v>
       </c>
       <c r="S18">
         <v>5.75</v>
@@ -24044,7 +24216,7 @@
         <v>210.2</v>
       </c>
       <c r="AE18">
-        <v>496.1</v>
+        <v>501</v>
       </c>
       <c r="AF18">
         <v>752.4</v>
@@ -24059,7 +24231,7 @@
         <v>0.38</v>
       </c>
       <c r="AJ18">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="AK18">
         <v>0</v>
@@ -24085,76 +24257,76 @@
         <v>BM-DV014</v>
       </c>
       <c r="C19" t="str">
-        <v>B3-D16</v>
+        <v>B5-D17</v>
       </c>
       <c r="D19" t="str">
-        <v>BÈ 3</v>
+        <v>BÈ 5</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>84.7</v>
       </c>
       <c r="F19">
-        <v>17.5</v>
+        <v>23.39</v>
       </c>
       <c r="G19" t="str">
-        <v>-</v>
+        <v>B6-D06</v>
       </c>
       <c r="H19" t="str">
-        <v>-</v>
-      </c>
-      <c r="I19" t="str">
-        <v>-</v>
-      </c>
-      <c r="J19" t="str">
-        <v>-</v>
+        <v>BÈ 6</v>
+      </c>
+      <c r="I19">
+        <v>153.1</v>
+      </c>
+      <c r="J19">
+        <v>23.4</v>
       </c>
       <c r="K19">
-        <v>65.58</v>
+        <v>-221.96</v>
       </c>
       <c r="L19">
-        <v>172.85</v>
+        <v>54.32</v>
       </c>
       <c r="M19">
-        <v>654.44</v>
+        <v>648.38</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O19">
-        <v>14.61</v>
+        <v>20.67</v>
       </c>
       <c r="P19" t="str">
-        <v>B3-D16 căng (MN cao)</v>
+        <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="Q19">
-        <v>23.2</v>
+        <v>51.5</v>
       </c>
       <c r="R19">
-        <v>19.1</v>
+        <v>156.6</v>
       </c>
       <c r="S19">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="T19">
         <v>0.4</v>
       </c>
       <c r="U19">
-        <v>2.48</v>
+        <v>13.21</v>
       </c>
       <c r="V19">
-        <v>62.5</v>
+        <v>330.6</v>
       </c>
       <c r="W19">
-        <v>37.5</v>
+        <v>198.4</v>
       </c>
       <c r="X19">
-        <v>6.4</v>
+        <v>33.7</v>
       </c>
       <c r="Y19" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="Z19">
-        <v>119</v>
+        <v>602</v>
       </c>
       <c r="AA19">
         <v>4</v>
@@ -24166,25 +24338,25 @@
         <v>3.7</v>
       </c>
       <c r="AD19">
-        <v>65.4</v>
+        <v>210.2</v>
       </c>
       <c r="AE19">
-        <v>36.6</v>
+        <v>478.5</v>
       </c>
       <c r="AF19">
-        <v>126</v>
+        <v>752.4</v>
       </c>
       <c r="AG19">
         <v>0</v>
       </c>
       <c r="AH19">
-        <v>0.29</v>
+        <v>0.74</v>
       </c>
       <c r="AI19">
-        <v>0.33</v>
+        <v>0.52</v>
       </c>
       <c r="AJ19">
-        <v>0.44</v>
+        <v>0.95</v>
       </c>
       <c r="AK19">
         <v>0</v>
@@ -24199,7 +24371,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AO19" t="str">
-        <v>Nền đế cao hơn MNC: đế lộ khô khi nước chết (dây thoải, bè ở gần cũng có thể chạm đáy)</v>
+        <v>Đế dùng chung hai bè: hai tai neo; Đế lớn hơn đế mẫu</v>
       </c>
     </row>
     <row r="20">
@@ -24210,16 +24382,16 @@
         <v>BM-DV015</v>
       </c>
       <c r="C20" t="str">
-        <v>B3-D18</v>
+        <v>B6-D13</v>
       </c>
       <c r="D20" t="str">
-        <v>BÈ 3</v>
+        <v>BÈ 6</v>
       </c>
       <c r="E20">
-        <v>53.8</v>
+        <v>109.1</v>
       </c>
       <c r="F20">
-        <v>17.5</v>
+        <v>17.51</v>
       </c>
       <c r="G20" t="str">
         <v>-</v>
@@ -24234,52 +24406,52 @@
         <v>-</v>
       </c>
       <c r="K20">
-        <v>104.82</v>
+        <v>-500.91</v>
       </c>
       <c r="L20">
-        <v>69.24</v>
+        <v>231.29</v>
       </c>
       <c r="M20">
-        <v>651.57</v>
+        <v>648.11</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O20">
-        <v>17.48</v>
+        <v>20.94</v>
       </c>
       <c r="P20" t="str">
-        <v>B3-D18 căng (MN cao)</v>
+        <v>B6-D13 căng (MN cao)</v>
       </c>
       <c r="Q20">
-        <v>38.3</v>
+        <v>70.4</v>
       </c>
       <c r="R20">
-        <v>37.8</v>
+        <v>83.3</v>
       </c>
       <c r="S20">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="T20">
         <v>0.4</v>
       </c>
       <c r="U20">
-        <v>2.48</v>
+        <v>6.38</v>
       </c>
       <c r="V20">
-        <v>62.5</v>
+        <v>160</v>
       </c>
       <c r="W20">
-        <v>37.5</v>
+        <v>96</v>
       </c>
       <c r="X20">
-        <v>6.4</v>
+        <v>16.3</v>
       </c>
       <c r="Y20" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="Z20">
-        <v>119</v>
+        <v>291</v>
       </c>
       <c r="AA20">
         <v>4</v>
@@ -24291,28 +24463,28 @@
         <v>3.7</v>
       </c>
       <c r="AD20">
-        <v>65.4</v>
+        <v>118.1</v>
       </c>
       <c r="AE20">
-        <v>68.3</v>
+        <v>205.3</v>
       </c>
       <c r="AF20">
-        <v>126</v>
+        <v>318.7</v>
       </c>
       <c r="AG20">
-        <v>5.55</v>
+        <v>4.23</v>
       </c>
       <c r="AH20">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="AI20">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="AJ20">
-        <v>0.81</v>
+        <v>0.97</v>
       </c>
       <c r="AK20">
-        <v>0.7</v>
+        <v>0.53</v>
       </c>
       <c r="AL20">
         <v>0.15</v>
@@ -24324,7 +24496,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AO20" t="str">
-        <v>Nền đế cao hơn MNC: đế lộ khô khi nước chết (dây thoải, bè ở gần cũng có thể chạm đáy)</v>
+        <v>Đế lớn hơn đế mẫu</v>
       </c>
     </row>
     <row r="21">
@@ -24335,76 +24507,76 @@
         <v>BM-DV016</v>
       </c>
       <c r="C21" t="str">
-        <v>B5-D17</v>
+        <v>B6-D25</v>
       </c>
       <c r="D21" t="str">
-        <v>BÈ 5</v>
+        <v>BÈ 6</v>
       </c>
       <c r="E21">
-        <v>84.7</v>
+        <v>112.9</v>
       </c>
       <c r="F21">
-        <v>23.39</v>
+        <v>17.51</v>
       </c>
       <c r="G21" t="str">
-        <v>B6-D06</v>
+        <v>-</v>
       </c>
       <c r="H21" t="str">
-        <v>BÈ 6</v>
-      </c>
-      <c r="I21">
-        <v>153.1</v>
-      </c>
-      <c r="J21">
-        <v>23.4</v>
+        <v>-</v>
+      </c>
+      <c r="I21" t="str">
+        <v>-</v>
+      </c>
+      <c r="J21" t="str">
+        <v>-</v>
       </c>
       <c r="K21">
-        <v>-221.96</v>
+        <v>-487.72</v>
       </c>
       <c r="L21">
-        <v>54.32</v>
+        <v>250.13</v>
       </c>
       <c r="M21">
-        <v>648.38</v>
+        <v>648.84</v>
       </c>
       <c r="N21">
-        <v>1.12</v>
+        <v>0.66</v>
       </c>
       <c r="O21">
-        <v>20.67</v>
+        <v>20.21</v>
       </c>
       <c r="P21" t="str">
-        <v>cả hai dây căng (MN cao)</v>
+        <v>B6-D25 căng (MN cao)</v>
       </c>
       <c r="Q21">
-        <v>51.5</v>
+        <v>74.3</v>
       </c>
       <c r="R21">
-        <v>156.6</v>
+        <v>85</v>
       </c>
       <c r="S21">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="T21">
         <v>0.4</v>
       </c>
       <c r="U21">
-        <v>13.21</v>
+        <v>6.38</v>
       </c>
       <c r="V21">
-        <v>330.6</v>
+        <v>160</v>
       </c>
       <c r="W21">
-        <v>198.4</v>
+        <v>96</v>
       </c>
       <c r="X21">
-        <v>33.7</v>
+        <v>16.3</v>
       </c>
       <c r="Y21" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="Z21">
-        <v>602</v>
+        <v>291</v>
       </c>
       <c r="AA21">
         <v>4</v>
@@ -24416,28 +24588,28 @@
         <v>3.7</v>
       </c>
       <c r="AD21">
-        <v>210.2</v>
+        <v>118.1</v>
       </c>
       <c r="AE21">
-        <v>478.5</v>
+        <v>210.8</v>
       </c>
       <c r="AF21">
-        <v>752.4</v>
+        <v>318.7</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AH21">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="AI21">
-        <v>0.52</v>
+        <v>0.69</v>
       </c>
       <c r="AJ21">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AL21">
         <v>0.15</v>
@@ -24449,7 +24621,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AO21" t="str">
-        <v>Đế dùng chung hai bè: hai tai neo; Đế lớn hơn đế mẫu</v>
+        <v>Đế lớn hơn đế mẫu</v>
       </c>
     </row>
     <row r="22">
@@ -24460,13 +24632,13 @@
         <v>BM-DV017</v>
       </c>
       <c r="C22" t="str">
-        <v>B6-D13</v>
+        <v>B6-D46</v>
       </c>
       <c r="D22" t="str">
         <v>BÈ 6</v>
       </c>
       <c r="E22">
-        <v>109.1</v>
+        <v>108.5</v>
       </c>
       <c r="F22">
         <v>17.51</v>
@@ -24484,28 +24656,28 @@
         <v>-</v>
       </c>
       <c r="K22">
-        <v>-500.91</v>
+        <v>-507.22</v>
       </c>
       <c r="L22">
-        <v>231.29</v>
+        <v>222.28</v>
       </c>
       <c r="M22">
-        <v>648.11</v>
+        <v>647.82</v>
       </c>
       <c r="N22">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="O22">
-        <v>20.94</v>
+        <v>21.23</v>
       </c>
       <c r="P22" t="str">
-        <v>B6-D13 căng (MN cao)</v>
+        <v>B6-D46 căng (MN cao)</v>
       </c>
       <c r="Q22">
-        <v>70.4</v>
+        <v>69.4</v>
       </c>
       <c r="R22">
-        <v>83.3</v>
+        <v>83.4</v>
       </c>
       <c r="S22">
         <v>4</v>
@@ -24544,22 +24716,22 @@
         <v>118.1</v>
       </c>
       <c r="AE22">
-        <v>205.3</v>
+        <v>204.9</v>
       </c>
       <c r="AF22">
         <v>318.7</v>
       </c>
       <c r="AG22">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="AH22">
         <v>0.71</v>
       </c>
       <c r="AI22">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="AJ22">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="AK22">
         <v>0.53</v>
@@ -24578,367 +24750,117 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>18</v>
-      </c>
-      <c r="B23" t="str">
-        <v>BM-DV018</v>
-      </c>
-      <c r="C23" t="str">
-        <v>B6-D25</v>
-      </c>
-      <c r="D23" t="str">
-        <v>BÈ 6</v>
-      </c>
-      <c r="E23">
-        <v>112.9</v>
-      </c>
-      <c r="F23">
-        <v>17.51</v>
-      </c>
-      <c r="G23" t="str">
-        <v>-</v>
-      </c>
-      <c r="H23" t="str">
-        <v>-</v>
-      </c>
-      <c r="I23" t="str">
-        <v>-</v>
-      </c>
-      <c r="J23" t="str">
-        <v>-</v>
-      </c>
-      <c r="K23">
-        <v>-487.72</v>
-      </c>
-      <c r="L23">
-        <v>250.13</v>
-      </c>
-      <c r="M23">
-        <v>648.84</v>
-      </c>
-      <c r="N23">
-        <v>0.66</v>
-      </c>
-      <c r="O23">
-        <v>20.21</v>
-      </c>
-      <c r="P23" t="str">
-        <v>B6-D25 căng (MN cao)</v>
-      </c>
-      <c r="Q23">
-        <v>74.3</v>
-      </c>
-      <c r="R23">
-        <v>85</v>
-      </c>
-      <c r="S23">
-        <v>4</v>
-      </c>
-      <c r="T23">
-        <v>0.4</v>
-      </c>
-      <c r="U23">
-        <v>6.38</v>
-      </c>
-      <c r="V23">
-        <v>160</v>
-      </c>
-      <c r="W23">
-        <v>96</v>
-      </c>
-      <c r="X23">
-        <v>16.3</v>
-      </c>
-      <c r="Y23" t="str">
-        <v>Ø12 a200</v>
-      </c>
-      <c r="Z23">
-        <v>291</v>
-      </c>
-      <c r="AA23">
-        <v>4</v>
-      </c>
-      <c r="AB23" t="str">
-        <v>Ø89×5</v>
-      </c>
-      <c r="AC23">
-        <v>3.7</v>
-      </c>
-      <c r="AD23">
-        <v>118.1</v>
-      </c>
-      <c r="AE23">
-        <v>210.8</v>
-      </c>
-      <c r="AF23">
-        <v>318.7</v>
-      </c>
-      <c r="AG23">
-        <v>4.94</v>
-      </c>
-      <c r="AH23">
-        <v>0.72</v>
-      </c>
-      <c r="AI23">
-        <v>0.69</v>
-      </c>
-      <c r="AJ23">
-        <v>0.99</v>
-      </c>
-      <c r="AK23">
-        <v>0.62</v>
-      </c>
-      <c r="AL23">
-        <v>0.15</v>
-      </c>
-      <c r="AM23">
-        <v>0.62</v>
-      </c>
-      <c r="AN23" t="str">
-        <v>ĐẠT</v>
-      </c>
-      <c r="AO23" t="str">
-        <v>Đế lớn hơn đế mẫu</v>
+      <c r="A23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>19</v>
+      <c r="A24" t="str">
+        <v>TỔNG</v>
       </c>
       <c r="B24" t="str">
-        <v>BM-DV019</v>
+        <v>17 đế</v>
       </c>
       <c r="C24" t="str">
-        <v>B6-D46</v>
+        <v/>
       </c>
       <c r="D24" t="str">
-        <v>BÈ 6</v>
-      </c>
-      <c r="E24">
-        <v>108.5</v>
-      </c>
-      <c r="F24">
-        <v>17.51</v>
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="H24" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="J24" t="str">
-        <v>-</v>
-      </c>
-      <c r="K24">
-        <v>-507.22</v>
-      </c>
-      <c r="L24">
-        <v>222.28</v>
-      </c>
-      <c r="M24">
-        <v>647.82</v>
-      </c>
-      <c r="N24">
-        <v>1.68</v>
-      </c>
-      <c r="O24">
-        <v>21.23</v>
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
       </c>
       <c r="P24" t="str">
-        <v>B6-D46 căng (MN cao)</v>
-      </c>
-      <c r="Q24">
-        <v>69.4</v>
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
       </c>
       <c r="R24">
-        <v>83.4</v>
-      </c>
-      <c r="S24">
-        <v>4</v>
-      </c>
-      <c r="T24">
-        <v>0.4</v>
+        <v>1746</v>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
       </c>
       <c r="U24">
-        <v>6.38</v>
-      </c>
-      <c r="V24">
-        <v>160</v>
-      </c>
-      <c r="W24">
-        <v>96</v>
-      </c>
-      <c r="X24">
-        <v>16.3</v>
+        <v>128.3</v>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <v/>
       </c>
       <c r="Y24" t="str">
-        <v>Ø12 a200</v>
+        <v/>
       </c>
       <c r="Z24">
-        <v>291</v>
+        <v>5620</v>
       </c>
       <c r="AA24">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="AB24" t="str">
-        <v>Ø89×5</v>
-      </c>
-      <c r="AC24">
-        <v>3.7</v>
+        <v/>
+      </c>
+      <c r="AC24" t="str">
+        <v/>
       </c>
       <c r="AD24">
-        <v>118.1</v>
-      </c>
-      <c r="AE24">
-        <v>204.9</v>
-      </c>
-      <c r="AF24">
-        <v>318.7</v>
-      </c>
-      <c r="AG24">
-        <v>4.17</v>
-      </c>
-      <c r="AH24">
-        <v>0.71</v>
-      </c>
-      <c r="AI24">
-        <v>0.66</v>
-      </c>
-      <c r="AJ24">
-        <v>0.96</v>
-      </c>
-      <c r="AK24">
-        <v>0.53</v>
-      </c>
-      <c r="AL24">
-        <v>0.15</v>
-      </c>
-      <c r="AM24">
-        <v>0.62</v>
-      </c>
-      <c r="AN24" t="str">
-        <v>ĐẠT</v>
-      </c>
-      <c r="AO24" t="str">
-        <v>Đế lớn hơn đế mẫu</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>TỔNG</v>
-      </c>
-      <c r="B26" t="str">
-        <v>19 đế</v>
-      </c>
-      <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-      <c r="Q26" t="str">
-        <v/>
-      </c>
-      <c r="R26">
-        <v>1798</v>
-      </c>
-      <c r="S26" t="str">
-        <v/>
-      </c>
-      <c r="T26" t="str">
-        <v/>
-      </c>
-      <c r="U26">
-        <v>133.2</v>
-      </c>
-      <c r="V26" t="str">
-        <v/>
-      </c>
-      <c r="W26" t="str">
-        <v/>
-      </c>
-      <c r="X26" t="str">
-        <v/>
-      </c>
-      <c r="Y26" t="str">
-        <v/>
-      </c>
-      <c r="Z26">
-        <v>5859</v>
-      </c>
-      <c r="AA26">
-        <v>76</v>
-      </c>
-      <c r="AB26" t="str">
-        <v/>
-      </c>
-      <c r="AC26" t="str">
-        <v/>
-      </c>
-      <c r="AD26">
-        <v>2405</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
         <v>Ghi chú: cột M_lật, M_giữ, N 1 vít, sức chống nhổ là của tổ hợp chi phối; các cột SV là giá trị lớn nhất trên mọi tổ hợp.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AO27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AO25"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I35"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="34.83203125" customWidth="1"/>
@@ -25156,10 +25078,10 @@
         <v>Tổng số vít / tổng chiều dài</v>
       </c>
       <c r="C14" t="str">
-        <v>19 đế × 4 vít</v>
+        <v>17 đế × 4 vít</v>
       </c>
       <c r="D14" t="str">
-        <v>76 cây / 282.8 m</v>
+        <v>68 cây / 253.2 m</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -25507,7 +25429,7 @@
         <v>6</v>
       </c>
       <c r="C29">
-        <v>175.1</v>
+        <v>177.7</v>
       </c>
       <c r="D29">
         <v>194.4</v>
@@ -25565,7 +25487,7 @@
         <v>5.75</v>
       </c>
       <c r="C31">
-        <v>169.3</v>
+        <v>171.2</v>
       </c>
       <c r="D31">
         <v>178.5</v>
@@ -25591,13 +25513,13 @@
         <v>BM-DV014</v>
       </c>
       <c r="B32">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="C32">
-        <v>19.1</v>
+        <v>156.6</v>
       </c>
       <c r="D32">
-        <v>33.8</v>
+        <v>178.5</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -25620,25 +25542,25 @@
         <v>BM-DV015</v>
       </c>
       <c r="B33">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>37.8</v>
+        <v>83.3</v>
       </c>
       <c r="D33">
-        <v>33.8</v>
+        <v>86.4</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>5.55</v>
+        <v>4.23</v>
       </c>
       <c r="G33">
         <v>7.92</v>
       </c>
       <c r="H33">
-        <v>0.7</v>
+        <v>0.53</v>
       </c>
       <c r="I33" t="str">
         <v>ĐẠT</v>
@@ -25649,25 +25571,25 @@
         <v>BM-DV016</v>
       </c>
       <c r="B34">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="C34">
-        <v>156.6</v>
+        <v>85</v>
       </c>
       <c r="D34">
-        <v>178.5</v>
+        <v>86.4</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="G34">
         <v>7.92</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="I34" t="str">
         <v>ĐẠT</v>
@@ -25681,7 +25603,7 @@
         <v>4</v>
       </c>
       <c r="C35">
-        <v>83.3</v>
+        <v>83.4</v>
       </c>
       <c r="D35">
         <v>86.4</v>
@@ -25690,7 +25612,7 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="G35">
         <v>7.92</v>
@@ -25702,67 +25624,9 @@
         <v>ĐẠT</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>BM-DV018</v>
-      </c>
-      <c r="B36">
-        <v>4</v>
-      </c>
-      <c r="C36">
-        <v>85</v>
-      </c>
-      <c r="D36">
-        <v>86.4</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>4.94</v>
-      </c>
-      <c r="G36">
-        <v>7.92</v>
-      </c>
-      <c r="H36">
-        <v>0.62</v>
-      </c>
-      <c r="I36" t="str">
-        <v>ĐẠT</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>BM-DV019</v>
-      </c>
-      <c r="B37">
-        <v>4</v>
-      </c>
-      <c r="C37">
-        <v>83.4</v>
-      </c>
-      <c r="D37">
-        <v>86.4</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>4.17</v>
-      </c>
-      <c r="G37">
-        <v>7.92</v>
-      </c>
-      <c r="H37">
-        <v>0.53</v>
-      </c>
-      <c r="I37" t="str">
-        <v>ĐẠT</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I35"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -25834,16 +25698,16 @@
         <v>md</v>
       </c>
       <c r="D6" s="1">
-        <v>1227.6</v>
+        <v>1240.8</v>
       </c>
       <c r="E6" s="2">
         <v>480000</v>
       </c>
       <c r="F6" s="2">
-        <v>589248000</v>
+        <v>595584000</v>
       </c>
       <c r="G6" t="str">
-        <v>Đơn giá trọn gói vật tư + nhân công; 186 cọc</v>
+        <v>Đơn giá trọn gói vật tư + nhân công; 188 cọc</v>
       </c>
     </row>
     <row r="7">
@@ -25857,7 +25721,7 @@
         <v>m³</v>
       </c>
       <c r="D7" s="1">
-        <v>133.2</v>
+        <v>128.3</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
@@ -25879,8 +25743,8 @@
       <c r="C8" t="str">
         <v>kg</v>
       </c>
-      <c r="D8" s="1">
-        <v>5858.8</v>
+      <c r="D8" s="2">
+        <v>5620</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
@@ -25903,7 +25767,7 @@
         <v>md</v>
       </c>
       <c r="D9" s="1">
-        <v>282.8</v>
+        <v>253.2</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
@@ -25926,7 +25790,7 @@
         <v>đế</v>
       </c>
       <c r="D10" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
@@ -25986,7 +25850,7 @@
         <v/>
       </c>
       <c r="F13" s="2">
-        <v>639248000</v>
+        <v>645584000</v>
       </c>
     </row>
     <row r="14">
@@ -26006,7 +25870,7 @@
         <v/>
       </c>
       <c r="F14" s="2">
-        <v>31962400</v>
+        <v>32279200</v>
       </c>
     </row>
     <row r="15">
@@ -26026,7 +25890,7 @@
         <v/>
       </c>
       <c r="F15" s="2">
-        <v>53696832</v>
+        <v>54229056</v>
       </c>
     </row>
     <row r="16">
@@ -26046,7 +25910,7 @@
         <v/>
       </c>
       <c r="F16" s="2">
-        <v>724907232</v>
+        <v>732092256</v>
       </c>
     </row>
     <row r="17">
@@ -26070,7 +25934,7 @@
         <v>m³</v>
       </c>
       <c r="D19" s="1">
-        <v>118.1</v>
+        <v>119.4</v>
       </c>
     </row>
     <row r="20">
@@ -26084,7 +25948,7 @@
         <v>tấn</v>
       </c>
       <c r="D20" s="1">
-        <v>36.2</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="21">
@@ -26193,22 +26057,22 @@
         <v>BÈ 3</v>
       </c>
       <c r="B28" s="2">
-        <v>15</v>
-      </c>
-      <c r="C28" s="2">
-        <v>99</v>
+        <v>17</v>
+      </c>
+      <c r="C28" s="1">
+        <v>112.2</v>
       </c>
       <c r="D28" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="1">
-        <v>18.8</v>
+        <v>13.8</v>
       </c>
       <c r="F28" s="2">
-        <v>865</v>
+        <v>626</v>
       </c>
       <c r="G28" s="1">
-        <v>44.4</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="29">
@@ -26317,7 +26181,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>BẢNG CHIỀU DÀI CẮT CÁP NEO (215 TUYẾN: 186 dây bờ, 29 dây đáy) — BM-FPV-2026</v>
+        <v>BẢNG CHIỀU DÀI CẮT CÁP NEO (215 TUYẾN: 188 dây bờ, 27 dây đáy) — BM-FPV-2026</v>
       </c>
     </row>
     <row r="2">
@@ -33899,61 +33763,61 @@
         <v>BÈ 3</v>
       </c>
       <c r="D117" t="str">
-        <v>ĐÁY</v>
+        <v>BỜ</v>
       </c>
       <c r="E117" t="str">
-        <v>DV-014</v>
+        <v>-</v>
       </c>
       <c r="F117">
-        <v>17.5</v>
+        <v>46.16</v>
       </c>
       <c r="G117">
-        <v>654.99</v>
+        <v>663.18</v>
       </c>
       <c r="H117">
-        <v>18.24</v>
+        <v>48.05</v>
       </c>
       <c r="I117">
-        <v>19.29</v>
+        <v>46.16</v>
       </c>
       <c r="J117">
-        <v>22.67</v>
+        <v>46.58</v>
       </c>
       <c r="K117" t="str">
-        <v>MNLKT</v>
+        <v>MNC</v>
       </c>
       <c r="L117">
-        <v>22.67</v>
+        <v>48.05</v>
       </c>
       <c r="M117">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="N117">
-        <v>3.38</v>
+        <v>1.89</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P117">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q117">
-        <v>3.67</v>
+        <v>1.89</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S117">
-        <v>-16.4</v>
+        <v>-16.1</v>
       </c>
       <c r="T117">
-        <v>24.9</v>
+        <v>-0.1</v>
       </c>
       <c r="U117">
-        <v>39.5</v>
+        <v>7.7</v>
       </c>
       <c r="V117" t="str">
-        <v>Cáp dốc tới 39°: thành phần đứng lớn tại bích bè; Đo cao độ đáy thực tế trước khi cắt</v>
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -34035,61 +33899,61 @@
         <v>BÈ 3</v>
       </c>
       <c r="D119" t="str">
-        <v>ĐÁY</v>
+        <v>BỜ</v>
       </c>
       <c r="E119" t="str">
-        <v>DV-015</v>
+        <v>-</v>
       </c>
       <c r="F119">
-        <v>17.5</v>
+        <v>42</v>
       </c>
       <c r="G119">
-        <v>652.12</v>
+        <v>662.42</v>
       </c>
       <c r="H119">
-        <v>17.65</v>
+        <v>43.84</v>
       </c>
       <c r="I119">
-        <v>20.66</v>
+        <v>42.01</v>
       </c>
       <c r="J119">
-        <v>24.59</v>
+        <v>42.58</v>
       </c>
       <c r="K119" t="str">
-        <v>MNLKT</v>
+        <v>MNC</v>
       </c>
       <c r="L119">
-        <v>24.59</v>
+        <v>43.84</v>
       </c>
       <c r="M119">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="N119">
-        <v>3.93</v>
+        <v>1.84</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P119">
-        <v>6.99</v>
+        <v>0</v>
       </c>
       <c r="Q119">
-        <v>4.5</v>
+        <v>1.84</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S119">
-        <v>-7.4</v>
+        <v>-16.7</v>
       </c>
       <c r="T119">
-        <v>32.1</v>
+        <v>0.9</v>
       </c>
       <c r="U119">
-        <v>44.6</v>
+        <v>9.4</v>
       </c>
       <c r="V119" t="str">
-        <v>Cáp dốc tới 45°: thành phần đứng lớn tại bích bè; Đo cao độ đáy thực tế trước khi cắt</v>
+        <v/>
       </c>
     </row>
     <row r="120">
@@ -36554,7 +36418,7 @@
         <v>ĐÁY</v>
       </c>
       <c r="E156" t="str">
-        <v>DV-016</v>
+        <v>DV-014</v>
       </c>
       <c r="F156">
         <v>23.39</v>
@@ -37982,7 +37846,7 @@
         <v>ĐÁY</v>
       </c>
       <c r="E177" t="str">
-        <v>DV-016</v>
+        <v>DV-014</v>
       </c>
       <c r="F177">
         <v>23.4</v>
@@ -38458,7 +38322,7 @@
         <v>ĐÁY</v>
       </c>
       <c r="E184" t="str">
-        <v>DV-017</v>
+        <v>DV-015</v>
       </c>
       <c r="F184">
         <v>17.51</v>
@@ -39274,7 +39138,7 @@
         <v>ĐÁY</v>
       </c>
       <c r="E196" t="str">
-        <v>DV-018</v>
+        <v>DV-016</v>
       </c>
       <c r="F196">
         <v>17.51</v>
@@ -40702,7 +40566,7 @@
         <v>ĐÁY</v>
       </c>
       <c r="E217" t="str">
-        <v>DV-019</v>
+        <v>DV-017</v>
       </c>
       <c r="F217">
         <v>17.51</v>
@@ -41043,7 +40907,7 @@
         <v>Tổng chiều dài cắt dây bờ (chốt tới chốt)</v>
       </c>
       <c r="B224">
-        <v>8624.3</v>
+        <v>8716.2</v>
       </c>
       <c r="C224" t="str">
         <v>m</v>
@@ -41054,7 +40918,7 @@
         <v>Tổng chiều dài cắt dây đáy (chốt tới chốt)</v>
       </c>
       <c r="B225">
-        <v>767</v>
+        <v>719.7</v>
       </c>
       <c r="C225" t="str">
         <v>m</v>
@@ -41065,7 +40929,7 @@
         <v>Số dây do MNC chi phối</v>
       </c>
       <c r="B226">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C226" t="str">
         <v>dây</v>
@@ -41087,7 +40951,7 @@
         <v>Số dây do MNLKT chi phối</v>
       </c>
       <c r="B228">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C228" t="str">
         <v>dây</v>
